--- a/AAII_Financials/Quarterly/KMTUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KMTUY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>KMTUY</t>
   </si>
@@ -656,410 +656,422 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6131700</v>
+        <v>6551300</v>
       </c>
       <c r="E8" s="3">
-        <v>5973000</v>
+        <v>6224000</v>
       </c>
       <c r="F8" s="3">
-        <v>6668200</v>
+        <v>6063000</v>
       </c>
       <c r="G8" s="3">
-        <v>6112100</v>
+        <v>6768600</v>
       </c>
       <c r="H8" s="3">
-        <v>5676700</v>
+        <v>6204100</v>
       </c>
       <c r="I8" s="3">
-        <v>5071700</v>
+        <v>5762200</v>
       </c>
       <c r="J8" s="3">
+        <v>5148100</v>
+      </c>
+      <c r="K8" s="3">
         <v>5230000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4968900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4637000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4764800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4794300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4072500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3887100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3913000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5439500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5593100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5548200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5585500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>6790800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6613400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6242700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5872700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6285600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5847500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5403600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5073300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5111600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3819400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3608800</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4156400</v>
+        <v>4481900</v>
       </c>
       <c r="E9" s="3">
-        <v>4058600</v>
+        <v>4219000</v>
       </c>
       <c r="F9" s="3">
-        <v>4733200</v>
+        <v>4119800</v>
       </c>
       <c r="G9" s="3">
-        <v>4277200</v>
+        <v>4804500</v>
       </c>
       <c r="H9" s="3">
-        <v>3997600</v>
+        <v>4341600</v>
       </c>
       <c r="I9" s="3">
-        <v>3621500</v>
+        <v>4057800</v>
       </c>
       <c r="J9" s="3">
+        <v>3676000</v>
+      </c>
+      <c r="K9" s="3">
         <v>3769800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3589200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3298400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3491800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3540700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2999800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2844100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2855200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3983000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4023200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3933000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3914600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4734300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4644500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4266600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4011000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4364100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4072000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>3892100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3635600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3643900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2714800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2572600</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1975300</v>
+        <v>2069300</v>
       </c>
       <c r="E10" s="3">
-        <v>1914400</v>
+        <v>2005100</v>
       </c>
       <c r="F10" s="3">
-        <v>1934900</v>
+        <v>1943200</v>
       </c>
       <c r="G10" s="3">
-        <v>1834900</v>
+        <v>1964100</v>
       </c>
       <c r="H10" s="3">
-        <v>1679100</v>
+        <v>1862500</v>
       </c>
       <c r="I10" s="3">
-        <v>1450200</v>
+        <v>1704400</v>
       </c>
       <c r="J10" s="3">
+        <v>1472100</v>
+      </c>
+      <c r="K10" s="3">
         <v>1460200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1379700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1338600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1272900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1253500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1072700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1043000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1057800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1456500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1569900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1615200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1670900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>2056500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1968800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1976100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1861700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1921400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1775500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1511500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1437700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1467700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1104600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1036300</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1092,8 +1104,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1184,8 +1197,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1276,8 +1292,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1287,11 +1306,11 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
-        <v>36700</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="G14" s="3">
+        <v>37200</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1299,11 +1318,11 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>9100</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1311,11 +1330,11 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>17000</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
@@ -1332,8 +1351,8 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1341,8 +1360,8 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1359,17 +1378,20 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
         <v>15500</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1460,8 +1482,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1491,192 +1516,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5136000</v>
+        <v>5496800</v>
       </c>
       <c r="E17" s="3">
-        <v>4996800</v>
+        <v>5213300</v>
       </c>
       <c r="F17" s="3">
-        <v>5711400</v>
+        <v>5072100</v>
       </c>
       <c r="G17" s="3">
-        <v>5215900</v>
+        <v>5797500</v>
       </c>
       <c r="H17" s="3">
-        <v>4892700</v>
+        <v>5294500</v>
       </c>
       <c r="I17" s="3">
-        <v>4450400</v>
+        <v>4966400</v>
       </c>
       <c r="J17" s="3">
+        <v>4517500</v>
+      </c>
+      <c r="K17" s="3">
         <v>4610800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4367900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4099600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4310900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4370300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3726600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3626700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3683400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5061800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4993300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4930400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4900700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5810800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5711600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5274100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4999600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5531700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5170900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4865900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4606000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4516700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3304300</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>995700</v>
+        <v>1054400</v>
       </c>
       <c r="E18" s="3">
-        <v>976200</v>
+        <v>1010700</v>
       </c>
       <c r="F18" s="3">
-        <v>956700</v>
+        <v>990900</v>
       </c>
       <c r="G18" s="3">
-        <v>896200</v>
+        <v>971100</v>
       </c>
       <c r="H18" s="3">
-        <v>784000</v>
+        <v>909700</v>
       </c>
       <c r="I18" s="3">
-        <v>621300</v>
+        <v>795800</v>
       </c>
       <c r="J18" s="3">
+        <v>630600</v>
+      </c>
+      <c r="K18" s="3">
         <v>619200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>601000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>537400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>453900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>423900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>345900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>260400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>229600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>377800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>599900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>617800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>684800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>979900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>901800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>968600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>873100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>753900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>676500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>537700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>467400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>594900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>380500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>304600</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1709,468 +1741,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>19500</v>
+        <v>3100</v>
       </c>
       <c r="E20" s="3">
-        <v>87000</v>
+        <v>19800</v>
       </c>
       <c r="F20" s="3">
-        <v>20100</v>
+        <v>88300</v>
       </c>
       <c r="G20" s="3">
-        <v>-79200</v>
+        <v>20400</v>
       </c>
       <c r="H20" s="3">
-        <v>22800</v>
+        <v>-80400</v>
       </c>
       <c r="I20" s="3">
-        <v>156600</v>
+        <v>23100</v>
       </c>
       <c r="J20" s="3">
+        <v>159000</v>
+      </c>
+      <c r="K20" s="3">
         <v>67100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>25400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>23800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>19600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>20000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>5800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>46200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-35100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>15000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-11000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>37200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-35000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>12000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>21000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-17900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>14300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>372500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-11900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>36500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1273900</v>
+        <v>1333800</v>
       </c>
       <c r="E21" s="3">
-        <v>1312200</v>
+        <v>1293100</v>
       </c>
       <c r="F21" s="3">
-        <v>1229900</v>
+        <v>1331900</v>
       </c>
       <c r="G21" s="3">
-        <v>1072600</v>
+        <v>1248400</v>
       </c>
       <c r="H21" s="3">
-        <v>1051800</v>
+        <v>1088800</v>
       </c>
       <c r="I21" s="3">
-        <v>1018100</v>
+        <v>1067600</v>
       </c>
       <c r="J21" s="3">
+        <v>1033400</v>
+      </c>
+      <c r="K21" s="3">
         <v>933900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>841300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>802800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>725200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>691100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>597700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>517900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>547300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>645500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>911300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>916800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>973100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1337600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1176100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1281800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1193400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1052800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>992600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1205300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>763800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>821800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>643700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>539800</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>86600</v>
+        <v>98800</v>
       </c>
       <c r="E22" s="3">
-        <v>79400</v>
+        <v>87900</v>
       </c>
       <c r="F22" s="3">
-        <v>69600</v>
+        <v>80600</v>
       </c>
       <c r="G22" s="3">
-        <v>73000</v>
+        <v>70700</v>
       </c>
       <c r="H22" s="3">
-        <v>41300</v>
+        <v>74100</v>
       </c>
       <c r="I22" s="3">
-        <v>31000</v>
+        <v>41900</v>
       </c>
       <c r="J22" s="3">
+        <v>31500</v>
+      </c>
+      <c r="K22" s="3">
         <v>20600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>23100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>21800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>22700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>23200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>27800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>32800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>50200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>52700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>59300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>60900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>61000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>59900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>55600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>49300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>44700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>46900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>42200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>32300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>22400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>16300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>928600</v>
+        <v>958800</v>
       </c>
       <c r="E23" s="3">
-        <v>983800</v>
+        <v>942600</v>
       </c>
       <c r="F23" s="3">
-        <v>907200</v>
+        <v>998700</v>
       </c>
       <c r="G23" s="3">
-        <v>744000</v>
+        <v>920900</v>
       </c>
       <c r="H23" s="3">
-        <v>765500</v>
+        <v>755200</v>
       </c>
       <c r="I23" s="3">
-        <v>746800</v>
+        <v>777000</v>
       </c>
       <c r="J23" s="3">
+        <v>758100</v>
+      </c>
+      <c r="K23" s="3">
         <v>665700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>603200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>541100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>451700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>421300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>328600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>234000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>243100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>292400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>562200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>563400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>612900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>956100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>806800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>925000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>844800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>691300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>643900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>868000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>434800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>560600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>400600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>300600</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>238700</v>
+        <v>266300</v>
       </c>
       <c r="E24" s="3">
-        <v>256900</v>
+        <v>242300</v>
       </c>
       <c r="F24" s="3">
-        <v>254500</v>
+        <v>260700</v>
       </c>
       <c r="G24" s="3">
+        <v>258300</v>
+      </c>
+      <c r="H24" s="3">
+        <v>258500</v>
+      </c>
+      <c r="I24" s="3">
+        <v>197800</v>
+      </c>
+      <c r="J24" s="3">
+        <v>198900</v>
+      </c>
+      <c r="K24" s="3">
+        <v>204400</v>
+      </c>
+      <c r="L24" s="3">
+        <v>158600</v>
+      </c>
+      <c r="M24" s="3">
+        <v>149000</v>
+      </c>
+      <c r="N24" s="3">
+        <v>132500</v>
+      </c>
+      <c r="O24" s="3">
+        <v>113200</v>
+      </c>
+      <c r="P24" s="3">
+        <v>101500</v>
+      </c>
+      <c r="Q24" s="3">
+        <v>56700</v>
+      </c>
+      <c r="R24" s="3">
+        <v>83700</v>
+      </c>
+      <c r="S24" s="3">
+        <v>114500</v>
+      </c>
+      <c r="T24" s="3">
+        <v>129800</v>
+      </c>
+      <c r="U24" s="3">
+        <v>163500</v>
+      </c>
+      <c r="V24" s="3">
+        <v>163300</v>
+      </c>
+      <c r="W24" s="3">
+        <v>239900</v>
+      </c>
+      <c r="X24" s="3">
+        <v>227500</v>
+      </c>
+      <c r="Y24" s="3">
+        <v>274200</v>
+      </c>
+      <c r="Z24" s="3">
         <v>254700</v>
       </c>
-      <c r="H24" s="3">
-        <v>194900</v>
-      </c>
-      <c r="I24" s="3">
-        <v>196000</v>
-      </c>
-      <c r="J24" s="3">
-        <v>204400</v>
-      </c>
-      <c r="K24" s="3">
-        <v>158600</v>
-      </c>
-      <c r="L24" s="3">
-        <v>149000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>132500</v>
-      </c>
-      <c r="N24" s="3">
-        <v>113200</v>
-      </c>
-      <c r="O24" s="3">
-        <v>101500</v>
-      </c>
-      <c r="P24" s="3">
-        <v>56700</v>
-      </c>
-      <c r="Q24" s="3">
-        <v>83700</v>
-      </c>
-      <c r="R24" s="3">
-        <v>114500</v>
-      </c>
-      <c r="S24" s="3">
-        <v>129800</v>
-      </c>
-      <c r="T24" s="3">
-        <v>163500</v>
-      </c>
-      <c r="U24" s="3">
-        <v>163300</v>
-      </c>
-      <c r="V24" s="3">
-        <v>239900</v>
-      </c>
-      <c r="W24" s="3">
-        <v>227500</v>
-      </c>
-      <c r="X24" s="3">
-        <v>274200</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>254700</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>293100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>142000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>259900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>85900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>135000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>124400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>105900</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2261,192 +2309,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>689900</v>
+        <v>692400</v>
       </c>
       <c r="E26" s="3">
-        <v>727000</v>
+        <v>700300</v>
       </c>
       <c r="F26" s="3">
-        <v>652800</v>
+        <v>737900</v>
       </c>
       <c r="G26" s="3">
-        <v>489300</v>
+        <v>662600</v>
       </c>
       <c r="H26" s="3">
-        <v>570600</v>
+        <v>496700</v>
       </c>
       <c r="I26" s="3">
-        <v>550900</v>
+        <v>579200</v>
       </c>
       <c r="J26" s="3">
+        <v>559200</v>
+      </c>
+      <c r="K26" s="3">
         <v>461200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>444600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>392100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>319200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>308000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>227100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>177200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>159300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>177900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>432300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>399900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>449600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>716200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>579400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>650800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>590100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>398100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>501800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>608200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>348900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>425700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>276200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>194700</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>664800</v>
+        <v>665400</v>
       </c>
       <c r="E27" s="3">
-        <v>700000</v>
+        <v>674800</v>
       </c>
       <c r="F27" s="3">
-        <v>627400</v>
+        <v>710600</v>
       </c>
       <c r="G27" s="3">
-        <v>460400</v>
+        <v>636800</v>
       </c>
       <c r="H27" s="3">
-        <v>545200</v>
+        <v>467400</v>
       </c>
       <c r="I27" s="3">
-        <v>534200</v>
+        <v>553400</v>
       </c>
       <c r="J27" s="3">
+        <v>542300</v>
+      </c>
+      <c r="K27" s="3">
         <v>461000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>428400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>376700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>300600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>285500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>210200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>163900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>138600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>163700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>411800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>391400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>434900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>694700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>555200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>579800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>572400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>373800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>481900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>590900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>329000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>399600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>273300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2537,8 +2594,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2629,8 +2689,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2721,8 +2784,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2813,192 +2879,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-19500</v>
+        <v>-3100</v>
       </c>
       <c r="E32" s="3">
-        <v>-87000</v>
+        <v>-19800</v>
       </c>
       <c r="F32" s="3">
-        <v>-20100</v>
+        <v>-88300</v>
       </c>
       <c r="G32" s="3">
-        <v>79200</v>
+        <v>-20400</v>
       </c>
       <c r="H32" s="3">
-        <v>-22800</v>
+        <v>80400</v>
       </c>
       <c r="I32" s="3">
-        <v>-156600</v>
+        <v>-23100</v>
       </c>
       <c r="J32" s="3">
+        <v>-159000</v>
+      </c>
+      <c r="K32" s="3">
         <v>-67100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-25400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-23800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-19600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-20000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-5800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-46200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>35100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-15000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>11000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-37200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>35000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-21000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>17900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-14300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-372500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>11900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-36500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-12800</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>664800</v>
+        <v>665400</v>
       </c>
       <c r="E33" s="3">
-        <v>700000</v>
+        <v>674800</v>
       </c>
       <c r="F33" s="3">
-        <v>627400</v>
+        <v>710600</v>
       </c>
       <c r="G33" s="3">
-        <v>460400</v>
+        <v>636800</v>
       </c>
       <c r="H33" s="3">
-        <v>545200</v>
+        <v>467400</v>
       </c>
       <c r="I33" s="3">
-        <v>534200</v>
+        <v>553400</v>
       </c>
       <c r="J33" s="3">
+        <v>542300</v>
+      </c>
+      <c r="K33" s="3">
         <v>461000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>428400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>376700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>300600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>285500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>210200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>163900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>138600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>163700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>411800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>391400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>434900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>694700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>555200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>579800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>572400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>373800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>481900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>590900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>329000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>399600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>273300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3089,197 +3164,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>664800</v>
+        <v>665400</v>
       </c>
       <c r="E35" s="3">
-        <v>700000</v>
+        <v>674800</v>
       </c>
       <c r="F35" s="3">
-        <v>627400</v>
+        <v>710600</v>
       </c>
       <c r="G35" s="3">
-        <v>460400</v>
+        <v>636800</v>
       </c>
       <c r="H35" s="3">
-        <v>545200</v>
+        <v>467400</v>
       </c>
       <c r="I35" s="3">
-        <v>534200</v>
+        <v>553400</v>
       </c>
       <c r="J35" s="3">
+        <v>542300</v>
+      </c>
+      <c r="K35" s="3">
         <v>461000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>428400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>376700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>300600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>285500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>210200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>163900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>138600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>163700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>411800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>391400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>434900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>694700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>555200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>579800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>572400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>373800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>481900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>590900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>329000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>399600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>273300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3312,8 +3396,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3346,100 +3431,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2106800</v>
+        <v>2314900</v>
       </c>
       <c r="E41" s="3">
-        <v>2280600</v>
+        <v>2138500</v>
       </c>
       <c r="F41" s="3">
-        <v>1925400</v>
+        <v>2315000</v>
       </c>
       <c r="G41" s="3">
-        <v>2218700</v>
+        <v>1954400</v>
       </c>
       <c r="H41" s="3">
-        <v>2130300</v>
+        <v>2252100</v>
       </c>
       <c r="I41" s="3">
-        <v>2546700</v>
+        <v>2162400</v>
       </c>
       <c r="J41" s="3">
+        <v>2585100</v>
+      </c>
+      <c r="K41" s="3">
         <v>2094000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1862000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1975600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1732900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1723800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1601600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1837300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2194200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2199600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1689900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1514000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1792800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1449300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1421600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1196300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1343400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1327600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1516900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1482200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1381200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1083800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1209600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>789900</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3452,24 +3541,24 @@
       <c r="F42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G42" s="3">
-        <v>13400</v>
+      <c r="G42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H42" s="3">
-        <v>5100</v>
+        <v>13600</v>
       </c>
       <c r="I42" s="3">
-        <v>7200</v>
+        <v>5200</v>
       </c>
       <c r="J42" s="3">
+        <v>7300</v>
+      </c>
+      <c r="K42" s="3">
         <v>8700</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>15600</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3530,652 +3619,676 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>7423500</v>
+        <v>7594700</v>
       </c>
       <c r="E43" s="3">
-        <v>7567300</v>
+        <v>7535300</v>
       </c>
       <c r="F43" s="3">
-        <v>7383100</v>
+        <v>7681300</v>
       </c>
       <c r="G43" s="3">
-        <v>6439100</v>
+        <v>7494300</v>
       </c>
       <c r="H43" s="3">
-        <v>6879400</v>
+        <v>6536100</v>
       </c>
       <c r="I43" s="3">
-        <v>6606400</v>
+        <v>6983100</v>
       </c>
       <c r="J43" s="3">
+        <v>6705900</v>
+      </c>
+      <c r="K43" s="3">
         <v>6338400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5855300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5745200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5791100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5818700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5049300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5218600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5668600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>6558100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>7002300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6799600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7109800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8093400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7464600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7593000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7131300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7166100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>6920900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6481500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>5949400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5492900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5117000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>4460600</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>9903700</v>
+        <v>9838200</v>
       </c>
       <c r="E44" s="3">
-        <v>9260500</v>
+        <v>10052800</v>
       </c>
       <c r="F44" s="3">
-        <v>8148700</v>
+        <v>9400000</v>
       </c>
       <c r="G44" s="3">
-        <v>8260400</v>
+        <v>8271400</v>
       </c>
       <c r="H44" s="3">
-        <v>8466200</v>
+        <v>8384800</v>
       </c>
       <c r="I44" s="3">
-        <v>7799600</v>
+        <v>8593700</v>
       </c>
       <c r="J44" s="3">
+        <v>7917100</v>
+      </c>
+      <c r="K44" s="3">
         <v>6560400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6192300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6123000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6020100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5628400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6025000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6535000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7393100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7094800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8199300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8217800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8015200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8048900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>7793600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>7851600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>7246200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>6601800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6847600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6441600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6211000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>4735700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5252300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4645600</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1648800</v>
+        <v>1453300</v>
       </c>
       <c r="E45" s="3">
-        <v>1647000</v>
+        <v>1673600</v>
       </c>
       <c r="F45" s="3">
-        <v>1377700</v>
+        <v>1671800</v>
       </c>
       <c r="G45" s="3">
-        <v>1316600</v>
+        <v>1398400</v>
       </c>
       <c r="H45" s="3">
-        <v>1328600</v>
+        <v>1336500</v>
       </c>
       <c r="I45" s="3">
-        <v>1244200</v>
+        <v>1348600</v>
       </c>
       <c r="J45" s="3">
+        <v>1262900</v>
+      </c>
+      <c r="K45" s="3">
         <v>1075800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1124300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>991000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1023700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>933200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>962600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1023800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1269500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1298700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1368900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1225300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1322900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1330200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1291000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1205900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1188900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1154700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1105700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1052800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1084600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1278800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1242800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1155000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>21082800</v>
+        <v>21201100</v>
       </c>
       <c r="E46" s="3">
-        <v>20755400</v>
+        <v>21400300</v>
       </c>
       <c r="F46" s="3">
-        <v>18834900</v>
+        <v>21068000</v>
       </c>
       <c r="G46" s="3">
-        <v>18248200</v>
+        <v>19118500</v>
       </c>
       <c r="H46" s="3">
-        <v>18809600</v>
+        <v>18523000</v>
       </c>
       <c r="I46" s="3">
-        <v>18204100</v>
+        <v>19092800</v>
       </c>
       <c r="J46" s="3">
+        <v>18478300</v>
+      </c>
+      <c r="K46" s="3">
         <v>16077300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>15049600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>14834700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14567700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14104100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>13638400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14614700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>16525500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>17151200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>18260400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>17756700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>18240800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18921700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17970800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17846800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>16909800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16250200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16391200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>15458100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>14626200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>12591200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>12821700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>11051100</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4824100</v>
+        <v>4749300</v>
       </c>
       <c r="E47" s="3">
-        <v>4687600</v>
+        <v>4896800</v>
       </c>
       <c r="F47" s="3">
-        <v>4200300</v>
+        <v>4758200</v>
       </c>
       <c r="G47" s="3">
-        <v>4275400</v>
+        <v>4263500</v>
       </c>
       <c r="H47" s="3">
-        <v>4548500</v>
+        <v>4339700</v>
       </c>
       <c r="I47" s="3">
-        <v>4243200</v>
+        <v>4617000</v>
       </c>
       <c r="J47" s="3">
+        <v>4307100</v>
+      </c>
+      <c r="K47" s="3">
         <v>3692900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3632900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3650400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3831400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3505200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3513400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3679600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4108100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4109500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4302400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4281700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4254400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4431700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3945800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4110500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3870100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3656300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3775100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3603400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3962700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3654400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3553700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3114700</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6302700</v>
+        <v>6399900</v>
       </c>
       <c r="E48" s="3">
-        <v>6188500</v>
+        <v>6397600</v>
       </c>
       <c r="F48" s="3">
-        <v>5959400</v>
+        <v>6281700</v>
       </c>
       <c r="G48" s="3">
-        <v>5908600</v>
+        <v>6049100</v>
       </c>
       <c r="H48" s="3">
-        <v>6184600</v>
+        <v>5997600</v>
       </c>
       <c r="I48" s="3">
-        <v>6082900</v>
+        <v>6277700</v>
       </c>
       <c r="J48" s="3">
+        <v>6174500</v>
+      </c>
+      <c r="K48" s="3">
         <v>5851600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5836700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6043400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6152900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5993200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6007500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6325100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6898700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>7146100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7436500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7400100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7454200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7461400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7167800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7111300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>6849300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6694400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6941200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6903500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6874400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6023000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6087900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>5725600</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2645400</v>
+        <v>2812400</v>
       </c>
       <c r="E49" s="3">
-        <v>2624200</v>
+        <v>2685300</v>
       </c>
       <c r="F49" s="3">
-        <v>2485700</v>
+        <v>2663700</v>
       </c>
       <c r="G49" s="3">
-        <v>2471800</v>
+        <v>2523100</v>
       </c>
       <c r="H49" s="3">
-        <v>2700500</v>
+        <v>2509000</v>
       </c>
       <c r="I49" s="3">
-        <v>2546700</v>
+        <v>2741200</v>
       </c>
       <c r="J49" s="3">
+        <v>2585000</v>
+      </c>
+      <c r="K49" s="3">
         <v>2367900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2330800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2406100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2479900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2408200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2370200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2505800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2768200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2815500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3096100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3079300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2972100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3155200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3161900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3289100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3137100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2975000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3245200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3273300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3281300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>897200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>891700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>852900</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4266,8 +4379,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4358,100 +4474,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1028100</v>
+        <v>1027300</v>
       </c>
       <c r="E52" s="3">
-        <v>923500</v>
+        <v>1043600</v>
       </c>
       <c r="F52" s="3">
-        <v>895400</v>
+        <v>937400</v>
       </c>
       <c r="G52" s="3">
-        <v>859500</v>
+        <v>908900</v>
       </c>
       <c r="H52" s="3">
-        <v>973800</v>
+        <v>872400</v>
       </c>
       <c r="I52" s="3">
-        <v>895300</v>
+        <v>988400</v>
       </c>
       <c r="J52" s="3">
+        <v>908800</v>
+      </c>
+      <c r="K52" s="3">
         <v>877800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>818200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>849300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>827500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>823800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>807200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>875700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>926900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>966700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>877800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>911400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>893200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>993200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>881500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>914100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>875400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>911800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>925500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>867000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>685400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>397300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>395700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>472700</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4542,100 +4664,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>35883100</v>
+        <v>36189900</v>
       </c>
       <c r="E54" s="3">
-        <v>35179300</v>
+        <v>36423500</v>
       </c>
       <c r="F54" s="3">
-        <v>32375600</v>
+        <v>35709100</v>
       </c>
       <c r="G54" s="3">
-        <v>31763400</v>
+        <v>32863200</v>
       </c>
       <c r="H54" s="3">
-        <v>33216900</v>
+        <v>32241800</v>
       </c>
       <c r="I54" s="3">
-        <v>31972200</v>
+        <v>33717200</v>
       </c>
       <c r="J54" s="3">
+        <v>32453700</v>
+      </c>
+      <c r="K54" s="3">
         <v>28867500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>27668100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27783800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27859400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>26834500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26336600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>28001000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>31227300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>32189000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>33973200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>33429200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33814600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>34963300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33127800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33271700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>31641700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>30487700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>31278300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>30105200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>29429900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>23563000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>23750700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>21217100</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4668,8 +4796,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4702,560 +4831,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2315200</v>
+        <v>2169500</v>
       </c>
       <c r="E57" s="3">
-        <v>2439300</v>
+        <v>2350100</v>
       </c>
       <c r="F57" s="3">
-        <v>2406100</v>
+        <v>2476000</v>
       </c>
       <c r="G57" s="3">
-        <v>2244900</v>
+        <v>2442300</v>
       </c>
       <c r="H57" s="3">
-        <v>2364600</v>
+        <v>2278700</v>
       </c>
       <c r="I57" s="3">
-        <v>2307000</v>
+        <v>2400200</v>
       </c>
       <c r="J57" s="3">
+        <v>2341700</v>
+      </c>
+      <c r="K57" s="3">
         <v>2250800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1971700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1939100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1908900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1831500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1597300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1511700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1742400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1939600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>2091700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2278800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2338800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2565400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2413100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2557500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2485200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2744100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2742000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2594600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2526300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2129800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1891800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1680000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3303600</v>
+        <v>4242400</v>
       </c>
       <c r="E58" s="3">
-        <v>4047500</v>
+        <v>3353300</v>
       </c>
       <c r="F58" s="3">
-        <v>3237500</v>
+        <v>4108400</v>
       </c>
       <c r="G58" s="3">
-        <v>4086500</v>
+        <v>3286200</v>
       </c>
       <c r="H58" s="3">
-        <v>4827800</v>
+        <v>4148000</v>
       </c>
       <c r="I58" s="3">
-        <v>4572300</v>
+        <v>4900500</v>
       </c>
       <c r="J58" s="3">
+        <v>4641200</v>
+      </c>
+      <c r="K58" s="3">
         <v>3442000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3599600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3247400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2968400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2619500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2928500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3409100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5190700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5308400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5845400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5004000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>4708300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4403400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4835900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3995900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4127800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2982300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3226400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2743000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4866100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1932300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2705700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1856900</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3951300</v>
+        <v>3846700</v>
       </c>
       <c r="E59" s="3">
-        <v>3857200</v>
+        <v>4010900</v>
       </c>
       <c r="F59" s="3">
-        <v>3464300</v>
+        <v>3915300</v>
       </c>
       <c r="G59" s="3">
-        <v>3253500</v>
+        <v>3516400</v>
       </c>
       <c r="H59" s="3">
-        <v>3301900</v>
+        <v>3302500</v>
       </c>
       <c r="I59" s="3">
-        <v>3140700</v>
+        <v>3351700</v>
       </c>
       <c r="J59" s="3">
+        <v>3188000</v>
+      </c>
+      <c r="K59" s="3">
         <v>3098700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2715800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2697500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2611000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2588500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2524800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2635500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2809300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2959500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3169700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3262900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3290300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3430500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3011500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3336600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3020600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3220100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3131200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>2985200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2675700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2148500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1977100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1932900</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>9570100</v>
+        <v>10258500</v>
       </c>
       <c r="E60" s="3">
-        <v>10344000</v>
+        <v>9714200</v>
       </c>
       <c r="F60" s="3">
-        <v>9107800</v>
+        <v>10499800</v>
       </c>
       <c r="G60" s="3">
-        <v>9584800</v>
+        <v>9245000</v>
       </c>
       <c r="H60" s="3">
-        <v>10494300</v>
+        <v>9729200</v>
       </c>
       <c r="I60" s="3">
-        <v>10020000</v>
+        <v>10652300</v>
       </c>
       <c r="J60" s="3">
+        <v>10170900</v>
+      </c>
+      <c r="K60" s="3">
         <v>8791500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8287000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>7884100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7488300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7039400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7050600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7556300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>9742300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>10207500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>11106800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10545700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10337400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10399400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10260500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>9890100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9633600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>8946500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9099600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8322800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>10068000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>6210600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6574700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>5469800</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4349300</v>
+        <v>3895500</v>
       </c>
       <c r="E61" s="3">
-        <v>3961200</v>
+        <v>4414800</v>
       </c>
       <c r="F61" s="3">
-        <v>3759500</v>
+        <v>4020900</v>
       </c>
       <c r="G61" s="3">
-        <v>3638000</v>
+        <v>3816100</v>
       </c>
       <c r="H61" s="3">
-        <v>2944700</v>
+        <v>3692800</v>
       </c>
       <c r="I61" s="3">
-        <v>3155800</v>
+        <v>2989100</v>
       </c>
       <c r="J61" s="3">
+        <v>3203300</v>
+      </c>
+      <c r="K61" s="3">
         <v>2848600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2748000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2986100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3685700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3832300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3788600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4116400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3747600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3610700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3704600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3739100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4491900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4540600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4285500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4526300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4365800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4345500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4771500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4645600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2829700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1692900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1742600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1577700</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1932100</v>
+        <v>1884900</v>
       </c>
       <c r="E62" s="3">
-        <v>1838300</v>
+        <v>1961200</v>
       </c>
       <c r="F62" s="3">
-        <v>1726700</v>
+        <v>1866000</v>
       </c>
       <c r="G62" s="3">
-        <v>1686400</v>
+        <v>1752700</v>
       </c>
       <c r="H62" s="3">
-        <v>1768300</v>
+        <v>1711800</v>
       </c>
       <c r="I62" s="3">
-        <v>1709400</v>
+        <v>1795000</v>
       </c>
       <c r="J62" s="3">
+        <v>1735200</v>
+      </c>
+      <c r="K62" s="3">
         <v>1581700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1611800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1672700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1756800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1697600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1628100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1786600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1929800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2017500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1936900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1955600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1946800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1736800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1588900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1545500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1485000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1433600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1437400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1448700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1400700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1037100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1041600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>965200</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5346,8 +5494,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5438,8 +5589,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5530,100 +5684,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>16857900</v>
+        <v>17073100</v>
       </c>
       <c r="E66" s="3">
-        <v>17125800</v>
+        <v>17111700</v>
       </c>
       <c r="F66" s="3">
-        <v>15512400</v>
+        <v>17383700</v>
       </c>
       <c r="G66" s="3">
-        <v>15776600</v>
+        <v>15746000</v>
       </c>
       <c r="H66" s="3">
-        <v>16104600</v>
+        <v>16014200</v>
       </c>
       <c r="I66" s="3">
-        <v>15735600</v>
+        <v>16347200</v>
       </c>
       <c r="J66" s="3">
+        <v>15972600</v>
+      </c>
+      <c r="K66" s="3">
         <v>14043700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>13489900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13380200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13660300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13276300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13146300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14153500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16184500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16581100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>17541800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>16997900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>17543800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>17515500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16912800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16751000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16218100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>15440300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16046200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15109600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>14968700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>9577900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9984500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>8556800</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5656,8 +5816,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5748,8 +5909,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5840,8 +6004,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5932,8 +6099,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6024,100 +6194,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>15247200</v>
+        <v>15682900</v>
       </c>
       <c r="E72" s="3">
-        <v>14582400</v>
+        <v>15476800</v>
       </c>
       <c r="F72" s="3">
-        <v>14364300</v>
+        <v>14802000</v>
       </c>
       <c r="G72" s="3">
-        <v>13736900</v>
+        <v>14580600</v>
       </c>
       <c r="H72" s="3">
-        <v>13678500</v>
+        <v>13943800</v>
       </c>
       <c r="I72" s="3">
-        <v>13133200</v>
+        <v>13884500</v>
       </c>
       <c r="J72" s="3">
+        <v>13331000</v>
+      </c>
+      <c r="K72" s="3">
         <v>12950700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12922300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13385000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>13260900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12749900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12886400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>13604200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>14720100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>15384800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15739500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15939800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15497700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>16338300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15366800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15023600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>14132800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>13901600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13527900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13353100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>12762200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12442100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>12042600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12011900</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6208,8 +6384,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6300,8 +6479,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6392,100 +6574,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>19025300</v>
+        <v>19116800</v>
       </c>
       <c r="E76" s="3">
-        <v>18053500</v>
+        <v>19311800</v>
       </c>
       <c r="F76" s="3">
-        <v>16863200</v>
+        <v>18325400</v>
       </c>
       <c r="G76" s="3">
-        <v>15986800</v>
+        <v>17117200</v>
       </c>
       <c r="H76" s="3">
-        <v>17112300</v>
+        <v>16227600</v>
       </c>
       <c r="I76" s="3">
-        <v>16236600</v>
+        <v>17370000</v>
       </c>
       <c r="J76" s="3">
+        <v>16481100</v>
+      </c>
+      <c r="K76" s="3">
         <v>14823900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14178100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14403600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14199100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>13558200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13190300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13847500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15042800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15607800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16431500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16431400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16270800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>17447700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16215000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16520700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>15423500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>15047400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15232100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>14995700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14461200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>13985100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13766200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>12660300</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6576,197 +6764,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>664800</v>
+        <v>665400</v>
       </c>
       <c r="E81" s="3">
-        <v>700000</v>
+        <v>674800</v>
       </c>
       <c r="F81" s="3">
-        <v>627400</v>
+        <v>710600</v>
       </c>
       <c r="G81" s="3">
-        <v>460400</v>
+        <v>636800</v>
       </c>
       <c r="H81" s="3">
-        <v>545200</v>
+        <v>467400</v>
       </c>
       <c r="I81" s="3">
-        <v>534200</v>
+        <v>553400</v>
       </c>
       <c r="J81" s="3">
+        <v>542300</v>
+      </c>
+      <c r="K81" s="3">
         <v>461000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>428400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>376700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>300600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>285500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>210200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>163900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>138600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>163700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>411800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>391400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>434900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>694700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>555200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>579800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>572400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>373800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>481900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>590900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>329000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>399600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>273300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6799,100 +6996,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>258700</v>
+        <v>276300</v>
       </c>
       <c r="E83" s="3">
-        <v>248900</v>
+        <v>262600</v>
       </c>
       <c r="F83" s="3">
-        <v>253100</v>
+        <v>252700</v>
       </c>
       <c r="G83" s="3">
-        <v>255700</v>
+        <v>256900</v>
       </c>
       <c r="H83" s="3">
-        <v>245000</v>
+        <v>259500</v>
       </c>
       <c r="I83" s="3">
-        <v>240200</v>
+        <v>248700</v>
       </c>
       <c r="J83" s="3">
+        <v>243800</v>
+      </c>
+      <c r="K83" s="3">
         <v>247600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>215000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>241600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>251700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>247200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>245900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>256200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>271400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>302800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>296400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>294100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>299300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>320500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>309400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>301200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>299200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>316900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>301900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>295000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>296800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>238900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>226700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>222400</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6983,8 +7184,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7075,8 +7279,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7167,8 +7374,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7259,8 +7469,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7351,100 +7564,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>676500</v>
+        <v>614500</v>
       </c>
       <c r="E89" s="3">
-        <v>567300</v>
+        <v>686700</v>
       </c>
       <c r="F89" s="3">
-        <v>819400</v>
+        <v>575800</v>
       </c>
       <c r="G89" s="3">
-        <v>382000</v>
+        <v>831700</v>
       </c>
       <c r="H89" s="3">
-        <v>185100</v>
+        <v>387800</v>
       </c>
       <c r="I89" s="3">
-        <v>-15600</v>
+        <v>187900</v>
       </c>
       <c r="J89" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="K89" s="3">
         <v>770900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>188500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>669300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>474800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>813600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>636600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>759600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>469400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1208900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>202300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>715400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>530400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>982200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>259100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>677800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>603600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>3900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>357400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>376500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>971600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>448000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>444400</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7477,100 +7696,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-63292000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-48195000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-40522000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-48621000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-48655000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-49879000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-36378000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-39135000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-41538000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-44307000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-279100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-314200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-380900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-374000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-317900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-397700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-434800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-439600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-403000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-453500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-552400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-411600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-382200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-288700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-389600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-331300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-390900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-378000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-298900</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7661,8 +7884,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7753,100 +7979,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-279300</v>
+        <v>-534000</v>
       </c>
       <c r="E94" s="3">
-        <v>-261300</v>
+        <v>-283500</v>
       </c>
       <c r="F94" s="3">
-        <v>-256400</v>
+        <v>-265200</v>
       </c>
       <c r="G94" s="3">
-        <v>-302700</v>
+        <v>-260200</v>
       </c>
       <c r="H94" s="3">
-        <v>-344500</v>
+        <v>-307200</v>
       </c>
       <c r="I94" s="3">
-        <v>-222100</v>
+        <v>-349700</v>
       </c>
       <c r="J94" s="3">
+        <v>-225400</v>
+      </c>
+      <c r="K94" s="3">
         <v>-262000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-239100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-285800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-218000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-258800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-341100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-347300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-302300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-366600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-388200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-542900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-436300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-432300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-524300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-408300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-388400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-520100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-228800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>103500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2769300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-347600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-233600</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7879,100 +8111,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-459300</v>
       </c>
       <c r="E96" s="3">
-        <v>-471100</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-478200</v>
       </c>
       <c r="G96" s="3">
-        <v>-402000</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-408100</v>
       </c>
       <c r="I96" s="3">
-        <v>-351700</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-357000</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-259900</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-257100</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-124700</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-314400</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-473400</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-510400</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-454600</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-411800</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-307100</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-247400</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-242700</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8063,8 +8299,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8155,8 +8394,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8247,280 +8489,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-569800</v>
+        <v>113300</v>
       </c>
       <c r="E100" s="3">
-        <v>41200</v>
+        <v>-578400</v>
       </c>
       <c r="F100" s="3">
-        <v>-847900</v>
+        <v>41800</v>
       </c>
       <c r="G100" s="3">
-        <v>102700</v>
+        <v>-860700</v>
       </c>
       <c r="H100" s="3">
-        <v>-182700</v>
+        <v>104300</v>
       </c>
       <c r="I100" s="3">
-        <v>485600</v>
+        <v>-185400</v>
       </c>
       <c r="J100" s="3">
+        <v>492900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-247600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>17200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-111700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-320400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-371100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-442100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-584000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-102700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-261700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>363600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-431900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>305300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-522600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>409300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-408800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>466900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-341500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>246200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-372500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>2673000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-763500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>417200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-385800</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-17400</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1300</v>
       </c>
-      <c r="E101" s="3">
-        <v>8000</v>
-      </c>
       <c r="F101" s="3">
-        <v>-8300</v>
+        <v>8200</v>
       </c>
       <c r="G101" s="3">
-        <v>-93700</v>
+        <v>-8400</v>
       </c>
       <c r="H101" s="3">
-        <v>-74400</v>
+        <v>-95100</v>
       </c>
       <c r="I101" s="3">
-        <v>204800</v>
+        <v>-75600</v>
       </c>
       <c r="J101" s="3">
+        <v>207900</v>
+      </c>
+      <c r="K101" s="3">
         <v>33000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>21100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>4100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>10400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-8200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>19000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>10900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-17000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>10400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-20800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>12800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-24800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>62300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-40600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-66000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>69000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>13700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>8900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>13800</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-66000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-173900</v>
+        <v>176400</v>
       </c>
       <c r="E102" s="3">
-        <v>355200</v>
+        <v>-176500</v>
       </c>
       <c r="F102" s="3">
-        <v>-293200</v>
+        <v>360600</v>
       </c>
       <c r="G102" s="3">
-        <v>88400</v>
+        <v>-297600</v>
       </c>
       <c r="H102" s="3">
-        <v>-416500</v>
+        <v>89700</v>
       </c>
       <c r="I102" s="3">
-        <v>452700</v>
+        <v>-422700</v>
       </c>
       <c r="J102" s="3">
+        <v>459600</v>
+      </c>
+      <c r="K102" s="3">
         <v>294300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>275900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-53300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>175400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-127500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-160800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>63900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>563600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>188100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-280200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>412300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>206500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-179800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>11900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>35100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>97400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>278000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-125700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>416200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-166700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KMTUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KMTUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>KMTUY</t>
   </si>
@@ -656,422 +656,434 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6551300</v>
+        <v>6827400</v>
       </c>
       <c r="E8" s="3">
-        <v>6224000</v>
+        <v>6201300</v>
       </c>
       <c r="F8" s="3">
-        <v>6063000</v>
+        <v>5891600</v>
       </c>
       <c r="G8" s="3">
-        <v>6768600</v>
+        <v>5739100</v>
       </c>
       <c r="H8" s="3">
-        <v>6204100</v>
+        <v>6407100</v>
       </c>
       <c r="I8" s="3">
-        <v>5762200</v>
+        <v>5872800</v>
       </c>
       <c r="J8" s="3">
+        <v>5454400</v>
+      </c>
+      <c r="K8" s="3">
         <v>5148100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5230000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>4968900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4637000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4764800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4794300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4072500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3887100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3913000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5439500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5593100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5548200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5585500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>6790800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6613400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6242700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5872700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6285600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5847500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5403600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5073300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5111600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>3819400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3608800</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4481900</v>
+        <v>4802500</v>
       </c>
       <c r="E9" s="3">
-        <v>4219000</v>
+        <v>4242500</v>
       </c>
       <c r="F9" s="3">
-        <v>4119800</v>
+        <v>3993600</v>
       </c>
       <c r="G9" s="3">
-        <v>4804500</v>
+        <v>3899700</v>
       </c>
       <c r="H9" s="3">
-        <v>4341600</v>
+        <v>4547900</v>
       </c>
       <c r="I9" s="3">
-        <v>4057800</v>
+        <v>4109700</v>
       </c>
       <c r="J9" s="3">
+        <v>3841100</v>
+      </c>
+      <c r="K9" s="3">
         <v>3676000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3769800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3589200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3298400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3491800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3540700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2999800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2844100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2855200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3983000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4023200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3933000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3914600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4734300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4644500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4266600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4011000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4364100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4072000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3892100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3635600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3643900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>2714800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2572600</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2069300</v>
+        <v>2024900</v>
       </c>
       <c r="E10" s="3">
-        <v>2005100</v>
+        <v>1958800</v>
       </c>
       <c r="F10" s="3">
-        <v>1943200</v>
+        <v>1898000</v>
       </c>
       <c r="G10" s="3">
-        <v>1964100</v>
+        <v>1839400</v>
       </c>
       <c r="H10" s="3">
-        <v>1862500</v>
+        <v>1859200</v>
       </c>
       <c r="I10" s="3">
-        <v>1704400</v>
+        <v>1763000</v>
       </c>
       <c r="J10" s="3">
+        <v>1613400</v>
+      </c>
+      <c r="K10" s="3">
         <v>1472100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1460200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1379700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1338600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1272900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1253500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1072700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1043000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1057800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1456500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1569900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1615200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1670900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2056500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1968800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1976100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1861700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1921400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1775500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1511500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1437700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1467700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1104600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1036300</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1105,8 +1117,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1200,8 +1213,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1295,13 +1311,16 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>39000</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1309,11 +1328,11 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>37200</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="H14" s="3">
+        <v>35200</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1321,11 +1340,11 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>9100</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1333,11 +1352,11 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>17000</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1354,8 +1373,8 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1363,8 +1382,8 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
@@ -1381,17 +1400,20 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3">
         <v>15500</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1485,8 +1507,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1517,198 +1542,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5496800</v>
+        <v>5846400</v>
       </c>
       <c r="E17" s="3">
-        <v>5213300</v>
+        <v>5203200</v>
       </c>
       <c r="F17" s="3">
-        <v>5072100</v>
+        <v>4934900</v>
       </c>
       <c r="G17" s="3">
-        <v>5797500</v>
+        <v>4801100</v>
       </c>
       <c r="H17" s="3">
-        <v>5294500</v>
+        <v>5487800</v>
       </c>
       <c r="I17" s="3">
-        <v>4966400</v>
+        <v>5011700</v>
       </c>
       <c r="J17" s="3">
+        <v>4701100</v>
+      </c>
+      <c r="K17" s="3">
         <v>4517500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4610800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4367900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4099600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4310900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4370300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3726600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3626700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3683400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5061800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4993300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4930400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4900700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5810800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5711600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5274100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4999600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5531700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5170900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4865900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4606000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4516700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3304300</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1054400</v>
+        <v>981100</v>
       </c>
       <c r="E18" s="3">
-        <v>1010700</v>
+        <v>998100</v>
       </c>
       <c r="F18" s="3">
-        <v>990900</v>
+        <v>956700</v>
       </c>
       <c r="G18" s="3">
-        <v>971100</v>
+        <v>938000</v>
       </c>
       <c r="H18" s="3">
-        <v>909700</v>
+        <v>919300</v>
       </c>
       <c r="I18" s="3">
-        <v>795800</v>
+        <v>861100</v>
       </c>
       <c r="J18" s="3">
+        <v>753300</v>
+      </c>
+      <c r="K18" s="3">
         <v>630600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>619200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>601000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>537400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>453900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>423900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>345900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>260400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>229600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>377800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>599900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>617800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>684800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>979900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>901800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>968600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>873100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>753900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>676500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>537700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>467400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>594900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>380500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>304600</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1742,483 +1774,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>3100</v>
+        <v>41300</v>
       </c>
       <c r="E20" s="3">
-        <v>19800</v>
+        <v>2900</v>
       </c>
       <c r="F20" s="3">
-        <v>88300</v>
+        <v>18800</v>
       </c>
       <c r="G20" s="3">
-        <v>20400</v>
+        <v>83600</v>
       </c>
       <c r="H20" s="3">
-        <v>-80400</v>
+        <v>19300</v>
       </c>
       <c r="I20" s="3">
-        <v>23100</v>
+        <v>-76100</v>
       </c>
       <c r="J20" s="3">
+        <v>21900</v>
+      </c>
+      <c r="K20" s="3">
         <v>159000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>67100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>25400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>23800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>19600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>20000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>5800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>46200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-35100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>15000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-11000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>37200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-35000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>12000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>21000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-17900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>14300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>372500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-11900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>36500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1333800</v>
+        <v>1273700</v>
       </c>
       <c r="E21" s="3">
-        <v>1293100</v>
+        <v>1262600</v>
       </c>
       <c r="F21" s="3">
-        <v>1331900</v>
+        <v>1224000</v>
       </c>
       <c r="G21" s="3">
-        <v>1248400</v>
+        <v>1260800</v>
       </c>
       <c r="H21" s="3">
-        <v>1088800</v>
+        <v>1181700</v>
       </c>
       <c r="I21" s="3">
-        <v>1067600</v>
+        <v>1030600</v>
       </c>
       <c r="J21" s="3">
+        <v>1010600</v>
+      </c>
+      <c r="K21" s="3">
         <v>1033400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>933900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>841300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>802800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>725200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>691100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>597700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>517900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>547300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>645500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>911300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>916800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>973100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1337600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1176100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1281800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1193400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1052800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>992600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1205300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>763800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>821800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>643700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>539800</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>98800</v>
+        <v>94700</v>
       </c>
       <c r="E22" s="3">
-        <v>87900</v>
+        <v>93500</v>
       </c>
       <c r="F22" s="3">
-        <v>80600</v>
+        <v>83200</v>
       </c>
       <c r="G22" s="3">
-        <v>70700</v>
+        <v>76300</v>
       </c>
       <c r="H22" s="3">
-        <v>74100</v>
+        <v>66900</v>
       </c>
       <c r="I22" s="3">
-        <v>41900</v>
+        <v>70100</v>
       </c>
       <c r="J22" s="3">
+        <v>39700</v>
+      </c>
+      <c r="K22" s="3">
         <v>31500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>23100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>21800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>22700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>23200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>27800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>32800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>50200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>52700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>59300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>60900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>61000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>59900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>55600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>49300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>44700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>46900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>42200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>32300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>22400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>16300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>958800</v>
+        <v>927600</v>
       </c>
       <c r="E23" s="3">
-        <v>942600</v>
+        <v>907600</v>
       </c>
       <c r="F23" s="3">
-        <v>998700</v>
+        <v>892300</v>
       </c>
       <c r="G23" s="3">
-        <v>920900</v>
+        <v>945300</v>
       </c>
       <c r="H23" s="3">
-        <v>755200</v>
+        <v>871700</v>
       </c>
       <c r="I23" s="3">
-        <v>777000</v>
+        <v>714900</v>
       </c>
       <c r="J23" s="3">
+        <v>735500</v>
+      </c>
+      <c r="K23" s="3">
         <v>758100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>665700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>603200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>541100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>451700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>421300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>328600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>234000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>243100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>292400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>562200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>563400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>612900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>956100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>806800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>925000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>844800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>691300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>643900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>868000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>434800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>560600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>400600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>300600</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>266300</v>
+        <v>340900</v>
       </c>
       <c r="E24" s="3">
-        <v>242300</v>
+        <v>252100</v>
       </c>
       <c r="F24" s="3">
-        <v>260700</v>
+        <v>229400</v>
       </c>
       <c r="G24" s="3">
-        <v>258300</v>
+        <v>246800</v>
       </c>
       <c r="H24" s="3">
-        <v>258500</v>
+        <v>244500</v>
       </c>
       <c r="I24" s="3">
-        <v>197800</v>
+        <v>244700</v>
       </c>
       <c r="J24" s="3">
+        <v>187300</v>
+      </c>
+      <c r="K24" s="3">
         <v>198900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>204400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>158600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>149000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>132500</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>113200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>101500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>56700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>83700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>114500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>129800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>163500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>163300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>239900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>227500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>274200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>254700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>293100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>142000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>259900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>85900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>135000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>124400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>105900</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2312,198 +2360,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>692400</v>
+        <v>586700</v>
       </c>
       <c r="E26" s="3">
-        <v>700300</v>
+        <v>655400</v>
       </c>
       <c r="F26" s="3">
-        <v>737900</v>
+        <v>662900</v>
       </c>
       <c r="G26" s="3">
-        <v>662600</v>
+        <v>698500</v>
       </c>
       <c r="H26" s="3">
-        <v>496700</v>
+        <v>627200</v>
       </c>
       <c r="I26" s="3">
-        <v>579200</v>
+        <v>470100</v>
       </c>
       <c r="J26" s="3">
+        <v>548200</v>
+      </c>
+      <c r="K26" s="3">
         <v>559200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>461200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>444600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>392100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>319200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>308000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>227100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>177200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>159300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>177900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>432300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>399900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>449600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>716200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>579400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>650800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>590100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>398100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>501800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>608200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>348900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>425700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>276200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>194700</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>665400</v>
+        <v>568800</v>
       </c>
       <c r="E27" s="3">
-        <v>674800</v>
+        <v>629800</v>
       </c>
       <c r="F27" s="3">
-        <v>710600</v>
+        <v>638800</v>
       </c>
       <c r="G27" s="3">
-        <v>636800</v>
+        <v>672600</v>
       </c>
       <c r="H27" s="3">
-        <v>467400</v>
+        <v>602800</v>
       </c>
       <c r="I27" s="3">
-        <v>553400</v>
+        <v>442400</v>
       </c>
       <c r="J27" s="3">
+        <v>523900</v>
+      </c>
+      <c r="K27" s="3">
         <v>542300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>461000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>428400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>376700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>300600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>285500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>210200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>163900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>138600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>163700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>411800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>391400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>434900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>694700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>555200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>579800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>572400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>373800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>481900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>590900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>329000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>399600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>273300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2597,8 +2654,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2692,8 +2752,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2787,8 +2850,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2882,198 +2948,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-3100</v>
+        <v>-41300</v>
       </c>
       <c r="E32" s="3">
-        <v>-19800</v>
+        <v>-2900</v>
       </c>
       <c r="F32" s="3">
-        <v>-88300</v>
+        <v>-18800</v>
       </c>
       <c r="G32" s="3">
-        <v>-20400</v>
+        <v>-83600</v>
       </c>
       <c r="H32" s="3">
-        <v>80400</v>
+        <v>-19300</v>
       </c>
       <c r="I32" s="3">
-        <v>-23100</v>
+        <v>76100</v>
       </c>
       <c r="J32" s="3">
+        <v>-21900</v>
+      </c>
+      <c r="K32" s="3">
         <v>-159000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-67100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-25400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-23800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-19600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-20000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-46200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>35100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-15000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>11000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-37200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>35000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-12000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>17900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-14300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-372500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>11900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-36500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-12800</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>665400</v>
+        <v>568800</v>
       </c>
       <c r="E33" s="3">
-        <v>674800</v>
+        <v>629800</v>
       </c>
       <c r="F33" s="3">
-        <v>710600</v>
+        <v>638800</v>
       </c>
       <c r="G33" s="3">
-        <v>636800</v>
+        <v>672600</v>
       </c>
       <c r="H33" s="3">
-        <v>467400</v>
+        <v>602800</v>
       </c>
       <c r="I33" s="3">
-        <v>553400</v>
+        <v>442400</v>
       </c>
       <c r="J33" s="3">
+        <v>523900</v>
+      </c>
+      <c r="K33" s="3">
         <v>542300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>461000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>428400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>376700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>300600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>285500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>210200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>163900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>138600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>163700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>411800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>391400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>434900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>694700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>555200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>579800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>572400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>373800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>481900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>590900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>329000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>399600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>273300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3167,203 +3242,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>665400</v>
+        <v>568800</v>
       </c>
       <c r="E35" s="3">
-        <v>674800</v>
+        <v>629800</v>
       </c>
       <c r="F35" s="3">
-        <v>710600</v>
+        <v>638800</v>
       </c>
       <c r="G35" s="3">
-        <v>636800</v>
+        <v>672600</v>
       </c>
       <c r="H35" s="3">
-        <v>467400</v>
+        <v>602800</v>
       </c>
       <c r="I35" s="3">
-        <v>553400</v>
+        <v>442400</v>
       </c>
       <c r="J35" s="3">
+        <v>523900</v>
+      </c>
+      <c r="K35" s="3">
         <v>542300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>461000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>428400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>376700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>300600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>285500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>210200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>163900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>138600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>163700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>411800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>391400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>434900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>694700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>555200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>579800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>572400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>373800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>481900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>590900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>329000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>399600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>273300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3397,8 +3481,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3432,103 +3517,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2314900</v>
+        <v>2572300</v>
       </c>
       <c r="E41" s="3">
-        <v>2138500</v>
+        <v>2191200</v>
       </c>
       <c r="F41" s="3">
-        <v>2315000</v>
+        <v>2024300</v>
       </c>
       <c r="G41" s="3">
-        <v>1954400</v>
+        <v>2191300</v>
       </c>
       <c r="H41" s="3">
-        <v>2252100</v>
+        <v>1850000</v>
       </c>
       <c r="I41" s="3">
-        <v>2162400</v>
+        <v>2131800</v>
       </c>
       <c r="J41" s="3">
+        <v>2046900</v>
+      </c>
+      <c r="K41" s="3">
         <v>2585100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2094000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1862000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1975600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1732900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1723800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1601600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1837300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2194200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2199600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1689900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1514000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1792800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1449300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1421600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1196300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1343400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1327600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1516900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1482200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1381200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1083800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1209600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>789900</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3544,24 +3633,24 @@
       <c r="G42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H42" s="3">
-        <v>13600</v>
+      <c r="H42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I42" s="3">
-        <v>5200</v>
+        <v>12800</v>
       </c>
       <c r="J42" s="3">
+        <v>4900</v>
+      </c>
+      <c r="K42" s="3">
         <v>7300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>8700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>15600</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -3622,673 +3711,697 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>7594700</v>
+        <v>8061400</v>
       </c>
       <c r="E43" s="3">
-        <v>7535300</v>
+        <v>7189000</v>
       </c>
       <c r="F43" s="3">
-        <v>7681300</v>
+        <v>7132800</v>
       </c>
       <c r="G43" s="3">
-        <v>7494300</v>
+        <v>7271000</v>
       </c>
       <c r="H43" s="3">
-        <v>6536100</v>
+        <v>7094000</v>
       </c>
       <c r="I43" s="3">
-        <v>6983100</v>
+        <v>6187000</v>
       </c>
       <c r="J43" s="3">
+        <v>6610100</v>
+      </c>
+      <c r="K43" s="3">
         <v>6705900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6338400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>5855300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5745200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5791100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5818700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5049300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5218600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5668600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6558100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7002300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6799600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7109800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>8093400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7464600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7593000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7131300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7166100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6920900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6481500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>5949400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5492900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5117000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>4460600</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>9838200</v>
+        <v>9178900</v>
       </c>
       <c r="E44" s="3">
-        <v>10052800</v>
+        <v>9312700</v>
       </c>
       <c r="F44" s="3">
-        <v>9400000</v>
+        <v>9515900</v>
       </c>
       <c r="G44" s="3">
-        <v>8271400</v>
+        <v>8897900</v>
       </c>
       <c r="H44" s="3">
-        <v>8384800</v>
+        <v>7829600</v>
       </c>
       <c r="I44" s="3">
-        <v>8593700</v>
+        <v>7936900</v>
       </c>
       <c r="J44" s="3">
+        <v>8134700</v>
+      </c>
+      <c r="K44" s="3">
         <v>7917100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>6560400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6192300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6123000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6020100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5628400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6025000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6535000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7393100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7094800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>8199300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8217800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8015200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>8048900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>7793600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>7851600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>7246200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>6601800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6847600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6441600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>6211000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>4735700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5252300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4645600</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1453300</v>
+        <v>1332000</v>
       </c>
       <c r="E45" s="3">
-        <v>1673600</v>
+        <v>1375700</v>
       </c>
       <c r="F45" s="3">
-        <v>1671800</v>
+        <v>1584300</v>
       </c>
       <c r="G45" s="3">
-        <v>1398400</v>
+        <v>1582500</v>
       </c>
       <c r="H45" s="3">
-        <v>1336500</v>
+        <v>1323700</v>
       </c>
       <c r="I45" s="3">
-        <v>1348600</v>
+        <v>1265100</v>
       </c>
       <c r="J45" s="3">
+        <v>1276600</v>
+      </c>
+      <c r="K45" s="3">
         <v>1262900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1075800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1124300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>991000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1023700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>933200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>962600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1023800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1269500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1298700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1368900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1225300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1322900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1330200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1291000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1205900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1188900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1154700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1105700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1052800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1084600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1278800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1242800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1155000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>21201100</v>
+        <v>21144500</v>
       </c>
       <c r="E46" s="3">
-        <v>21400300</v>
+        <v>20068700</v>
       </c>
       <c r="F46" s="3">
-        <v>21068000</v>
+        <v>20257200</v>
       </c>
       <c r="G46" s="3">
-        <v>19118500</v>
+        <v>19942700</v>
       </c>
       <c r="H46" s="3">
-        <v>18523000</v>
+        <v>18097300</v>
       </c>
       <c r="I46" s="3">
-        <v>19092800</v>
+        <v>17533600</v>
       </c>
       <c r="J46" s="3">
+        <v>18073000</v>
+      </c>
+      <c r="K46" s="3">
         <v>18478300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>16077300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>15049600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>14834700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14567700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14104100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>13638400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14614700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>16525500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>17151200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>18260400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17756700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18240800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>18921700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17970800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17846800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16909800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16250200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16391200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>15458100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>14626200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>12591200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>12821700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>11051100</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4749300</v>
+        <v>4886100</v>
       </c>
       <c r="E47" s="3">
-        <v>4896800</v>
+        <v>4495600</v>
       </c>
       <c r="F47" s="3">
-        <v>4758200</v>
+        <v>4635200</v>
       </c>
       <c r="G47" s="3">
-        <v>4263500</v>
+        <v>4504000</v>
       </c>
       <c r="H47" s="3">
-        <v>4339700</v>
+        <v>4035800</v>
       </c>
       <c r="I47" s="3">
-        <v>4617000</v>
+        <v>4107900</v>
       </c>
       <c r="J47" s="3">
+        <v>4370400</v>
+      </c>
+      <c r="K47" s="3">
         <v>4307100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3692900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3632900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3650400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3831400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3505200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3513400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3679600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4108100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4109500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4302400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4281700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4254400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4431700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3945800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4110500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3870100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3656300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3775100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3603400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3962700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3654400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3553700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3114700</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6399900</v>
+        <v>6235100</v>
       </c>
       <c r="E48" s="3">
-        <v>6397600</v>
+        <v>6058100</v>
       </c>
       <c r="F48" s="3">
-        <v>6281700</v>
+        <v>6055900</v>
       </c>
       <c r="G48" s="3">
-        <v>6049100</v>
+        <v>5946200</v>
       </c>
       <c r="H48" s="3">
-        <v>5997600</v>
+        <v>5726000</v>
       </c>
       <c r="I48" s="3">
-        <v>6277700</v>
+        <v>5677200</v>
       </c>
       <c r="J48" s="3">
+        <v>5942400</v>
+      </c>
+      <c r="K48" s="3">
         <v>6174500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5851600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5836700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6043400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6152900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5993200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6007500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6325100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6898700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>7146100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7436500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7400100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7454200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7461400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7167800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7111300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>6849300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6694400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6941200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6903500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6874400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6023000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6087900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>5725600</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2812400</v>
+        <v>2735700</v>
       </c>
       <c r="E49" s="3">
-        <v>2685300</v>
+        <v>2662200</v>
       </c>
       <c r="F49" s="3">
-        <v>2663700</v>
+        <v>2541800</v>
       </c>
       <c r="G49" s="3">
-        <v>2523100</v>
+        <v>2521400</v>
       </c>
       <c r="H49" s="3">
-        <v>2509000</v>
+        <v>2388400</v>
       </c>
       <c r="I49" s="3">
-        <v>2741200</v>
+        <v>2375000</v>
       </c>
       <c r="J49" s="3">
+        <v>2594800</v>
+      </c>
+      <c r="K49" s="3">
         <v>2585000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2367900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2330800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2406100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2479900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2408200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2370200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2505800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2768200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2815500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3096100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3079300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2972100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3155200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3161900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3289100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3137100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2975000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3245200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3273300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3281300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>897200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>891700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>852900</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4382,8 +4495,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4477,103 +4593,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1027300</v>
+        <v>960400</v>
       </c>
       <c r="E52" s="3">
-        <v>1043600</v>
+        <v>972400</v>
       </c>
       <c r="F52" s="3">
-        <v>937400</v>
+        <v>987900</v>
       </c>
       <c r="G52" s="3">
-        <v>908900</v>
+        <v>887400</v>
       </c>
       <c r="H52" s="3">
-        <v>872400</v>
+        <v>860400</v>
       </c>
       <c r="I52" s="3">
-        <v>988400</v>
+        <v>825800</v>
       </c>
       <c r="J52" s="3">
+        <v>935600</v>
+      </c>
+      <c r="K52" s="3">
         <v>908800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>877800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>818200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>849300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>827500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>823800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>807200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>875700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>926900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>966700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>877800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>911400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>893200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>993200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>881500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>914100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>875400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>911800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>925500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>867000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>685400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>397300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>395700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>472700</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4667,103 +4789,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>36189900</v>
+        <v>35961900</v>
       </c>
       <c r="E54" s="3">
-        <v>36423500</v>
+        <v>34256900</v>
       </c>
       <c r="F54" s="3">
-        <v>35709100</v>
+        <v>34478100</v>
       </c>
       <c r="G54" s="3">
-        <v>32863200</v>
+        <v>33801800</v>
       </c>
       <c r="H54" s="3">
-        <v>32241800</v>
+        <v>31107900</v>
       </c>
       <c r="I54" s="3">
-        <v>33717200</v>
+        <v>30519700</v>
       </c>
       <c r="J54" s="3">
+        <v>31916200</v>
+      </c>
+      <c r="K54" s="3">
         <v>32453700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>28867500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>27668100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27783800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27859400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>26834500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26336600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>28001000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>31227300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>32189000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>33973200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33429200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>33814600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>34963300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33127800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33271700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>31641700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>30487700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>31278300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>30105200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>29429900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>23563000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>23750700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>21217100</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4797,8 +4925,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4832,578 +4961,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2169500</v>
+        <v>2043600</v>
       </c>
       <c r="E57" s="3">
-        <v>2350100</v>
+        <v>2053600</v>
       </c>
       <c r="F57" s="3">
-        <v>2476000</v>
+        <v>2224500</v>
       </c>
       <c r="G57" s="3">
-        <v>2442300</v>
+        <v>2343800</v>
       </c>
       <c r="H57" s="3">
-        <v>2278700</v>
+        <v>2311900</v>
       </c>
       <c r="I57" s="3">
-        <v>2400200</v>
+        <v>2157000</v>
       </c>
       <c r="J57" s="3">
+        <v>2272000</v>
+      </c>
+      <c r="K57" s="3">
         <v>2341700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2250800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1971700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1939100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1908900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1831500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1597300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1511700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1742400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1939600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>2091700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2278800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2338800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2565400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2413100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2557500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2485200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2744100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2742000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2594600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2526300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2129800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1891800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1680000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4242400</v>
+        <v>3706600</v>
       </c>
       <c r="E58" s="3">
-        <v>3353300</v>
+        <v>4015800</v>
       </c>
       <c r="F58" s="3">
-        <v>4108400</v>
+        <v>3174200</v>
       </c>
       <c r="G58" s="3">
-        <v>3286200</v>
+        <v>3889000</v>
       </c>
       <c r="H58" s="3">
-        <v>4148000</v>
+        <v>3110700</v>
       </c>
       <c r="I58" s="3">
-        <v>4900500</v>
+        <v>3926400</v>
       </c>
       <c r="J58" s="3">
+        <v>4638700</v>
+      </c>
+      <c r="K58" s="3">
         <v>4641200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3442000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3599600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3247400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2968400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2619500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2928500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3409100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5190700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5308400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5845400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5004000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4708300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4403400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4835900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>3995900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4127800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2982300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3226400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2743000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4866100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1932300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2705700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1856900</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3846700</v>
+        <v>3986900</v>
       </c>
       <c r="E59" s="3">
-        <v>4010900</v>
+        <v>3641200</v>
       </c>
       <c r="F59" s="3">
-        <v>3915300</v>
+        <v>3796600</v>
       </c>
       <c r="G59" s="3">
-        <v>3516400</v>
+        <v>3706200</v>
       </c>
       <c r="H59" s="3">
-        <v>3302500</v>
+        <v>3328600</v>
       </c>
       <c r="I59" s="3">
-        <v>3351700</v>
+        <v>3126100</v>
       </c>
       <c r="J59" s="3">
+        <v>3172600</v>
+      </c>
+      <c r="K59" s="3">
         <v>3188000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3098700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2715800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2697500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2611000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2588500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2524800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2635500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2809300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2959500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>3169700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3262900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3290300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3430500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3011500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3336600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3020600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3220100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3131200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>2985200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2675700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2148500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1977100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1932900</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>10258500</v>
+        <v>9737100</v>
       </c>
       <c r="E60" s="3">
-        <v>9714200</v>
+        <v>9710600</v>
       </c>
       <c r="F60" s="3">
-        <v>10499800</v>
+        <v>9195400</v>
       </c>
       <c r="G60" s="3">
-        <v>9245000</v>
+        <v>9939000</v>
       </c>
       <c r="H60" s="3">
-        <v>9729200</v>
+        <v>8751200</v>
       </c>
       <c r="I60" s="3">
-        <v>10652300</v>
+        <v>9209500</v>
       </c>
       <c r="J60" s="3">
+        <v>10083400</v>
+      </c>
+      <c r="K60" s="3">
         <v>10170900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8791500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8287000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>7884100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7488300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7039400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7050600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7556300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>9742300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>10207500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>11106800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10545700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10337400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10399400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10260500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>9890100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9633600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>8946500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9099600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8322800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>10068000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>6210600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6574700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>5469800</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3895500</v>
+        <v>3945300</v>
       </c>
       <c r="E61" s="3">
-        <v>4414800</v>
+        <v>3687500</v>
       </c>
       <c r="F61" s="3">
-        <v>4020900</v>
+        <v>4179000</v>
       </c>
       <c r="G61" s="3">
-        <v>3816100</v>
+        <v>3806100</v>
       </c>
       <c r="H61" s="3">
-        <v>3692800</v>
+        <v>3612300</v>
       </c>
       <c r="I61" s="3">
-        <v>2989100</v>
+        <v>3495500</v>
       </c>
       <c r="J61" s="3">
+        <v>2829400</v>
+      </c>
+      <c r="K61" s="3">
         <v>3203300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2848600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2748000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2986100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3685700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3832300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3788600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4116400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3747600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3610700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3704600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3739100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4491900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4540600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4285500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4526300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4365800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4345500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4771500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4645600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2829700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1692900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1742600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1577700</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1884900</v>
+        <v>1873300</v>
       </c>
       <c r="E62" s="3">
-        <v>1961200</v>
+        <v>1784200</v>
       </c>
       <c r="F62" s="3">
-        <v>1866000</v>
+        <v>1856400</v>
       </c>
       <c r="G62" s="3">
-        <v>1752700</v>
+        <v>1766300</v>
       </c>
       <c r="H62" s="3">
-        <v>1711800</v>
+        <v>1659100</v>
       </c>
       <c r="I62" s="3">
-        <v>1795000</v>
+        <v>1620300</v>
       </c>
       <c r="J62" s="3">
+        <v>1699100</v>
+      </c>
+      <c r="K62" s="3">
         <v>1735200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1581700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1611800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1672700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1756800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1697600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1628100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1786600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1929800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>2017500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1936900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1955600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1946800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1736800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1588900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1545500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1485000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1433600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1437400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1448700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1400700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1037100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1041600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>965200</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5497,8 +5645,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5592,8 +5743,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5687,103 +5841,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>17073100</v>
+        <v>16607700</v>
       </c>
       <c r="E66" s="3">
-        <v>17111700</v>
+        <v>16161200</v>
       </c>
       <c r="F66" s="3">
-        <v>17383700</v>
+        <v>16197800</v>
       </c>
       <c r="G66" s="3">
-        <v>15746000</v>
+        <v>16455200</v>
       </c>
       <c r="H66" s="3">
-        <v>16014200</v>
+        <v>14905000</v>
       </c>
       <c r="I66" s="3">
-        <v>16347200</v>
+        <v>15158900</v>
       </c>
       <c r="J66" s="3">
+        <v>15474000</v>
+      </c>
+      <c r="K66" s="3">
         <v>15972600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>14043700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>13489900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13380200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13660300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13276300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13146300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>14153500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>16184500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16581100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>17541800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16997900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>17543800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>17515500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16912800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16751000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16218100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>15440300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16046200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15109600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>14968700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>9577900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9984500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>8556800</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5817,8 +5977,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5912,8 +6073,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6007,8 +6171,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6102,8 +6269,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6197,103 +6367,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>15682900</v>
+        <v>15414100</v>
       </c>
       <c r="E72" s="3">
-        <v>15476800</v>
+        <v>14845200</v>
       </c>
       <c r="F72" s="3">
-        <v>14802000</v>
+        <v>14650100</v>
       </c>
       <c r="G72" s="3">
-        <v>14580600</v>
+        <v>14011400</v>
       </c>
       <c r="H72" s="3">
-        <v>13943800</v>
+        <v>13801800</v>
       </c>
       <c r="I72" s="3">
-        <v>13884500</v>
+        <v>13199000</v>
       </c>
       <c r="J72" s="3">
+        <v>13142900</v>
+      </c>
+      <c r="K72" s="3">
         <v>13331000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>12950700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12922300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>13385000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13260900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12749900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12886400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>13604200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14720100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15384800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15739500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15939800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15497700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>16338300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15366800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15023600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>14132800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>13901600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13527900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13353100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>12762200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>12442100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12042600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>12011900</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6387,8 +6563,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6482,8 +6661,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6577,103 +6759,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>19116800</v>
+        <v>19354200</v>
       </c>
       <c r="E76" s="3">
-        <v>19311800</v>
+        <v>18095700</v>
       </c>
       <c r="F76" s="3">
-        <v>18325400</v>
+        <v>18280300</v>
       </c>
       <c r="G76" s="3">
-        <v>17117200</v>
+        <v>17346600</v>
       </c>
       <c r="H76" s="3">
-        <v>16227600</v>
+        <v>16202900</v>
       </c>
       <c r="I76" s="3">
-        <v>17370000</v>
+        <v>15360800</v>
       </c>
       <c r="J76" s="3">
+        <v>16442200</v>
+      </c>
+      <c r="K76" s="3">
         <v>16481100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14823900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14178100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14403600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14199100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>13558200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13190300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13847500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15042800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15607800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16431500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16431400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16270800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>17447700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16215000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16520700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>15423500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15047400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15232100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>14995700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14461200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>13985100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13766200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>12660300</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6767,203 +6955,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>665400</v>
+        <v>568800</v>
       </c>
       <c r="E81" s="3">
-        <v>674800</v>
+        <v>629800</v>
       </c>
       <c r="F81" s="3">
-        <v>710600</v>
+        <v>638800</v>
       </c>
       <c r="G81" s="3">
-        <v>636800</v>
+        <v>672600</v>
       </c>
       <c r="H81" s="3">
-        <v>467400</v>
+        <v>602800</v>
       </c>
       <c r="I81" s="3">
-        <v>553400</v>
+        <v>442400</v>
       </c>
       <c r="J81" s="3">
+        <v>523900</v>
+      </c>
+      <c r="K81" s="3">
         <v>542300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>461000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>428400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>376700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>300600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>285500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>210200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>163900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>138600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>163700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>411800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>391400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>434900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>694700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>555200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>579800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>572400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>373800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>481900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>590900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>329000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>399600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>273300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6997,103 +7194,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>276300</v>
+        <v>251400</v>
       </c>
       <c r="E83" s="3">
-        <v>262600</v>
+        <v>261500</v>
       </c>
       <c r="F83" s="3">
-        <v>252700</v>
+        <v>248600</v>
       </c>
       <c r="G83" s="3">
-        <v>256900</v>
+        <v>239200</v>
       </c>
       <c r="H83" s="3">
-        <v>259500</v>
+        <v>243100</v>
       </c>
       <c r="I83" s="3">
-        <v>248700</v>
+        <v>245600</v>
       </c>
       <c r="J83" s="3">
+        <v>235400</v>
+      </c>
+      <c r="K83" s="3">
         <v>243800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>247600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>215000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>241600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>251700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>247200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>245900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>256200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>271400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>302800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>296400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>294100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>299300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>320500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>309400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>301200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>299200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>316900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>301900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>295000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>296800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>238900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>226700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>222400</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7187,8 +7388,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7282,8 +7486,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7377,8 +7584,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7472,8 +7682,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7567,103 +7780,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>614500</v>
+        <v>997200</v>
       </c>
       <c r="E89" s="3">
-        <v>686700</v>
+        <v>581700</v>
       </c>
       <c r="F89" s="3">
-        <v>575800</v>
+        <v>650000</v>
       </c>
       <c r="G89" s="3">
-        <v>831700</v>
+        <v>545000</v>
       </c>
       <c r="H89" s="3">
-        <v>387800</v>
+        <v>787300</v>
       </c>
       <c r="I89" s="3">
-        <v>187900</v>
+        <v>367100</v>
       </c>
       <c r="J89" s="3">
+        <v>177900</v>
+      </c>
+      <c r="K89" s="3">
         <v>-15800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>770900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>188500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>669300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>474800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>813600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>636600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>759600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>469400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1208900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>202300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>715400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>530400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>982200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>259100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>677800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>603600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>3900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>357400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>376500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>971600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>448000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>444400</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7697,103 +7916,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-50938000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-63292000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-48195000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-40522000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-48621000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-48655000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-49879000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-36378000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-39135000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-41538000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-44307000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-279100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-314200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-380900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-374000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-317900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-397700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-434800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-439600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-403000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-453500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-552400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-411600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-382200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-288700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-389600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-331300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-390900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-378000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-298900</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7887,8 +8110,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7982,103 +8208,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-534000</v>
+        <v>-279400</v>
       </c>
       <c r="E94" s="3">
-        <v>-283500</v>
+        <v>-505400</v>
       </c>
       <c r="F94" s="3">
-        <v>-265200</v>
+        <v>-268300</v>
       </c>
       <c r="G94" s="3">
-        <v>-260200</v>
+        <v>-251100</v>
       </c>
       <c r="H94" s="3">
-        <v>-307200</v>
+        <v>-246300</v>
       </c>
       <c r="I94" s="3">
-        <v>-349700</v>
+        <v>-290800</v>
       </c>
       <c r="J94" s="3">
+        <v>-331000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-225400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-262000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-239100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-285800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-218000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-258800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-341100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-347300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-302300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-366600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-388200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-542900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-436300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-432300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-524300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-408300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-388400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-520100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-228800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>103500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2769300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-347600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-233600</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8112,103 +8344,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-459300</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>-434700</v>
       </c>
       <c r="F96" s="3">
-        <v>-478200</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>-452700</v>
       </c>
       <c r="H96" s="3">
-        <v>-408100</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>-386300</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-357000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-259900</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-257100</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-124700</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-314400</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-473400</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-510400</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-454600</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-411800</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-307100</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-247400</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-242700</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8302,8 +8538,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8397,8 +8636,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8492,289 +8734,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>113300</v>
+        <v>-377900</v>
       </c>
       <c r="E100" s="3">
-        <v>-578400</v>
+        <v>107200</v>
       </c>
       <c r="F100" s="3">
-        <v>41800</v>
+        <v>-547500</v>
       </c>
       <c r="G100" s="3">
-        <v>-860700</v>
+        <v>39600</v>
       </c>
       <c r="H100" s="3">
-        <v>104300</v>
+        <v>-814700</v>
       </c>
       <c r="I100" s="3">
-        <v>-185400</v>
+        <v>98700</v>
       </c>
       <c r="J100" s="3">
+        <v>-175500</v>
+      </c>
+      <c r="K100" s="3">
         <v>492900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-247600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>17200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-111700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-320400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-371100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-442100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-584000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-102700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-261700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>363600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-431900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>305300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-522600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>409300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-408800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>466900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-341500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>246200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-372500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>2673000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-763500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>417200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-385800</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-17400</v>
+        <v>41100</v>
       </c>
       <c r="E101" s="3">
+        <v>-16500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-1300</v>
       </c>
-      <c r="F101" s="3">
-        <v>8200</v>
-      </c>
       <c r="G101" s="3">
-        <v>-8400</v>
+        <v>7700</v>
       </c>
       <c r="H101" s="3">
-        <v>-95100</v>
+        <v>-8000</v>
       </c>
       <c r="I101" s="3">
-        <v>-75600</v>
+        <v>-90000</v>
       </c>
       <c r="J101" s="3">
+        <v>-71500</v>
+      </c>
+      <c r="K101" s="3">
         <v>207900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>33000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>21100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>4100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>10400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-8200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>19000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>10900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-17000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>10400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-20800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>12800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-24800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>62300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-40600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-66000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>69000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>13700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>8900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>13800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-66000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>176400</v>
+        <v>381000</v>
       </c>
       <c r="E102" s="3">
-        <v>-176500</v>
+        <v>167000</v>
       </c>
       <c r="F102" s="3">
-        <v>360600</v>
+        <v>-167100</v>
       </c>
       <c r="G102" s="3">
-        <v>-297600</v>
+        <v>341300</v>
       </c>
       <c r="H102" s="3">
-        <v>89700</v>
+        <v>-281700</v>
       </c>
       <c r="I102" s="3">
-        <v>-422700</v>
+        <v>84900</v>
       </c>
       <c r="J102" s="3">
+        <v>-400100</v>
+      </c>
+      <c r="K102" s="3">
         <v>459600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>294300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-12300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>275900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-53300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>175400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-127500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-160800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>63900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>563600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>188100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-280200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>412300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>2500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>206500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-179800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>11900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>35100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>97400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>278000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-125700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>416200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-166700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KMTUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KMTUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>KMTUY</t>
   </si>
@@ -656,434 +656,446 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>6827400</v>
+        <v>6814800</v>
       </c>
       <c r="E8" s="3">
-        <v>6201300</v>
+        <v>7597900</v>
       </c>
       <c r="F8" s="3">
-        <v>5891600</v>
+        <v>6901200</v>
       </c>
       <c r="G8" s="3">
-        <v>5739100</v>
+        <v>6556400</v>
       </c>
       <c r="H8" s="3">
-        <v>6407100</v>
+        <v>6386800</v>
       </c>
       <c r="I8" s="3">
-        <v>5872800</v>
+        <v>7130100</v>
       </c>
       <c r="J8" s="3">
+        <v>6535500</v>
+      </c>
+      <c r="K8" s="3">
         <v>5454400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5148100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5230000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4968900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4637000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4764800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4794300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4072500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3887100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3913000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5439500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5593100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5548200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5585500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>6790800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6613400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6242700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5872700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6285600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5847500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5403600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5073300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5111600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>3819400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3608800</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>4802500</v>
+        <v>4574400</v>
       </c>
       <c r="E9" s="3">
-        <v>4242500</v>
+        <v>5344500</v>
       </c>
       <c r="F9" s="3">
-        <v>3993600</v>
+        <v>4721300</v>
       </c>
       <c r="G9" s="3">
-        <v>3899700</v>
+        <v>4444300</v>
       </c>
       <c r="H9" s="3">
-        <v>4547900</v>
+        <v>4339800</v>
       </c>
       <c r="I9" s="3">
-        <v>4109700</v>
+        <v>5061100</v>
       </c>
       <c r="J9" s="3">
+        <v>4573500</v>
+      </c>
+      <c r="K9" s="3">
         <v>3841100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3676000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3769800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3589200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3298400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3491800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3540700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2999800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2844100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2855200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3983000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4023200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3933000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3914600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4734300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4644500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4266600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4011000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4364100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4072000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3892100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3635600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3643900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>2714800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2572600</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>2024900</v>
+        <v>2240400</v>
       </c>
       <c r="E10" s="3">
-        <v>1958800</v>
+        <v>2253500</v>
       </c>
       <c r="F10" s="3">
-        <v>1898000</v>
+        <v>2179900</v>
       </c>
       <c r="G10" s="3">
-        <v>1839400</v>
+        <v>2112200</v>
       </c>
       <c r="H10" s="3">
-        <v>1859200</v>
+        <v>2047000</v>
       </c>
       <c r="I10" s="3">
-        <v>1763000</v>
+        <v>2069000</v>
       </c>
       <c r="J10" s="3">
+        <v>1962000</v>
+      </c>
+      <c r="K10" s="3">
         <v>1613400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1472100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1460200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1379700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1338600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1272900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1253500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1072700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1043000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1057800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1456500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1569900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1615200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1670900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2056500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1968800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1976100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1861700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1921400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1775500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1511500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1437700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1467700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1104600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1036300</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1118,8 +1130,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1216,8 +1229,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1314,16 +1330,19 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>39000</v>
-      </c>
-      <c r="E14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="E14" s="3">
+        <v>43400</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1331,11 +1350,11 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
-        <v>35200</v>
-      </c>
-      <c r="I14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="I14" s="3">
+        <v>39200</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1343,11 +1362,11 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>9100</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>8</v>
@@ -1355,11 +1374,11 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>17000</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1376,8 +1395,8 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1385,8 +1404,8 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1403,17 +1422,20 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3">
         <v>15500</v>
-      </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1510,8 +1532,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1543,204 +1568,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>5846400</v>
+        <v>5700200</v>
       </c>
       <c r="E17" s="3">
-        <v>5203200</v>
+        <v>6506100</v>
       </c>
       <c r="F17" s="3">
-        <v>4934900</v>
+        <v>5790400</v>
       </c>
       <c r="G17" s="3">
-        <v>4801100</v>
+        <v>5491800</v>
       </c>
       <c r="H17" s="3">
-        <v>5487800</v>
+        <v>5343000</v>
       </c>
       <c r="I17" s="3">
-        <v>5011700</v>
+        <v>6107100</v>
       </c>
       <c r="J17" s="3">
+        <v>5577300</v>
+      </c>
+      <c r="K17" s="3">
         <v>4701100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4517500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4610800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4367900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4099600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4310900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4370300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3726600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3626700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3683400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5061800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4993300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4930400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4900700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5810800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5711600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5274100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4999600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5531700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5170900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4865900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4606000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4516700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3304300</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>981100</v>
+        <v>1114700</v>
       </c>
       <c r="E18" s="3">
-        <v>998100</v>
+        <v>1091800</v>
       </c>
       <c r="F18" s="3">
-        <v>956700</v>
+        <v>1110800</v>
       </c>
       <c r="G18" s="3">
-        <v>938000</v>
+        <v>1064700</v>
       </c>
       <c r="H18" s="3">
-        <v>919300</v>
+        <v>1043800</v>
       </c>
       <c r="I18" s="3">
-        <v>861100</v>
+        <v>1023000</v>
       </c>
       <c r="J18" s="3">
+        <v>958300</v>
+      </c>
+      <c r="K18" s="3">
         <v>753300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>630600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>619200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>601000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>537400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>453900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>423900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>345900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>260400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>229600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>377800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>599900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>617800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>684800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>979900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>901800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>968600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>873100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>753900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>676500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>537700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>467400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>594900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>380500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>304600</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1775,498 +1807,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>41300</v>
+        <v>63600</v>
       </c>
       <c r="E20" s="3">
-        <v>2900</v>
+        <v>45900</v>
       </c>
       <c r="F20" s="3">
-        <v>18800</v>
+        <v>3300</v>
       </c>
       <c r="G20" s="3">
-        <v>83600</v>
+        <v>20900</v>
       </c>
       <c r="H20" s="3">
-        <v>19300</v>
+        <v>93100</v>
       </c>
       <c r="I20" s="3">
-        <v>-76100</v>
+        <v>21500</v>
       </c>
       <c r="J20" s="3">
+        <v>-84700</v>
+      </c>
+      <c r="K20" s="3">
         <v>21900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>159000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>67100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>25400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>23800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>19600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>20000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>5800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>1400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>46200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-35100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>15000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-11000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>37200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-35000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>12000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>21000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>14300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>372500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-11900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>36500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1273700</v>
+        <v>1468500</v>
       </c>
       <c r="E21" s="3">
-        <v>1262600</v>
+        <v>1417400</v>
       </c>
       <c r="F21" s="3">
-        <v>1224000</v>
+        <v>1405100</v>
       </c>
       <c r="G21" s="3">
-        <v>1260800</v>
+        <v>1362200</v>
       </c>
       <c r="H21" s="3">
-        <v>1181700</v>
+        <v>1403100</v>
       </c>
       <c r="I21" s="3">
-        <v>1030600</v>
+        <v>1315100</v>
       </c>
       <c r="J21" s="3">
+        <v>1146900</v>
+      </c>
+      <c r="K21" s="3">
         <v>1010600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1033400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>933900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>841300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>802800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>725200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>691100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>597700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>517900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>547300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>645500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>911300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>916800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>973100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1337600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1176100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1281800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1193400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1052800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>992600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1205300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>763800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>821800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>643700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>539800</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>94700</v>
+        <v>109400</v>
       </c>
       <c r="E22" s="3">
-        <v>93500</v>
+        <v>105400</v>
       </c>
       <c r="F22" s="3">
-        <v>83200</v>
+        <v>104100</v>
       </c>
       <c r="G22" s="3">
-        <v>76300</v>
+        <v>92600</v>
       </c>
       <c r="H22" s="3">
-        <v>66900</v>
+        <v>84900</v>
       </c>
       <c r="I22" s="3">
-        <v>70100</v>
+        <v>74500</v>
       </c>
       <c r="J22" s="3">
+        <v>78000</v>
+      </c>
+      <c r="K22" s="3">
         <v>39700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>31500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>23100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>21800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>22700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>23200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>27800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>32800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>50200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>52700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>59300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>60900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>61000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>59900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>55600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>49300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>44700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>46900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>42200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>32300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>22400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>16300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>927600</v>
+        <v>1068900</v>
       </c>
       <c r="E23" s="3">
-        <v>907600</v>
+        <v>1032300</v>
       </c>
       <c r="F23" s="3">
-        <v>892300</v>
+        <v>1010000</v>
       </c>
       <c r="G23" s="3">
-        <v>945300</v>
+        <v>992900</v>
       </c>
       <c r="H23" s="3">
-        <v>871700</v>
+        <v>1052000</v>
       </c>
       <c r="I23" s="3">
-        <v>714900</v>
+        <v>970100</v>
       </c>
       <c r="J23" s="3">
+        <v>795500</v>
+      </c>
+      <c r="K23" s="3">
         <v>735500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>758100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>665700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>603200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>541100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>451700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>421300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>328600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>234000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>243100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>292400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>562200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>563400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>612900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>956100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>806800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>925000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>844800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>691300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>643900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>868000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>434800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>560600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>400600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>300600</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>340900</v>
+        <v>266200</v>
       </c>
       <c r="E24" s="3">
-        <v>252100</v>
+        <v>379300</v>
       </c>
       <c r="F24" s="3">
-        <v>229400</v>
+        <v>280600</v>
       </c>
       <c r="G24" s="3">
-        <v>246800</v>
+        <v>255300</v>
       </c>
       <c r="H24" s="3">
-        <v>244500</v>
+        <v>274600</v>
       </c>
       <c r="I24" s="3">
-        <v>244700</v>
+        <v>272100</v>
       </c>
       <c r="J24" s="3">
+        <v>272300</v>
+      </c>
+      <c r="K24" s="3">
         <v>187300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>198900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>204400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>158600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>149000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>132500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>113200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>101500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>56700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>83700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>114500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>129800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>163500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>163300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>239900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>227500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>274200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>254700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>293100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>142000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>259900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>85900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>135000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>124400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>105900</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2363,204 +2411,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>586700</v>
+        <v>802600</v>
       </c>
       <c r="E26" s="3">
-        <v>655400</v>
+        <v>653000</v>
       </c>
       <c r="F26" s="3">
-        <v>662900</v>
+        <v>729400</v>
       </c>
       <c r="G26" s="3">
-        <v>698500</v>
+        <v>737700</v>
       </c>
       <c r="H26" s="3">
-        <v>627200</v>
+        <v>777300</v>
       </c>
       <c r="I26" s="3">
-        <v>470100</v>
+        <v>698000</v>
       </c>
       <c r="J26" s="3">
+        <v>523200</v>
+      </c>
+      <c r="K26" s="3">
         <v>548200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>559200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>461200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>444600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>392100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>319200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>308000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>227100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>177200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>159300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>177900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>432300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>399900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>449600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>716200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>579400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>650800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>590100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>398100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>501800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>608200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>348900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>425700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>276200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>194700</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>568800</v>
+        <v>779100</v>
       </c>
       <c r="E27" s="3">
-        <v>629800</v>
+        <v>633000</v>
       </c>
       <c r="F27" s="3">
-        <v>638800</v>
+        <v>700900</v>
       </c>
       <c r="G27" s="3">
-        <v>672600</v>
+        <v>710900</v>
       </c>
       <c r="H27" s="3">
-        <v>602800</v>
+        <v>748500</v>
       </c>
       <c r="I27" s="3">
-        <v>442400</v>
+        <v>670900</v>
       </c>
       <c r="J27" s="3">
+        <v>492300</v>
+      </c>
+      <c r="K27" s="3">
         <v>523900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>542300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>461000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>428400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>376700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>300600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>285500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>210200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>163900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>138600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>163700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>411800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>391400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>434900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>694700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>555200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>579800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>572400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>373800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>481900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>590900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>329000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>399600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>273300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2657,8 +2714,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2755,8 +2815,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2853,8 +2916,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2951,204 +3017,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-41300</v>
+        <v>-63600</v>
       </c>
       <c r="E32" s="3">
-        <v>-2900</v>
+        <v>-45900</v>
       </c>
       <c r="F32" s="3">
-        <v>-18800</v>
+        <v>-3300</v>
       </c>
       <c r="G32" s="3">
-        <v>-83600</v>
+        <v>-20900</v>
       </c>
       <c r="H32" s="3">
-        <v>-19300</v>
+        <v>-93100</v>
       </c>
       <c r="I32" s="3">
-        <v>76100</v>
+        <v>-21500</v>
       </c>
       <c r="J32" s="3">
+        <v>84700</v>
+      </c>
+      <c r="K32" s="3">
         <v>-21900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-159000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-67100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-25400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-23800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-19600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-20000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-5800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-1400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-46200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>35100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-15000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>11000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-37200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>35000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>17900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-14300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-372500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>11900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-36500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-12800</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>568800</v>
+        <v>779100</v>
       </c>
       <c r="E33" s="3">
-        <v>629800</v>
+        <v>633000</v>
       </c>
       <c r="F33" s="3">
-        <v>638800</v>
+        <v>700900</v>
       </c>
       <c r="G33" s="3">
-        <v>672600</v>
+        <v>710900</v>
       </c>
       <c r="H33" s="3">
-        <v>602800</v>
+        <v>748500</v>
       </c>
       <c r="I33" s="3">
-        <v>442400</v>
+        <v>670900</v>
       </c>
       <c r="J33" s="3">
+        <v>492300</v>
+      </c>
+      <c r="K33" s="3">
         <v>523900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>542300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>461000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>428400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>376700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>300600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>285500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>210200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>163900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>138600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>163700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>411800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>391400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>434900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>694700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>555200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>579800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>572400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>373800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>481900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>590900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>329000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>399600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>273300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3245,209 +3320,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>568800</v>
+        <v>779100</v>
       </c>
       <c r="E35" s="3">
-        <v>629800</v>
+        <v>633000</v>
       </c>
       <c r="F35" s="3">
-        <v>638800</v>
+        <v>700900</v>
       </c>
       <c r="G35" s="3">
-        <v>672600</v>
+        <v>710900</v>
       </c>
       <c r="H35" s="3">
-        <v>602800</v>
+        <v>748500</v>
       </c>
       <c r="I35" s="3">
-        <v>442400</v>
+        <v>670900</v>
       </c>
       <c r="J35" s="3">
+        <v>492300</v>
+      </c>
+      <c r="K35" s="3">
         <v>523900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>542300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>461000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>428400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>376700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>300600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>285500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>210200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>163900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>138600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>163700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>411800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>391400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>434900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>694700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>555200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>579800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>572400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>373800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>481900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>590900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>329000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>399600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>273300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3482,8 +3566,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3518,106 +3603,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>2572300</v>
+        <v>3350100</v>
       </c>
       <c r="E41" s="3">
-        <v>2191200</v>
+        <v>2862600</v>
       </c>
       <c r="F41" s="3">
-        <v>2024300</v>
+        <v>2438500</v>
       </c>
       <c r="G41" s="3">
-        <v>2191300</v>
+        <v>2252700</v>
       </c>
       <c r="H41" s="3">
-        <v>1850000</v>
+        <v>2438600</v>
       </c>
       <c r="I41" s="3">
-        <v>2131800</v>
+        <v>2058800</v>
       </c>
       <c r="J41" s="3">
+        <v>2372400</v>
+      </c>
+      <c r="K41" s="3">
         <v>2046900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2585100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2094000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1862000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1975600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1732900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1723800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1601600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1837300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2194200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2199600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1689900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1514000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1792800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1449300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1421600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1196300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1343400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1327600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1516900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1482200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1381200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1083800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1209600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>789900</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3636,24 +3725,24 @@
       <c r="H42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I42" s="3">
-        <v>12800</v>
+      <c r="I42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J42" s="3">
+        <v>14300</v>
+      </c>
+      <c r="K42" s="3">
         <v>4900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>7300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>8700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>15600</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -3714,694 +3803,718 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>8061400</v>
+        <v>9051700</v>
       </c>
       <c r="E43" s="3">
-        <v>7189000</v>
+        <v>9020500</v>
       </c>
       <c r="F43" s="3">
-        <v>7132800</v>
+        <v>8000300</v>
       </c>
       <c r="G43" s="3">
-        <v>7271000</v>
+        <v>7937700</v>
       </c>
       <c r="H43" s="3">
-        <v>7094000</v>
+        <v>8091600</v>
       </c>
       <c r="I43" s="3">
-        <v>6187000</v>
+        <v>7894600</v>
       </c>
       <c r="J43" s="3">
+        <v>6885200</v>
+      </c>
+      <c r="K43" s="3">
         <v>6610100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6705900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6338400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>5855300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5745200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5791100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5818700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5049300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5218600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5668600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>6558100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7002300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6799600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7109800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>8093400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7464600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7593000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7131300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7166100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6920900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6481500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>5949400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5492900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5117000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>4460600</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>9178900</v>
+        <v>11335400</v>
       </c>
       <c r="E44" s="3">
-        <v>9312700</v>
+        <v>10214700</v>
       </c>
       <c r="F44" s="3">
-        <v>9515900</v>
+        <v>10363700</v>
       </c>
       <c r="G44" s="3">
-        <v>8897900</v>
+        <v>10589800</v>
       </c>
       <c r="H44" s="3">
-        <v>7829600</v>
+        <v>9902100</v>
       </c>
       <c r="I44" s="3">
-        <v>7936900</v>
+        <v>8713200</v>
       </c>
       <c r="J44" s="3">
+        <v>8832600</v>
+      </c>
+      <c r="K44" s="3">
         <v>8134700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7917100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6560400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6192300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6123000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6020100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5628400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6025000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6535000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7393100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7094800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>8199300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8217800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>8015200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>8048900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>7793600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>7851600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>7246200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>6601800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6847600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>6441600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>6211000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>4735700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5252300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4645600</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1332000</v>
+        <v>1738200</v>
       </c>
       <c r="E45" s="3">
-        <v>1375700</v>
+        <v>1433000</v>
       </c>
       <c r="F45" s="3">
-        <v>1584300</v>
+        <v>1530900</v>
       </c>
       <c r="G45" s="3">
-        <v>1582500</v>
+        <v>1763000</v>
       </c>
       <c r="H45" s="3">
-        <v>1323700</v>
+        <v>1761000</v>
       </c>
       <c r="I45" s="3">
-        <v>1265100</v>
+        <v>1473100</v>
       </c>
       <c r="J45" s="3">
+        <v>1407800</v>
+      </c>
+      <c r="K45" s="3">
         <v>1276600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1262900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1075800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1124300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>991000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1023700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>933200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>962600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1023800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1269500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1298700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1368900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1225300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1322900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1330200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1291000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1205900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1188900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1154700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1105700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1052800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1084600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1278800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1242800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1155000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>21144500</v>
+        <v>25475300</v>
       </c>
       <c r="E46" s="3">
-        <v>20068700</v>
+        <v>23530700</v>
       </c>
       <c r="F46" s="3">
-        <v>20257200</v>
+        <v>22333500</v>
       </c>
       <c r="G46" s="3">
-        <v>19942700</v>
+        <v>22543300</v>
       </c>
       <c r="H46" s="3">
-        <v>18097300</v>
+        <v>22193300</v>
       </c>
       <c r="I46" s="3">
-        <v>17533600</v>
+        <v>20139700</v>
       </c>
       <c r="J46" s="3">
+        <v>19512400</v>
+      </c>
+      <c r="K46" s="3">
         <v>18073000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18478300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>16077300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>15049600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14834700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14567700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14104100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>13638400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14614700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>16525500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>17151200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>18260400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17756700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>18240800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>18921700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17970800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17846800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16909800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16250200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16391200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>15458100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>14626200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>12591200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>12821700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>11051100</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>4886100</v>
+        <v>5984700</v>
       </c>
       <c r="E47" s="3">
-        <v>4495600</v>
+        <v>5437500</v>
       </c>
       <c r="F47" s="3">
-        <v>4635200</v>
+        <v>5002900</v>
       </c>
       <c r="G47" s="3">
-        <v>4504000</v>
+        <v>5158300</v>
       </c>
       <c r="H47" s="3">
-        <v>4035800</v>
+        <v>5012300</v>
       </c>
       <c r="I47" s="3">
-        <v>4107900</v>
+        <v>4491300</v>
       </c>
       <c r="J47" s="3">
+        <v>4571500</v>
+      </c>
+      <c r="K47" s="3">
         <v>4370400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4307100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3692900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3632900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3650400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3831400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3505200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3513400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3679600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4108100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4109500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4302400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4281700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4254400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4431700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>3945800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4110500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3870100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3656300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3775100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3603400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3962700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3654400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3553700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3114700</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6235100</v>
+        <v>7181200</v>
       </c>
       <c r="E48" s="3">
-        <v>6058100</v>
+        <v>6938800</v>
       </c>
       <c r="F48" s="3">
-        <v>6055900</v>
+        <v>6741700</v>
       </c>
       <c r="G48" s="3">
-        <v>5946200</v>
+        <v>6739300</v>
       </c>
       <c r="H48" s="3">
-        <v>5726000</v>
+        <v>6617300</v>
       </c>
       <c r="I48" s="3">
-        <v>5677200</v>
+        <v>6372200</v>
       </c>
       <c r="J48" s="3">
+        <v>6317900</v>
+      </c>
+      <c r="K48" s="3">
         <v>5942400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6174500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5851600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5836700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6043400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6152900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5993200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6007500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6325100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6898700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>7146100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7436500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7400100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7454200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7461400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7167800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7111300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>6849300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6694400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6941200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6903500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6874400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6023000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6087900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>5725600</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2735700</v>
+        <v>3198200</v>
       </c>
       <c r="E49" s="3">
-        <v>2662200</v>
+        <v>3044500</v>
       </c>
       <c r="F49" s="3">
-        <v>2541800</v>
+        <v>2962600</v>
       </c>
       <c r="G49" s="3">
-        <v>2521400</v>
+        <v>2828700</v>
       </c>
       <c r="H49" s="3">
-        <v>2388400</v>
+        <v>2806000</v>
       </c>
       <c r="I49" s="3">
-        <v>2375000</v>
+        <v>2657900</v>
       </c>
       <c r="J49" s="3">
+        <v>2643100</v>
+      </c>
+      <c r="K49" s="3">
         <v>2594800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2585000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2367900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2330800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2406100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2479900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2408200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2370200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2505800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2768200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2815500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3096100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3079300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2972100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3155200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3161900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3289100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3137100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>2975000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3245200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3273300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3281300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>897200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>891700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>852900</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4498,8 +4611,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4596,106 +4712,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>960400</v>
+        <v>1029400</v>
       </c>
       <c r="E52" s="3">
-        <v>972400</v>
+        <v>1068800</v>
       </c>
       <c r="F52" s="3">
-        <v>987900</v>
+        <v>1082100</v>
       </c>
       <c r="G52" s="3">
-        <v>887400</v>
+        <v>1099400</v>
       </c>
       <c r="H52" s="3">
-        <v>860400</v>
+        <v>987500</v>
       </c>
       <c r="I52" s="3">
-        <v>825800</v>
+        <v>957500</v>
       </c>
       <c r="J52" s="3">
+        <v>919000</v>
+      </c>
+      <c r="K52" s="3">
         <v>935600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>908800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>877800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>818200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>849300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>827500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>823800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>807200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>875700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>926900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>966700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>877800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>911400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>893200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>993200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>881500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>914100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>875400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>911800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>925500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>867000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>685400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>397300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>395700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>472700</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4792,106 +4914,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>35961900</v>
+        <v>42868800</v>
       </c>
       <c r="E54" s="3">
-        <v>34256900</v>
+        <v>40020300</v>
       </c>
       <c r="F54" s="3">
-        <v>34478100</v>
+        <v>38122900</v>
       </c>
       <c r="G54" s="3">
-        <v>33801800</v>
+        <v>38369000</v>
       </c>
       <c r="H54" s="3">
-        <v>31107900</v>
+        <v>37616400</v>
       </c>
       <c r="I54" s="3">
-        <v>30519700</v>
+        <v>34618500</v>
       </c>
       <c r="J54" s="3">
+        <v>33963900</v>
+      </c>
+      <c r="K54" s="3">
         <v>31916200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>32453700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>28867500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>27668100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27783800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27859400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>26834500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26336600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>28001000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>31227300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>32189000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>33973200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>33429200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33814600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>34963300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33127800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>33271700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>31641700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>30487700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>31278300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>30105200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>29429900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>23563000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>23750700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>21217100</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4926,8 +5054,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4962,596 +5091,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2043600</v>
+        <v>2322200</v>
       </c>
       <c r="E57" s="3">
-        <v>2053600</v>
+        <v>2274200</v>
       </c>
       <c r="F57" s="3">
-        <v>2224500</v>
+        <v>2285400</v>
       </c>
       <c r="G57" s="3">
-        <v>2343800</v>
+        <v>2475600</v>
       </c>
       <c r="H57" s="3">
-        <v>2311900</v>
+        <v>2608300</v>
       </c>
       <c r="I57" s="3">
-        <v>2157000</v>
+        <v>2572800</v>
       </c>
       <c r="J57" s="3">
+        <v>2400400</v>
+      </c>
+      <c r="K57" s="3">
         <v>2272000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2341700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2250800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1971700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1939100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1908900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1831500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1597300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1511700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1742400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1939600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2091700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2278800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2338800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2565400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2413100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2557500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2485200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2744100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2742000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2594600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2526300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2129800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>1891800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1680000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3706600</v>
+        <v>5957500</v>
       </c>
       <c r="E58" s="3">
-        <v>4015800</v>
+        <v>4124900</v>
       </c>
       <c r="F58" s="3">
-        <v>3174200</v>
+        <v>4469000</v>
       </c>
       <c r="G58" s="3">
-        <v>3889000</v>
+        <v>3532400</v>
       </c>
       <c r="H58" s="3">
-        <v>3110700</v>
+        <v>4327900</v>
       </c>
       <c r="I58" s="3">
-        <v>3926400</v>
+        <v>3461800</v>
       </c>
       <c r="J58" s="3">
+        <v>4369600</v>
+      </c>
+      <c r="K58" s="3">
         <v>4638700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4641200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3442000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3599600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3247400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2968400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2619500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2928500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3409100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>5190700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5308400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5845400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5004000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4708300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4403400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4835900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>3995900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4127800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>2982300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3226400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2743000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4866100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1932300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2705700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1856900</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3986900</v>
+        <v>4590900</v>
       </c>
       <c r="E59" s="3">
-        <v>3641200</v>
+        <v>4436900</v>
       </c>
       <c r="F59" s="3">
-        <v>3796600</v>
+        <v>4052200</v>
       </c>
       <c r="G59" s="3">
-        <v>3706200</v>
+        <v>4225100</v>
       </c>
       <c r="H59" s="3">
-        <v>3328600</v>
+        <v>4124400</v>
       </c>
       <c r="I59" s="3">
-        <v>3126100</v>
+        <v>3704300</v>
       </c>
       <c r="J59" s="3">
+        <v>3478900</v>
+      </c>
+      <c r="K59" s="3">
         <v>3172600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3188000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3098700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2715800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2697500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2611000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2588500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2524800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2635500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2809300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2959500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3169700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3262900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3290300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3430500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3011500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3336600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3020600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3220100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3131200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>2985200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2675700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2148500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1977100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1932900</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>9737100</v>
+        <v>12870600</v>
       </c>
       <c r="E60" s="3">
-        <v>9710600</v>
+        <v>10836000</v>
       </c>
       <c r="F60" s="3">
-        <v>9195400</v>
+        <v>10806500</v>
       </c>
       <c r="G60" s="3">
-        <v>9939000</v>
+        <v>10233100</v>
       </c>
       <c r="H60" s="3">
-        <v>8751200</v>
+        <v>11060600</v>
       </c>
       <c r="I60" s="3">
-        <v>9209500</v>
+        <v>9738800</v>
       </c>
       <c r="J60" s="3">
+        <v>10248800</v>
+      </c>
+      <c r="K60" s="3">
         <v>10083400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10170900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8791500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8287000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>7884100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7488300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7039400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7050600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7556300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>9742300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>10207500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>11106800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10545700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10337400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10399400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10260500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>9890100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9633600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>8946500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9099600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8322800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>10068000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>6210600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6574700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>5469800</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3945300</v>
+        <v>4187600</v>
       </c>
       <c r="E61" s="3">
-        <v>3687500</v>
+        <v>4390600</v>
       </c>
       <c r="F61" s="3">
-        <v>4179000</v>
+        <v>4103600</v>
       </c>
       <c r="G61" s="3">
-        <v>3806100</v>
+        <v>4650600</v>
       </c>
       <c r="H61" s="3">
-        <v>3612300</v>
+        <v>4235700</v>
       </c>
       <c r="I61" s="3">
-        <v>3495500</v>
+        <v>4019900</v>
       </c>
       <c r="J61" s="3">
+        <v>3890000</v>
+      </c>
+      <c r="K61" s="3">
         <v>2829400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3203300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2848600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2748000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2986100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3685700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3832300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3788600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4116400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3747600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3610700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3704600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3739100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4491900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4540600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4285500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4526300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4365800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4345500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4771500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4645600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2829700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1692900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1742600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1577700</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1873300</v>
+        <v>2143400</v>
       </c>
       <c r="E62" s="3">
-        <v>1784200</v>
+        <v>2084700</v>
       </c>
       <c r="F62" s="3">
-        <v>1856400</v>
+        <v>1985600</v>
       </c>
       <c r="G62" s="3">
-        <v>1766300</v>
+        <v>2065900</v>
       </c>
       <c r="H62" s="3">
-        <v>1659100</v>
+        <v>1965600</v>
       </c>
       <c r="I62" s="3">
-        <v>1620300</v>
+        <v>1846300</v>
       </c>
       <c r="J62" s="3">
+        <v>1803200</v>
+      </c>
+      <c r="K62" s="3">
         <v>1699100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1735200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1581700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1611800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1672700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1756800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1697600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1628100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1786600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1929800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>2017500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1936900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1955600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1946800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1736800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1588900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1545500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1485000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1433600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1437400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1448700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1400700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1037100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1041600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>965200</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5648,8 +5796,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5746,8 +5897,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5844,106 +5998,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>16607700</v>
+        <v>20437900</v>
       </c>
       <c r="E66" s="3">
-        <v>16161200</v>
+        <v>18481900</v>
       </c>
       <c r="F66" s="3">
-        <v>16197800</v>
+        <v>17985000</v>
       </c>
       <c r="G66" s="3">
-        <v>16455200</v>
+        <v>18025700</v>
       </c>
       <c r="H66" s="3">
-        <v>14905000</v>
+        <v>18312200</v>
       </c>
       <c r="I66" s="3">
-        <v>15158900</v>
+        <v>16587100</v>
       </c>
       <c r="J66" s="3">
+        <v>16869600</v>
+      </c>
+      <c r="K66" s="3">
         <v>15474000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15972600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>14043700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>13489900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13380200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13660300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13276300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13146300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>14153500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>16184500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>16581100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>17541800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16997900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>17543800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17515500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16912800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16751000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16218100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>15440300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16046200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>15109600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>14968700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>9577900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9984500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>8556800</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5978,8 +6138,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6076,8 +6237,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6174,8 +6338,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6272,8 +6439,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6370,106 +6540,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>15414100</v>
+        <v>17294400</v>
       </c>
       <c r="E72" s="3">
-        <v>14845200</v>
+        <v>17153600</v>
       </c>
       <c r="F72" s="3">
-        <v>14650100</v>
+        <v>16520600</v>
       </c>
       <c r="G72" s="3">
-        <v>14011400</v>
+        <v>16303500</v>
       </c>
       <c r="H72" s="3">
-        <v>13801800</v>
+        <v>15592600</v>
       </c>
       <c r="I72" s="3">
-        <v>13199000</v>
+        <v>15359400</v>
       </c>
       <c r="J72" s="3">
+        <v>14688600</v>
+      </c>
+      <c r="K72" s="3">
         <v>13142900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13331000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>12950700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12922300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13385000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>13260900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12749900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12886400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>13604200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>14720100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>15384800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15739500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15939800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15497700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>16338300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15366800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>15023600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>14132800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>13901600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13527900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13353100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>12762200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12442100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>12042600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>12011900</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6566,8 +6742,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6664,8 +6843,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6762,106 +6944,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>19354200</v>
+        <v>22430900</v>
       </c>
       <c r="E76" s="3">
-        <v>18095700</v>
+        <v>21538300</v>
       </c>
       <c r="F76" s="3">
-        <v>18280300</v>
+        <v>20137900</v>
       </c>
       <c r="G76" s="3">
-        <v>17346600</v>
+        <v>20343300</v>
       </c>
       <c r="H76" s="3">
-        <v>16202900</v>
+        <v>19304200</v>
       </c>
       <c r="I76" s="3">
-        <v>15360800</v>
+        <v>18031500</v>
       </c>
       <c r="J76" s="3">
+        <v>17094300</v>
+      </c>
+      <c r="K76" s="3">
         <v>16442200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16481100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14823900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14178100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14403600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14199100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>13558200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13190300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13847500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15042800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15607800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16431500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16431400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16270800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>17447700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16215000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16520700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15423500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15047400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15232100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>14995700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14461200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>13985100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13766200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>12660300</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6958,209 +7146,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>568800</v>
+        <v>779100</v>
       </c>
       <c r="E81" s="3">
-        <v>629800</v>
+        <v>633000</v>
       </c>
       <c r="F81" s="3">
-        <v>638800</v>
+        <v>700900</v>
       </c>
       <c r="G81" s="3">
-        <v>672600</v>
+        <v>710900</v>
       </c>
       <c r="H81" s="3">
-        <v>602800</v>
+        <v>748500</v>
       </c>
       <c r="I81" s="3">
-        <v>442400</v>
+        <v>670900</v>
       </c>
       <c r="J81" s="3">
+        <v>492300</v>
+      </c>
+      <c r="K81" s="3">
         <v>523900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>542300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>461000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>428400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>376700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>300600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>285500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>210200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>163900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>138600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>163700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>411800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>391400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>434900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>694700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>555200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>579800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>572400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>373800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>481900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>590900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>329000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>399600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>273300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7195,106 +7392,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>251400</v>
+        <v>290200</v>
       </c>
       <c r="E83" s="3">
-        <v>261500</v>
+        <v>279700</v>
       </c>
       <c r="F83" s="3">
-        <v>248600</v>
+        <v>291100</v>
       </c>
       <c r="G83" s="3">
-        <v>239200</v>
+        <v>276600</v>
       </c>
       <c r="H83" s="3">
-        <v>243100</v>
+        <v>266200</v>
       </c>
       <c r="I83" s="3">
-        <v>245600</v>
+        <v>270600</v>
       </c>
       <c r="J83" s="3">
+        <v>273400</v>
+      </c>
+      <c r="K83" s="3">
         <v>235400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>243800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>247600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>215000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>241600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>251700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>247200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>245900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>256200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>271400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>302800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>296400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>294100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>299300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>320500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>309400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>301200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>299200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>316900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>301900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>295000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>296800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>238900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>226700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>222400</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7391,8 +7592,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7489,8 +7693,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7587,8 +7794,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7685,8 +7895,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7783,106 +7996,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>997200</v>
+        <v>596000</v>
       </c>
       <c r="E89" s="3">
-        <v>581700</v>
+        <v>1109700</v>
       </c>
       <c r="F89" s="3">
-        <v>650000</v>
+        <v>647300</v>
       </c>
       <c r="G89" s="3">
-        <v>545000</v>
+        <v>723400</v>
       </c>
       <c r="H89" s="3">
-        <v>787300</v>
+        <v>606600</v>
       </c>
       <c r="I89" s="3">
-        <v>367100</v>
+        <v>876200</v>
       </c>
       <c r="J89" s="3">
+        <v>408500</v>
+      </c>
+      <c r="K89" s="3">
         <v>177900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-15800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>770900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>188500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>669300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>474800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>813600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>636600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>759600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>469400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1208900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>202300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>715400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>530400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>982200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>259100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>677800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>603600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>357400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>376500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>971600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>448000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>444400</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7917,106 +8136,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-46288000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-50938000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-63292000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-48195000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-40522000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-48621000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-48655000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-49879000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-36378000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-39135000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-41538000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-44307000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-279100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-314200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-380900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-374000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-317900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-397700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-434800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-439600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-403000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-453500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-552400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-411600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-382200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-288700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-389600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-331300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-390900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-378000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-298900</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8113,8 +8336,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8211,106 +8437,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-290900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-310900</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-562500</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-298600</v>
+      </c>
+      <c r="H94" s="3">
         <v>-279400</v>
       </c>
-      <c r="E94" s="3">
-        <v>-505400</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-268300</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-251100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-246300</v>
-      </c>
       <c r="I94" s="3">
-        <v>-290800</v>
+        <v>-274100</v>
       </c>
       <c r="J94" s="3">
+        <v>-323700</v>
+      </c>
+      <c r="K94" s="3">
         <v>-331000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-225400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-262000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-239100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-285800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-218000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-258800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-341100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-347300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-302300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-366600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-388200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-542900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-436300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-432300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-524300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-408300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-388400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-520100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-228800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>103500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2769300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-347600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-233600</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8345,106 +8577,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>-638300</v>
       </c>
       <c r="E96" s="3">
-        <v>-434700</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>-483800</v>
       </c>
       <c r="G96" s="3">
-        <v>-452700</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>-503700</v>
       </c>
       <c r="I96" s="3">
-        <v>-386300</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>0</v>
+        <v>-429800</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-357000</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-259900</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-257100</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-124700</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-314400</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-473400</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-510400</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-454600</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-411800</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-307100</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-247400</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-242700</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8541,8 +8777,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8639,8 +8878,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8737,298 +8979,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-377900</v>
+        <v>85100</v>
       </c>
       <c r="E100" s="3">
-        <v>107200</v>
+        <v>-420500</v>
       </c>
       <c r="F100" s="3">
-        <v>-547500</v>
+        <v>119300</v>
       </c>
       <c r="G100" s="3">
-        <v>39600</v>
+        <v>-609300</v>
       </c>
       <c r="H100" s="3">
-        <v>-814700</v>
+        <v>44000</v>
       </c>
       <c r="I100" s="3">
-        <v>98700</v>
+        <v>-906700</v>
       </c>
       <c r="J100" s="3">
+        <v>109900</v>
+      </c>
+      <c r="K100" s="3">
         <v>-175500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>492900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-247600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>17200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-111700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-320400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-371100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-442100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-584000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-102700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-261700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>363600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-431900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>305300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-522600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>409300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-408800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>466900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-341500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>246200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-372500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>2673000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-763500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>417200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-385800</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>41100</v>
+        <v>97300</v>
       </c>
       <c r="E101" s="3">
-        <v>-16500</v>
+        <v>45800</v>
       </c>
       <c r="F101" s="3">
-        <v>-1300</v>
+        <v>-18300</v>
       </c>
       <c r="G101" s="3">
-        <v>7700</v>
+        <v>-1400</v>
       </c>
       <c r="H101" s="3">
-        <v>-8000</v>
+        <v>8600</v>
       </c>
       <c r="I101" s="3">
-        <v>-90000</v>
+        <v>-8900</v>
       </c>
       <c r="J101" s="3">
+        <v>-100200</v>
+      </c>
+      <c r="K101" s="3">
         <v>-71500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>207900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>33000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>21100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>4100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>10400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>19000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>10900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-17000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>10400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-20800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>12800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-24800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>62300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-40600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-66000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>69000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>13700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>8900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>13800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-66000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>381000</v>
+        <v>487500</v>
       </c>
       <c r="E102" s="3">
-        <v>167000</v>
+        <v>424000</v>
       </c>
       <c r="F102" s="3">
-        <v>-167100</v>
+        <v>185800</v>
       </c>
       <c r="G102" s="3">
-        <v>341300</v>
+        <v>-185900</v>
       </c>
       <c r="H102" s="3">
-        <v>-281700</v>
+        <v>379800</v>
       </c>
       <c r="I102" s="3">
-        <v>84900</v>
+        <v>-313500</v>
       </c>
       <c r="J102" s="3">
+        <v>94500</v>
+      </c>
+      <c r="K102" s="3">
         <v>-400100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>459600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>294300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-12300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>275900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-53300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>175400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-127500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-160800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>63900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>563600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>188100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-280200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>412300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>2500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>206500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-179800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>11900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>35100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>97400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>278000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-125700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>416200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-166700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KMTUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KMTUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>KMTUY</t>
   </si>
@@ -656,446 +656,464 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>6814800</v>
-      </c>
-      <c r="E8" s="3">
-        <v>7597900</v>
-      </c>
-      <c r="F8" s="3">
-        <v>6901200</v>
-      </c>
-      <c r="G8" s="3">
-        <v>6556400</v>
-      </c>
-      <c r="H8" s="3">
-        <v>6386800</v>
-      </c>
-      <c r="I8" s="3">
-        <v>7130100</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="3">
         <v>6535500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5454400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5148100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5230000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4968900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4637000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4764800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4794300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4072500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3887100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3913000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>5439500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5593100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5548200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5585500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>6790800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6613400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6242700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>5872700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6285600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5847500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5403600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5073300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5111600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3819400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3608800</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
-        <v>4574400</v>
-      </c>
-      <c r="E9" s="3">
-        <v>5344500</v>
-      </c>
-      <c r="F9" s="3">
-        <v>4721300</v>
-      </c>
-      <c r="G9" s="3">
-        <v>4444300</v>
-      </c>
-      <c r="H9" s="3">
-        <v>4339800</v>
-      </c>
-      <c r="I9" s="3">
-        <v>5061100</v>
-      </c>
-      <c r="J9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K9" s="3">
         <v>4573500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>3841100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3676000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3769800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3589200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3298400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3491800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3540700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2999800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2844100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2855200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3983000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4023200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3933000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3914600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4734300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4644500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4266600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4011000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4364100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4072000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>3892100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3635600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3643900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2714800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2572600</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3">
-        <v>2240400</v>
-      </c>
-      <c r="E10" s="3">
-        <v>2253500</v>
-      </c>
-      <c r="F10" s="3">
-        <v>2179900</v>
-      </c>
-      <c r="G10" s="3">
-        <v>2112200</v>
-      </c>
-      <c r="H10" s="3">
-        <v>2047000</v>
-      </c>
-      <c r="I10" s="3">
-        <v>2069000</v>
-      </c>
-      <c r="J10" s="3">
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K10" s="3">
         <v>1962000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1613400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1472100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1460200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1379700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1338600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1272900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1253500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1072700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1043000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1057800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1456500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1569900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1615200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1670900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2056500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1968800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1976100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1861700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1921400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1775500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1511500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1437700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1467700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1104600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1036300</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1131,8 +1149,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1232,8 +1251,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1333,16 +1355,19 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>43400</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1353,8 +1378,8 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>39200</v>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1365,24 +1390,24 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>9100</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>17000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1398,8 +1423,8 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1407,8 +1432,8 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1425,40 +1450,43 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>15500</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1535,8 +1563,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1569,210 +1600,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>5700200</v>
-      </c>
-      <c r="E17" s="3">
-        <v>6506100</v>
-      </c>
-      <c r="F17" s="3">
-        <v>5790400</v>
-      </c>
-      <c r="G17" s="3">
-        <v>5491800</v>
-      </c>
-      <c r="H17" s="3">
-        <v>5343000</v>
-      </c>
-      <c r="I17" s="3">
-        <v>6107100</v>
-      </c>
-      <c r="J17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K17" s="3">
         <v>5577300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4701100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4517500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4610800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4367900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4099600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4310900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4370300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>3726600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3626700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3683400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>5061800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4993300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4930400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4900700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>5810800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5711600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5274100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4999600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5531700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5170900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4865900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4606000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4516700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3304300</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>1114700</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1091800</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1110800</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1064700</v>
-      </c>
-      <c r="H18" s="3">
-        <v>1043800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>1023000</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K18" s="3">
         <v>958300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>753300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>630600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>619200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>601000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>537400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>453900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>423900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>345900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>260400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>229600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>377800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>599900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>617800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>684800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>979900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>901800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>968600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>873100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>753900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>676500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>537700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>467400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>594900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>380500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>304600</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1808,513 +1846,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>63600</v>
-      </c>
-      <c r="E20" s="3">
-        <v>45900</v>
-      </c>
-      <c r="F20" s="3">
-        <v>3300</v>
-      </c>
-      <c r="G20" s="3">
-        <v>20900</v>
-      </c>
-      <c r="H20" s="3">
-        <v>93100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>21500</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>-84700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>21900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>159000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>67100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>25400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>23800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>19600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>20000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>5800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>46200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-35100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>15000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>37200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-35000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>12000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>21000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-17900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>14300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>372500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-11900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>36500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>1468500</v>
-      </c>
-      <c r="E21" s="3">
-        <v>1417400</v>
-      </c>
-      <c r="F21" s="3">
-        <v>1405100</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1362200</v>
-      </c>
-      <c r="H21" s="3">
-        <v>1403100</v>
-      </c>
-      <c r="I21" s="3">
-        <v>1315100</v>
-      </c>
-      <c r="J21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K21" s="3">
         <v>1146900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1010600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1033400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>933900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>841300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>802800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>725200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>691100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>597700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>517900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>547300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>645500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>911300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>916800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>973100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1337600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1176100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1281800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1193400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1052800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>992600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1205300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>763800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>821800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>643700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>539800</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>109400</v>
-      </c>
-      <c r="E22" s="3">
-        <v>105400</v>
-      </c>
-      <c r="F22" s="3">
-        <v>104100</v>
-      </c>
-      <c r="G22" s="3">
-        <v>92600</v>
-      </c>
-      <c r="H22" s="3">
-        <v>84900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>74500</v>
-      </c>
-      <c r="J22" s="3">
+      <c r="D22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K22" s="3">
         <v>78000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>39700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>31500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>23100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>21800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>22700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>23200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>27800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>32800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>50200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>52700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>59300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>60900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>61000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>59900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>55600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>49300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>44700</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>46900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>42200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>32300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>22400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>16300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>1068900</v>
-      </c>
-      <c r="E23" s="3">
-        <v>1032300</v>
-      </c>
-      <c r="F23" s="3">
-        <v>1010000</v>
-      </c>
-      <c r="G23" s="3">
-        <v>992900</v>
-      </c>
-      <c r="H23" s="3">
-        <v>1052000</v>
-      </c>
-      <c r="I23" s="3">
-        <v>970100</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K23" s="3">
         <v>795500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>735500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>758100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>665700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>603200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>541100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>451700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>421300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>328600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>234000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>243100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>292400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>562200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>563400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>612900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>956100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>806800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>925000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>844800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>691300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>643900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>868000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>434800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>560600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>400600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>300600</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>266200</v>
-      </c>
-      <c r="E24" s="3">
-        <v>379300</v>
-      </c>
-      <c r="F24" s="3">
-        <v>280600</v>
-      </c>
-      <c r="G24" s="3">
-        <v>255300</v>
-      </c>
-      <c r="H24" s="3">
-        <v>274600</v>
-      </c>
-      <c r="I24" s="3">
-        <v>272100</v>
-      </c>
-      <c r="J24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K24" s="3">
         <v>272300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>187300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>198900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>204400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>158600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>149000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>132500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>113200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>101500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>56700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>83700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>114500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>129800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>163500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>163300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>239900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>227500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>274200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>254700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>293100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>142000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>259900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>85900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>135000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>124400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>105900</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2414,210 +2468,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>802600</v>
-      </c>
-      <c r="E26" s="3">
-        <v>653000</v>
-      </c>
-      <c r="F26" s="3">
-        <v>729400</v>
-      </c>
-      <c r="G26" s="3">
-        <v>737700</v>
-      </c>
-      <c r="H26" s="3">
-        <v>777300</v>
-      </c>
-      <c r="I26" s="3">
-        <v>698000</v>
-      </c>
-      <c r="J26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K26" s="3">
         <v>523200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>548200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>559200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>461200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>444600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>392100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>319200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>308000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>227100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>177200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>159300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>177900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>432300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>399900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>449600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>716200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>579400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>650800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>590100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>398100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>501800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>608200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>348900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>425700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>276200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>194700</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>779100</v>
-      </c>
-      <c r="E27" s="3">
-        <v>633000</v>
-      </c>
-      <c r="F27" s="3">
-        <v>700900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>710900</v>
-      </c>
-      <c r="H27" s="3">
-        <v>748500</v>
-      </c>
-      <c r="I27" s="3">
-        <v>670900</v>
-      </c>
-      <c r="J27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K27" s="3">
         <v>492300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>523900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>542300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>461000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>428400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>376700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>300600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>285500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>210200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>163900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>138600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>163700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>411800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>391400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>434900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>694700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>555200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>579800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>572400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>373800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>481900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>590900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>329000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>399600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>273300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2717,31 +2780,34 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2818,8 +2884,11 @@
       <c r="AI29" s="3">
         <v>0</v>
       </c>
+      <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2919,8 +2988,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3020,210 +3092,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>-63600</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-45900</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-20900</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-93100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>-21500</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>84700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-21900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-159000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-67100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-25400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-23800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-19600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-20000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-5800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-46200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>35100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-15000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>11000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-37200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>35000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>17900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-14300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-372500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>11900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-36500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-12800</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>779100</v>
-      </c>
-      <c r="E33" s="3">
-        <v>633000</v>
-      </c>
-      <c r="F33" s="3">
-        <v>700900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>710900</v>
-      </c>
-      <c r="H33" s="3">
-        <v>748500</v>
-      </c>
-      <c r="I33" s="3">
-        <v>670900</v>
-      </c>
-      <c r="J33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K33" s="3">
         <v>492300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>523900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>542300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>461000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>428400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>376700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>300600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>285500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>210200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>163900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>138600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>163700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>411800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>391400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>434900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>694700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>555200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>579800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>572400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>373800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>481900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>590900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>329000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>399600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>273300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3323,215 +3404,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>779100</v>
-      </c>
-      <c r="E35" s="3">
-        <v>633000</v>
-      </c>
-      <c r="F35" s="3">
-        <v>700900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>710900</v>
-      </c>
-      <c r="H35" s="3">
-        <v>748500</v>
-      </c>
-      <c r="I35" s="3">
-        <v>670900</v>
-      </c>
-      <c r="J35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K35" s="3">
         <v>492300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>523900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>542300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>461000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>428400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>376700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>300600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>285500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>210200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>163900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>138600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>163700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>411800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>391400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>434900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>694700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>555200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>579800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>572400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>373800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>481900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>590900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>329000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>399600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>273300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3567,8 +3657,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3604,148 +3695,152 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3350100</v>
+        <v>2858600</v>
       </c>
       <c r="E41" s="3">
-        <v>2862600</v>
+        <v>2933100</v>
       </c>
       <c r="F41" s="3">
-        <v>2438500</v>
+        <v>2665600</v>
       </c>
       <c r="G41" s="3">
-        <v>2252700</v>
+        <v>2436500</v>
       </c>
       <c r="H41" s="3">
-        <v>2438600</v>
+        <v>2124300</v>
       </c>
       <c r="I41" s="3">
-        <v>2058800</v>
+        <v>2375600</v>
       </c>
       <c r="J41" s="3">
+        <v>2181300</v>
+      </c>
+      <c r="K41" s="3">
         <v>2372400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2046900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2585100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2094000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1862000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1975600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1732900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1723800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1601600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1837300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2194200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2199600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1689900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1514000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1792800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1449300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1421600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1196300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1343400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1327600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1516900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1482200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1381200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1083800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1209600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>789900</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>8</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>25000</v>
+      </c>
+      <c r="G42" s="3">
+        <v>22700</v>
+      </c>
+      <c r="H42" s="3">
+        <v>33500</v>
+      </c>
+      <c r="I42" s="3">
+        <v>36600</v>
       </c>
       <c r="J42" s="3">
+        <v>33800</v>
+      </c>
+      <c r="K42" s="3">
         <v>14300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>4900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>15600</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -3806,715 +3901,739 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>9051700</v>
+        <v>8090200</v>
       </c>
       <c r="E43" s="3">
-        <v>9020500</v>
+        <v>7925100</v>
       </c>
       <c r="F43" s="3">
-        <v>8000300</v>
+        <v>8399600</v>
       </c>
       <c r="G43" s="3">
-        <v>7937700</v>
+        <v>7993700</v>
       </c>
       <c r="H43" s="3">
-        <v>8091600</v>
+        <v>7485100</v>
       </c>
       <c r="I43" s="3">
-        <v>7894600</v>
+        <v>7882300</v>
       </c>
       <c r="J43" s="3">
+        <v>8383000</v>
+      </c>
+      <c r="K43" s="3">
         <v>6885200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6610100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6705900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6338400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>5855300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5745200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5791100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5818700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5049300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5218600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5668600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>6558100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>7002300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6799600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7109800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>8093400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7464600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7593000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7131300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7166100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>6920900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6481500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>5949400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5492900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5117000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>4460600</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>11335400</v>
+        <v>10168000</v>
       </c>
       <c r="E44" s="3">
-        <v>10214700</v>
+        <v>9924600</v>
       </c>
       <c r="F44" s="3">
-        <v>10363700</v>
+        <v>9511700</v>
       </c>
       <c r="G44" s="3">
-        <v>10589800</v>
+        <v>10355100</v>
       </c>
       <c r="H44" s="3">
-        <v>9902100</v>
+        <v>9985900</v>
       </c>
       <c r="I44" s="3">
-        <v>8713200</v>
+        <v>9645900</v>
       </c>
       <c r="J44" s="3">
+        <v>9231700</v>
+      </c>
+      <c r="K44" s="3">
         <v>8832600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8134700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7917100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6560400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6192300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6123000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6020100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5628400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6025000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6535000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>7393100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>7094800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>8199300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>8217800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>8015200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>8048900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>7793600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>7851600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>7246200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>6601800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>6847600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>6441600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>6211000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>4735700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5252300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4645600</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>1738200</v>
+        <v>1625000</v>
       </c>
       <c r="E45" s="3">
-        <v>1433000</v>
+        <v>1521800</v>
       </c>
       <c r="F45" s="3">
-        <v>1530900</v>
+        <v>1192600</v>
       </c>
       <c r="G45" s="3">
-        <v>1763000</v>
+        <v>1507000</v>
       </c>
       <c r="H45" s="3">
-        <v>1761000</v>
+        <v>1629000</v>
       </c>
       <c r="I45" s="3">
-        <v>1473100</v>
+        <v>1678900</v>
       </c>
       <c r="J45" s="3">
+        <v>1416200</v>
+      </c>
+      <c r="K45" s="3">
         <v>1407800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1276600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1262900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1075800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1124300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>991000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1023700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>933200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>962600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1023800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1269500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1298700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1368900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1225300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1322900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1330200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1291000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1205900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1188900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1154700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1105700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1052800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1084600</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1278800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1242800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1155000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>25475300</v>
+        <v>22741800</v>
       </c>
       <c r="E46" s="3">
-        <v>23530700</v>
+        <v>22304700</v>
       </c>
       <c r="F46" s="3">
-        <v>22333500</v>
+        <v>21911300</v>
       </c>
       <c r="G46" s="3">
-        <v>22543300</v>
+        <v>22314900</v>
       </c>
       <c r="H46" s="3">
-        <v>22193300</v>
+        <v>21257800</v>
       </c>
       <c r="I46" s="3">
-        <v>20139700</v>
+        <v>21619200</v>
       </c>
       <c r="J46" s="3">
+        <v>21338200</v>
+      </c>
+      <c r="K46" s="3">
         <v>19512400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>18073000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18478300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>16077300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>15049600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14834700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14567700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14104100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>13638400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>14614700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>16525500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17151200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18260400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17756700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>18240800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>18921700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17970800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>17846800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>16909800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16250200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>16391200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>15458100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>14626200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>12591200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>12821700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>11051100</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>5984700</v>
+        <v>6518300</v>
       </c>
       <c r="E47" s="3">
-        <v>5437500</v>
+        <v>6141100</v>
       </c>
       <c r="F47" s="3">
-        <v>5002900</v>
+        <v>543600</v>
       </c>
       <c r="G47" s="3">
-        <v>5158300</v>
+        <v>566700</v>
       </c>
       <c r="H47" s="3">
-        <v>5012300</v>
+        <v>481600</v>
       </c>
       <c r="I47" s="3">
-        <v>4491300</v>
+        <v>495500</v>
       </c>
       <c r="J47" s="3">
+        <v>506000</v>
+      </c>
+      <c r="K47" s="3">
         <v>4571500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4370400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4307100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3692900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3632900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3650400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3831400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3505200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3513400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3679600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>4108100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4109500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4302400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4281700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4254400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4431700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>3945800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4110500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3870100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3656300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3775100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3603400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3962700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3654400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3553700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>3114700</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7181200</v>
+        <v>6682600</v>
       </c>
       <c r="E48" s="3">
-        <v>6938800</v>
+        <v>6287500</v>
       </c>
       <c r="F48" s="3">
-        <v>6741700</v>
+        <v>6461200</v>
       </c>
       <c r="G48" s="3">
-        <v>6739300</v>
+        <v>6736200</v>
       </c>
       <c r="H48" s="3">
-        <v>6617300</v>
+        <v>6355000</v>
       </c>
       <c r="I48" s="3">
-        <v>6372200</v>
+        <v>6446100</v>
       </c>
       <c r="J48" s="3">
+        <v>6751400</v>
+      </c>
+      <c r="K48" s="3">
         <v>6317900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5942400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6174500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5851600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5836700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6043400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6152900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5993200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6007500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6325100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6898700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>7146100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7436500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7400100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7454200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7461400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7167800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7111300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>6849300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6694400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6941200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6903500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6874400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6023000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6087900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>5725600</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>3198200</v>
+        <v>2857100</v>
       </c>
       <c r="E49" s="3">
-        <v>3044500</v>
+        <v>2800100</v>
       </c>
       <c r="F49" s="3">
-        <v>2962600</v>
+        <v>2834900</v>
       </c>
       <c r="G49" s="3">
-        <v>2828700</v>
+        <v>2960200</v>
       </c>
       <c r="H49" s="3">
-        <v>2806000</v>
+        <v>2667400</v>
       </c>
       <c r="I49" s="3">
-        <v>2657900</v>
+        <v>2733400</v>
       </c>
       <c r="J49" s="3">
+        <v>2816100</v>
+      </c>
+      <c r="K49" s="3">
         <v>2643100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2594800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2585000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2367900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2330800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2406100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2479900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2408200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2370200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2505800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2768200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2815500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3096100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3079300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2972100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3155200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3161900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3289100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3137100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2975000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3245200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3273300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3281300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>897200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>891700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>852900</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4614,8 +4733,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4715,109 +4837,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>1029400</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1068800</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F52" s="3">
-        <v>1082100</v>
+        <v>300</v>
       </c>
       <c r="G52" s="3">
-        <v>1099400</v>
+        <v>300</v>
       </c>
       <c r="H52" s="3">
-        <v>987500</v>
+        <v>500</v>
       </c>
       <c r="I52" s="3">
-        <v>957500</v>
+        <v>1000</v>
       </c>
       <c r="J52" s="3">
+        <v>800</v>
+      </c>
+      <c r="K52" s="3">
         <v>919000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>935600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>908800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>877800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>818200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>849300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>827500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>823800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>807200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>875700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>926900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>966700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>877800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>911400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>893200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>993200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>881500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>914100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>875400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>911800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>925500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>867000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>685400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>397300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>395700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>472700</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4917,109 +5045,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>42868800</v>
+        <v>38799800</v>
       </c>
       <c r="E54" s="3">
-        <v>40020300</v>
+        <v>37533500</v>
       </c>
       <c r="F54" s="3">
-        <v>38122900</v>
+        <v>37265900</v>
       </c>
       <c r="G54" s="3">
-        <v>38369000</v>
+        <v>38091300</v>
       </c>
       <c r="H54" s="3">
-        <v>37616400</v>
+        <v>36181100</v>
       </c>
       <c r="I54" s="3">
-        <v>34618500</v>
+        <v>36643400</v>
       </c>
       <c r="J54" s="3">
+        <v>36678700</v>
+      </c>
+      <c r="K54" s="3">
         <v>33963900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>31916200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>32453700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>28867500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>27668100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27783800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>27859400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>26834500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26336600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>28001000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>31227300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>32189000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>33973200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33429200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33814600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>34963300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>33127800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>33271700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>31641700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>30487700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>31278300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>30105200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>29429900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>23563000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>23750700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>21217100</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5055,8 +5189,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5092,614 +5227,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2322200</v>
+        <v>2197800</v>
       </c>
       <c r="E57" s="3">
-        <v>2274200</v>
+        <v>2033200</v>
       </c>
       <c r="F57" s="3">
-        <v>2285400</v>
+        <v>2117700</v>
       </c>
       <c r="G57" s="3">
-        <v>2475600</v>
+        <v>2283500</v>
       </c>
       <c r="H57" s="3">
-        <v>2608300</v>
+        <v>2334400</v>
       </c>
       <c r="I57" s="3">
-        <v>2572800</v>
+        <v>2540800</v>
       </c>
       <c r="J57" s="3">
+        <v>2725900</v>
+      </c>
+      <c r="K57" s="3">
         <v>2400400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2272000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2341700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2250800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1971700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1939100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1908900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1831500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1597300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1511700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1742400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1939600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2091700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2278800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2338800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2565400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2413100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2557500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2485200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2744100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2742000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2594600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2526300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2129800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>1891800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1680000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5957500</v>
+        <v>5145100</v>
       </c>
       <c r="E58" s="3">
-        <v>4124900</v>
+        <v>5344300</v>
       </c>
       <c r="F58" s="3">
-        <v>4469000</v>
+        <v>3976200</v>
       </c>
       <c r="G58" s="3">
-        <v>3532400</v>
+        <v>4600800</v>
       </c>
       <c r="H58" s="3">
-        <v>4327900</v>
+        <v>3474900</v>
       </c>
       <c r="I58" s="3">
-        <v>3461800</v>
+        <v>4366200</v>
       </c>
       <c r="J58" s="3">
+        <v>3813300</v>
+      </c>
+      <c r="K58" s="3">
         <v>4369600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4638700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4641200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3442000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3599600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3247400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2968400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2619500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2928500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3409100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>5190700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5308400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5845400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5004000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4708300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4403400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4835900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3995900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4127800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>2982300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3226400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2743000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>4866100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1932300</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2705700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1856900</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4590900</v>
+        <v>4076100</v>
       </c>
       <c r="E59" s="3">
-        <v>4436900</v>
+        <v>3891200</v>
       </c>
       <c r="F59" s="3">
-        <v>4052200</v>
+        <v>2772300</v>
       </c>
       <c r="G59" s="3">
-        <v>4225100</v>
+        <v>3913300</v>
       </c>
       <c r="H59" s="3">
-        <v>4124400</v>
+        <v>3840200</v>
       </c>
       <c r="I59" s="3">
-        <v>3704300</v>
+        <v>3867500</v>
       </c>
       <c r="J59" s="3">
+        <v>2613000</v>
+      </c>
+      <c r="K59" s="3">
         <v>3478900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3172600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3188000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3098700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2715800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2697500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2611000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2588500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2524800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2635500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2809300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2959500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3169700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3262900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3290300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3430500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3011500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3336600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3020600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3220100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3131200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>2985200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2675700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2148500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1977100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1932900</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>12870600</v>
+        <v>11419000</v>
       </c>
       <c r="E60" s="3">
-        <v>10836000</v>
+        <v>11268800</v>
       </c>
       <c r="F60" s="3">
-        <v>10806500</v>
+        <v>10090200</v>
       </c>
       <c r="G60" s="3">
-        <v>10233100</v>
+        <v>10797500</v>
       </c>
       <c r="H60" s="3">
-        <v>11060600</v>
+        <v>9649600</v>
       </c>
       <c r="I60" s="3">
-        <v>9738800</v>
+        <v>10774500</v>
       </c>
       <c r="J60" s="3">
+        <v>10318400</v>
+      </c>
+      <c r="K60" s="3">
         <v>10248800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10083400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10170900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8791500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8287000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>7884100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7488300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7039400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7050600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7556300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>9742300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>10207500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>11106800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10545700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10337400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10399400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10260500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>9890100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9633600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>8946500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9099600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8322800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>10068000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>6210600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6574700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5469800</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4187600</v>
+        <v>4100600</v>
       </c>
       <c r="E61" s="3">
-        <v>4390600</v>
+        <v>3992200</v>
       </c>
       <c r="F61" s="3">
-        <v>4103600</v>
+        <v>4441300</v>
       </c>
       <c r="G61" s="3">
-        <v>4650600</v>
+        <v>4454300</v>
       </c>
       <c r="H61" s="3">
-        <v>4235700</v>
+        <v>4727900</v>
       </c>
       <c r="I61" s="3">
-        <v>4019900</v>
+        <v>4457000</v>
       </c>
       <c r="J61" s="3">
+        <v>4600800</v>
+      </c>
+      <c r="K61" s="3">
         <v>3890000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2829400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3203300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2848600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2748000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2986100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3685700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3832300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3788600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>4116400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3747600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3610700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3704600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3739100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4491900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4540600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4285500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4526300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4365800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4345500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4771500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4645600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2829700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1692900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1742600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1577700</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>2143400</v>
+        <v>1092200</v>
       </c>
       <c r="E62" s="3">
-        <v>2084700</v>
+        <v>1051000</v>
       </c>
       <c r="F62" s="3">
-        <v>1985600</v>
+        <v>2500</v>
       </c>
       <c r="G62" s="3">
-        <v>2065900</v>
+        <v>1200</v>
       </c>
       <c r="H62" s="3">
-        <v>1965600</v>
+        <v>5100</v>
       </c>
       <c r="I62" s="3">
-        <v>1846300</v>
+        <v>3400</v>
       </c>
       <c r="J62" s="3">
+        <v>1000</v>
+      </c>
+      <c r="K62" s="3">
         <v>1803200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1699100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1735200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1581700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1611800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1672700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1756800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1697600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1628100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1786600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1929800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>2017500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1936900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1955600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1946800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1736800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1588900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1545500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1485000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1433600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1437400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1448700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1400700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1037100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1041600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>965200</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5799,8 +5953,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5900,8 +6057,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6001,109 +6161,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>20437900</v>
+        <v>17155500</v>
       </c>
       <c r="E66" s="3">
-        <v>18481900</v>
+        <v>16811800</v>
       </c>
       <c r="F66" s="3">
-        <v>17985000</v>
+        <v>16119800</v>
       </c>
       <c r="G66" s="3">
-        <v>18025700</v>
+        <v>16881700</v>
       </c>
       <c r="H66" s="3">
-        <v>18312200</v>
+        <v>15983100</v>
       </c>
       <c r="I66" s="3">
-        <v>16587100</v>
+        <v>16815400</v>
       </c>
       <c r="J66" s="3">
+        <v>16533700</v>
+      </c>
+      <c r="K66" s="3">
         <v>16869600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15474000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15972600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>14043700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>13489900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13380200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13660300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13276300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13146300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>14153500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>16184500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16581100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>17541800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16997900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17543800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17515500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16912800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16751000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16218100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>15440300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16046200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>15109600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>14968700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>9577900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9984500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>8556800</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6139,8 +6305,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6240,8 +6407,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6341,8 +6511,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6442,8 +6615,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6543,109 +6719,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>17294400</v>
+        <v>17644500</v>
       </c>
       <c r="E72" s="3">
-        <v>17153600</v>
+        <v>15142000</v>
       </c>
       <c r="F72" s="3">
-        <v>16520600</v>
+        <v>15973000</v>
       </c>
       <c r="G72" s="3">
-        <v>16303500</v>
+        <v>16506900</v>
       </c>
       <c r="H72" s="3">
-        <v>15592600</v>
+        <v>15373800</v>
       </c>
       <c r="I72" s="3">
-        <v>15359400</v>
+        <v>15189300</v>
       </c>
       <c r="J72" s="3">
+        <v>16273500</v>
+      </c>
+      <c r="K72" s="3">
         <v>14688600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13142900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13331000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>12950700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12922300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>13385000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>13260900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12749900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12886400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>13604200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>14720100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15384800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15739500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15939800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15497700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>16338300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>15366800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>15023600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>14132800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>13901600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13527900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13353100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>12762200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>12442100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>12042600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>12011900</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6745,8 +6927,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6846,8 +7031,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6947,109 +7135,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>22430900</v>
+        <v>20490500</v>
       </c>
       <c r="E76" s="3">
-        <v>21538300</v>
+        <v>19639200</v>
       </c>
       <c r="F76" s="3">
-        <v>20137900</v>
+        <v>20056000</v>
       </c>
       <c r="G76" s="3">
-        <v>20343300</v>
+        <v>20121200</v>
       </c>
       <c r="H76" s="3">
-        <v>19304200</v>
+        <v>19183300</v>
       </c>
       <c r="I76" s="3">
-        <v>18031500</v>
+        <v>18804800</v>
       </c>
       <c r="J76" s="3">
+        <v>19104500</v>
+      </c>
+      <c r="K76" s="3">
         <v>17094300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>16442200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16481100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>14823900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14178100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14403600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14199100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>13558200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13190300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13847500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15042800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15607800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16431500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16431400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16270800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>17447700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16215000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16520700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>15423500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15047400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15232100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>14995700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14461200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>13985100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13766200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>12660300</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7149,215 +7343,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>779100</v>
-      </c>
-      <c r="E81" s="3">
-        <v>633000</v>
-      </c>
-      <c r="F81" s="3">
-        <v>700900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>710900</v>
-      </c>
-      <c r="H81" s="3">
-        <v>748500</v>
-      </c>
-      <c r="I81" s="3">
-        <v>670900</v>
-      </c>
-      <c r="J81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K81" s="3">
         <v>492300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>523900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>542300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>461000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>428400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>376700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>300600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>285500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>210200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>163900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>138600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>163700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>411800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>391400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>434900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>694700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>555200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>579800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>572400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>373800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>481900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>590900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>329000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>399600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>273300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7393,109 +7596,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>290200</v>
+        <v>211300</v>
       </c>
       <c r="E83" s="3">
-        <v>279700</v>
+        <v>208200</v>
       </c>
       <c r="F83" s="3">
-        <v>291100</v>
+        <v>208000</v>
       </c>
       <c r="G83" s="3">
-        <v>276600</v>
+        <v>236900</v>
       </c>
       <c r="H83" s="3">
-        <v>266200</v>
+        <v>204000</v>
       </c>
       <c r="I83" s="3">
-        <v>270600</v>
+        <v>216600</v>
       </c>
       <c r="J83" s="3">
+        <v>229000</v>
+      </c>
+      <c r="K83" s="3">
         <v>273400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>235400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>243800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>247600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>215000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>241600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>251700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>247200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>245900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>256200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>271400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>302800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>296400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>294100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>299300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>320500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>309400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>301200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>299200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>316900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>301900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>295000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>296800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>238900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>226700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>222400</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7595,8 +7802,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7696,8 +7906,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7797,8 +8010,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7898,8 +8114,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7999,109 +8218,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>596000</v>
+        <v>933500</v>
       </c>
       <c r="E89" s="3">
-        <v>1109700</v>
+        <v>521800</v>
       </c>
       <c r="F89" s="3">
-        <v>647300</v>
+        <v>1033300</v>
       </c>
       <c r="G89" s="3">
-        <v>723400</v>
+        <v>646800</v>
       </c>
       <c r="H89" s="3">
-        <v>606600</v>
+        <v>682100</v>
       </c>
       <c r="I89" s="3">
-        <v>876200</v>
+        <v>590900</v>
       </c>
       <c r="J89" s="3">
+        <v>928300</v>
+      </c>
+      <c r="K89" s="3">
         <v>408500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>177900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-15800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>770900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>188500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>669300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>474800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>813600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>636600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>759600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>469400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1208900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>202300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>715400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>530400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>982200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>259100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>677800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>603600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>357400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>376500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>971600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>448000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>444400</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8137,109 +8362,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-46288000</v>
+        <v>-399300</v>
       </c>
       <c r="E91" s="3">
-        <v>-50938000</v>
+        <v>-264500</v>
       </c>
       <c r="F91" s="3">
-        <v>-63292000</v>
+        <v>-336800</v>
       </c>
       <c r="G91" s="3">
-        <v>-48195000</v>
+        <v>-449000</v>
       </c>
       <c r="H91" s="3">
-        <v>-40522000</v>
+        <v>-322700</v>
       </c>
       <c r="I91" s="3">
-        <v>-48621000</v>
+        <v>-280300</v>
       </c>
       <c r="J91" s="3">
+        <v>-365800</v>
+      </c>
+      <c r="K91" s="3">
         <v>-48655000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-49879000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-36378000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-39135000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-41538000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-44307000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-279100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-314200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-380900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-374000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-317900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-397700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-434800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-439600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-403000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-453500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-552400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-411600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-382200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-288700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-389600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-331300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-390900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-378000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-298900</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8339,8 +8568,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8440,109 +8672,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-290900</v>
+        <v>-442200</v>
       </c>
       <c r="E94" s="3">
-        <v>-310900</v>
+        <v>-254700</v>
       </c>
       <c r="F94" s="3">
-        <v>-562500</v>
+        <v>-289500</v>
       </c>
       <c r="G94" s="3">
-        <v>-298600</v>
+        <v>-562000</v>
       </c>
       <c r="H94" s="3">
-        <v>-279400</v>
+        <v>-281600</v>
       </c>
       <c r="I94" s="3">
-        <v>-274100</v>
+        <v>-272200</v>
       </c>
       <c r="J94" s="3">
+        <v>-290500</v>
+      </c>
+      <c r="K94" s="3">
         <v>-323700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-331000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-225400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-262000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-239100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-285800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-218000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-258800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-341100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-347300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-302300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-366600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-388200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-542900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-436300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-432300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-524300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-408300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-388400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-520100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-228800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>103500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2769300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-347600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-233600</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8578,109 +8816,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>-638300</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F96" s="3">
-        <v>-483800</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>483400</v>
       </c>
       <c r="H96" s="3">
-        <v>-503700</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>490700</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>-429800</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-357000</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-259900</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-257100</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-124700</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-314400</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-473400</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-510400</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-454600</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-411800</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-307100</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-247400</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-242700</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8780,8 +9022,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8881,8 +9126,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8982,307 +9230,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>85100</v>
+        <v>-756600</v>
       </c>
       <c r="E100" s="3">
-        <v>-420500</v>
+        <v>74500</v>
       </c>
       <c r="F100" s="3">
-        <v>119300</v>
+        <v>-391600</v>
       </c>
       <c r="G100" s="3">
-        <v>-609300</v>
+        <v>119200</v>
       </c>
       <c r="H100" s="3">
-        <v>44000</v>
+        <v>-574500</v>
       </c>
       <c r="I100" s="3">
-        <v>-906700</v>
+        <v>42900</v>
       </c>
       <c r="J100" s="3">
+        <v>-960600</v>
+      </c>
+      <c r="K100" s="3">
         <v>109900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-175500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>492900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-247600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>17200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-111700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-320400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-371100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-442100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-584000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-102700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-261700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>363600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-431900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>305300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-522600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>409300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-408800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>466900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-341500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>246200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-372500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2673000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-763500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>417200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-385800</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>97300</v>
+        <v>-1300</v>
       </c>
       <c r="E101" s="3">
-        <v>45800</v>
+        <v>8400</v>
       </c>
       <c r="F101" s="3">
-        <v>-18300</v>
+        <v>-9400</v>
       </c>
       <c r="G101" s="3">
-        <v>-1400</v>
+        <v>-107000</v>
       </c>
       <c r="H101" s="3">
-        <v>8600</v>
+        <v>-77500</v>
       </c>
       <c r="I101" s="3">
-        <v>-8900</v>
+        <v>227000</v>
       </c>
       <c r="J101" s="3">
+        <v>40900</v>
+      </c>
+      <c r="K101" s="3">
         <v>-100200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-71500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>207900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>33000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>21100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>10400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-8200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>19000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>10900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-17000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>10400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-20800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>12800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-24800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>62300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-40600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-66000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>69000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>13700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>8900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>13800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-66000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>487500</v>
+        <v>-434900</v>
       </c>
       <c r="E102" s="3">
-        <v>424000</v>
+        <v>426800</v>
       </c>
       <c r="F102" s="3">
-        <v>185800</v>
+        <v>394800</v>
       </c>
       <c r="G102" s="3">
-        <v>-185900</v>
+        <v>185600</v>
       </c>
       <c r="H102" s="3">
-        <v>379800</v>
+        <v>-175300</v>
       </c>
       <c r="I102" s="3">
-        <v>-313500</v>
+        <v>370000</v>
       </c>
       <c r="J102" s="3">
+        <v>-332200</v>
+      </c>
+      <c r="K102" s="3">
         <v>94500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-400100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>459600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>294300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-12300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>275900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-53300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>175400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-127500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-160800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>63900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>563600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>188100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-280200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>412300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>2500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>206500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-179800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>11900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>35100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>97400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>278000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-125700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>416200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-166700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KMTUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KMTUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>KMTUY</t>
   </si>
@@ -656,152 +656,155 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -826,86 +829,89 @@
       <c r="J8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="3">
         <v>6535500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5454400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5148100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5230000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4968900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4637000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4764800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4794300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4072500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3887100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3913000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5439500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5593100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5548200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5585500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6790800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6613400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6242700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>5872700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6285600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5847500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5403600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5073300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5111600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3819400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3608800</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -930,86 +936,89 @@
       <c r="J9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K9" s="3">
+      <c r="K9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L9" s="3">
         <v>4573500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>3841100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3676000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3769800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3589200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3298400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3491800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3540700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2999800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2844100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2855200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3983000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4023200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3933000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3914600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4734300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4644500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4266600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4011000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4364100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4072000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3892100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3635600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3643900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2714800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2572600</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1034,86 +1043,89 @@
       <c r="J10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="3">
+      <c r="K10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="3">
         <v>1962000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1613400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1472100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1460200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1379700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1338600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1272900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1253500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1072700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1043000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1057800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1456500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1569900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1615200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1670900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2056500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1968800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1976100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1861700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1921400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1775500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1511500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1437700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1467700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1104600</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1036300</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1150,8 +1162,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1254,8 +1267,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1358,8 +1374,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1393,24 +1412,24 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3">
         <v>9100</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3">
         <v>17000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1426,8 +1445,8 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1435,8 +1454,8 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1453,17 +1472,20 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3">
         <v>15500</v>
       </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1488,8 +1510,8 @@
       <c r="J15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1566,8 +1588,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1601,8 +1626,9 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1627,86 +1653,89 @@
       <c r="J17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="3">
         <v>5577300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>4701100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4517500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4610800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4367900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4099600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4310900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4370300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>3726600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3626700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3683400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>5061800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4993300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4930400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4900700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>5810800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5711600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5274100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4999600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5531700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5170900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4865900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4606000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4516700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3304300</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1731,86 +1760,89 @@
       <c r="J18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="3">
         <v>958300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>753300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>630600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>619200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>601000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>537400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>453900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>423900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>345900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>260400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>229600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>377800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>599900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>617800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>684800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>979900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>901800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>968600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>873100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>753900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>676500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>537700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>467400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>594900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>380500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>304600</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1847,8 +1879,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1873,86 +1906,89 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>-84700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>21900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>159000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>67100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>25400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>23800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>19600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>20000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>5800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>46200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-35100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>15000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>37200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-35000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>12000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>21000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-17900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>14300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>372500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-11900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>36500</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1977,86 +2013,89 @@
       <c r="J21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="3">
         <v>1146900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1010600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1033400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>933900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>841300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>802800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>725200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>691100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>597700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>517900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>547300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>645500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>911300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>916800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>973100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>1337600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1176100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1281800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1193400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1052800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>992600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1205300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>763800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>821800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>643700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>539800</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2081,86 +2120,89 @@
       <c r="J22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K22" s="3">
+      <c r="K22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="3">
         <v>78000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>39700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>31500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>23100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>20100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>21800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>22700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>23200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>27800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>32800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>50200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>52700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>59300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>60900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>61000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>59900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>55600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>49300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>44700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>46900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>42200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>32300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>22400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>16300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2185,86 +2227,89 @@
       <c r="J23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L23" s="3">
         <v>795500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>735500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>758100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>665700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>603200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>541100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>451700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>421300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>328600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>234000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>243100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>292400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>562200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>563400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>612900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>956100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>806800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>925000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>844800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>691300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>643900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>868000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>434800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>560600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>400600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>300600</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2289,86 +2334,89 @@
       <c r="J24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="3">
         <v>272300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>187300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>198900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>204400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>158600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>149000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>132500</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>113200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>101500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>56700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>83700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>114500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>129800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>163500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>163300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>239900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>227500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>274200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>254700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>293100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>142000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>259900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>85900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>135000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>124400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>105900</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2471,8 +2519,11 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2497,86 +2548,89 @@
       <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="3">
         <v>523200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>548200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>559200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>461200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>444600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>392100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>319200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>308000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>227100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>177200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>159300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>177900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>432300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>399900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>449600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>716200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>579400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>650800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>590100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>398100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>501800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>608200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>348900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>425700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>276200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>194700</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2601,86 +2655,89 @@
       <c r="J27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="3">
         <v>492300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>523900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>542300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>461000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>428400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>376700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>300600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>285500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>210200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>163900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>138600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>163700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>411800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>391400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>434900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>694700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>555200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>579800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>572400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>373800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>481900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>590900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>329000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>399600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>273300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2783,8 +2840,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2809,8 +2869,8 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2887,8 +2947,11 @@
       <c r="AJ29" s="3">
         <v>0</v>
       </c>
+      <c r="AK29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2991,8 +3054,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3095,8 +3161,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3121,86 +3190,89 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>84700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-21900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-159000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-67100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-25400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-23800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-19600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-20000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-5800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-46200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>35100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-15000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>11000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-37200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>35000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>17900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-14300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-372500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>11900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-36500</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-12800</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3225,86 +3297,89 @@
       <c r="J33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="3">
         <v>492300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>523900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>542300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>461000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>428400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>376700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>300600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>285500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>210200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>163900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>138600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>163700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>411800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>391400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>434900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>694700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>555200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>579800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>572400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>373800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>481900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>590900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>329000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>399600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>273300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3407,8 +3482,11 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3433,195 +3511,201 @@
       <c r="J35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="3">
         <v>492300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>523900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>542300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>461000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>428400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>376700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>300600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>285500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>210200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>163900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>138600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>163700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>411800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>391400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>434900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>694700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>555200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>579800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>572400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>373800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>481900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>590900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>329000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>399600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>273300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3658,8 +3742,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3696,112 +3781,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2586500</v>
+      </c>
+      <c r="E41" s="3">
         <v>2858600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2933100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2665600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2436500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2124300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2375600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2181300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2372400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2046900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2585100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2094000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1862000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1975600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1732900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1723800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1601600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1837300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2194200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2199600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1689900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1514000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1792800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1449300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1421600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1196300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1343400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1327600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1516900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1482200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1381200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1083800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1209600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>789900</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3812,38 +3901,38 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>25000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>22700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>33500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>36600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>33800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>14300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>4900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>7300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>8700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>15600</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -3904,736 +3993,760 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>7889900</v>
+      </c>
+      <c r="E43" s="3">
         <v>8090200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7925100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8399600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7993700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7485100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7882300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8383000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>6885200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6610100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6705900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6338400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5855300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5745200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5791100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5818700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5049300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5218600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5668600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>6558100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>7002300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6799600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7109800</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8093400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7464600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7593000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7131300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7166100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>6920900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>6481500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5949400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5492900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5117000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>4460600</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9957900</v>
+      </c>
+      <c r="E44" s="3">
         <v>10168000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>9924600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9511700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>10355100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>9985900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9645900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9231700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8832600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8134700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7917100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6560400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6192300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6123000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6020100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5628400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6025000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6535000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>7393100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7094800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>8199300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>8217800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>8015200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>8048900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>7793600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>7851600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>7246200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>6601800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>6847600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>6441600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>6211000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>4735700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5252300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4645600</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1532900</v>
+      </c>
+      <c r="E45" s="3">
         <v>1625000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1521800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1192600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1507000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1629000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1678900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1416200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1407800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1276600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1262900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1075800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1124300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>991000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1023700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>933200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>962600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1023800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1269500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1298700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1368900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1225300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1322900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1330200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1291000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1205900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1188900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1154700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1105700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1052800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1084600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1278800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1242800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1155000</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21967200</v>
+      </c>
+      <c r="E46" s="3">
         <v>22741800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22304700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>21911300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>22314900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>21257800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21619200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21338200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19512400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>18073000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18478300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>16077300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>15049600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14834700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14567700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14104100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>13638400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>14614700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>16525500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17151200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>18260400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17756700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>18240800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>18921700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>17970800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>17846800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>16909800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>16250200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>16391200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>15458100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>14626200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>12591200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>12821700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>11051100</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6618500</v>
+      </c>
+      <c r="E47" s="3">
         <v>6518300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6141100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>543600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>566700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>481600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>495500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>506000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4571500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4370400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4307100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3692900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3632900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3650400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3831400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3505200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3513400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3679600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4108100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4109500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4302400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4281700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4254400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4431700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>3945800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4110500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3870100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3656300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3775100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3603400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3962700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3654400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>3553700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>3114700</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6325000</v>
+      </c>
+      <c r="E48" s="3">
         <v>6682600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6287500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6461200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6736200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6355000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6446100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6751400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6317900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5942400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6174500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5851600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5836700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>6043400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6152900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5993200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6007500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6325100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6898700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>7146100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7436500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7400100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7454200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7461400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7167800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7111300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>6849300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6694400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6941200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6903500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6874400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6023000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>6087900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>5725600</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2738700</v>
+      </c>
+      <c r="E49" s="3">
         <v>2857100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2800100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2834900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2960200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2667400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2733400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2816100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2643100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2594800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2585000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2367900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2330800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2406100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2479900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2408200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2370200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2505800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2768200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2815500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3096100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3079300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>2972100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3155200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3161900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3289100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3137100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>2975000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3245200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3273300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3281300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>897200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>891700</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>852900</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4736,8 +4849,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4840,8 +4956,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4851,101 +4970,104 @@
       <c r="E52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F52" s="3">
-        <v>300</v>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G52" s="3">
         <v>300</v>
       </c>
       <c r="H52" s="3">
+        <v>300</v>
+      </c>
+      <c r="I52" s="3">
         <v>500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>919000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>935600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>908800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>877800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>818200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>849300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>827500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>823800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>807200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>875700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>926900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>966700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>877800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>911400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>893200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>993200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>881500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>914100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>875400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>911800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>925500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>867000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>685400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>397300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>395700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>472700</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5048,112 +5170,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>37649300</v>
+      </c>
+      <c r="E54" s="3">
         <v>38799800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>37533500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>37265900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>38091300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>36181100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36643400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36678700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33963900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>31916200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>32453700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>28867500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>27668100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>27783800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>27859400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>26834500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26336600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>28001000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>31227300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>32189000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>33973200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33429200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33814600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>34963300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>33127800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>33271700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>31641700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>30487700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>31278300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>30105200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>29429900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>23563000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>23750700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>21217100</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5190,8 +5318,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5228,632 +5357,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2009600</v>
+      </c>
+      <c r="E57" s="3">
         <v>2197800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2033200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2117700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2283500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2334400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2540800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2725900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2400400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2272000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2341700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2250800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1971700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1939100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1908900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1831500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1597300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1511700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1742400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1939600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2091700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2278800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2338800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2565400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2413100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2557500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2485200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2744100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2742000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2594600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2526300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2129800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>1891800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1680000</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5519900</v>
+      </c>
+      <c r="E58" s="3">
         <v>5145100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5344300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3976200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4600800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3474900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4366200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3813300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4369600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4638700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4641200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3442000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3599600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3247400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2968400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2619500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2928500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>3409100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5190700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5308400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5845400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5004000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4708300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4403400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4835900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3995900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4127800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>2982300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>3226400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2743000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>4866100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1932300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>2705700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1856900</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3973300</v>
+      </c>
+      <c r="E59" s="3">
         <v>4076100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>3891200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2772300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3913300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3840200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3867500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2613000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3478900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3172600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3188000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3098700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2715800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2697500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2611000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2588500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2524800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2635500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2809300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2959500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>3169700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3262900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3290300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3430500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3011500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3336600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3020600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3220100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3131200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>2985200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2675700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2148500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1977100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1932900</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11502800</v>
+      </c>
+      <c r="E60" s="3">
         <v>11419000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11268800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>10090200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10797500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>9649600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10774500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10318400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10248800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10083400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10170900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8791500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8287000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>7884100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7488300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7039400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7050600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7556300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>9742300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>10207500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>11106800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10545700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10337400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10399400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>10260500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>9890100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9633600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>8946500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9099600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8322800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>10068000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>6210600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6574700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5469800</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3603500</v>
+      </c>
+      <c r="E61" s="3">
         <v>4100600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3992200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4441300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4454300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4727900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4457000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4600800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3890000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2829400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3203300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2848600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2748000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2986100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3685700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3832300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3788600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>4116400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3747600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3610700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3704600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3739100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4491900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4540600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4285500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4526300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4365800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4345500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4771500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4645600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2829700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1692900</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1742600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1577700</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1065500</v>
+      </c>
+      <c r="E62" s="3">
         <v>1092200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1051000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>5100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1803200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1699100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1735200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1581700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1611800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1672700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1756800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1697600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1628100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1786600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1929800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>2017500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1936900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1955600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1946800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1736800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1588900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1545500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1485000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1433600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1437400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1448700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1400700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1037100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1041600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>965200</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5956,8 +6104,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6060,8 +6211,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6164,112 +6318,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>16690100</v>
+      </c>
+      <c r="E66" s="3">
         <v>17155500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16811800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16119800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16881700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>15983100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16815400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16533700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16869600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15474000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15972600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>14043700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>13489900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13380200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13660300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13276300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13146300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>14153500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>16184500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16581100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>17541800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16997900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17543800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17515500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>16912800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16751000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16218100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>15440300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>16046200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>15109600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>14968700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>9577900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>9984500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>8556800</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6306,8 +6466,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6410,8 +6571,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6514,8 +6678,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6618,8 +6785,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6722,112 +6892,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>15852300</v>
+      </c>
+      <c r="E72" s="3">
         <v>17644500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15142000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15973000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>16506900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>15373800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15189300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>16273500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>14688600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13142900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>13331000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12950700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12922300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>13385000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>13260900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>12749900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>12886400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>13604200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>14720100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15384800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15739500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15939800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15497700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>16338300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>15366800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>15023600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>14132800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>13901600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13527900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13353100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>12762200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>12442100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>12042600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>12011900</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6930,8 +7106,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7034,8 +7213,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7138,112 +7320,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19891900</v>
+      </c>
+      <c r="E76" s="3">
         <v>20490500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19639200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>20056000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20121200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>19183300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>18804800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19104500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>17094300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>16442200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16481100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14823900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14178100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14403600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14199100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>13558200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13190300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13847500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15042800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15607800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>16431500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16431400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16270800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>17447700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16215000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>16520700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>15423500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15047400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15232100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>14995700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14461200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>13985100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13766200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>12660300</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7346,117 +7534,123 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7481,86 +7675,89 @@
       <c r="J81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L81" s="3">
         <v>492300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>523900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>542300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>461000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>428400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>376700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>300600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>285500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>210200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>163900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>138600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>163700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>411800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>391400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>434900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>694700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>555200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>579800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>572400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>373800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>481900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>590900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>329000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>399600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>273300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7597,112 +7794,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>238400</v>
+      </c>
+      <c r="E83" s="3">
         <v>211300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>208200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>208000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>236900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>204000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>216600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>229000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>273400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>235400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>243800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>247600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>215000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>241600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>251700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>247200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>245900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>256200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>271400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>302800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>296400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>294100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>299300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>320500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>309400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>301200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>299200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>316900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>301900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>295000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>296800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>238900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>226700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>222400</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7805,8 +8006,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7909,8 +8113,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8013,8 +8220,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8117,8 +8327,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8221,112 +8434,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>603000</v>
+      </c>
+      <c r="E89" s="3">
         <v>933500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>521800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1033300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>646800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>682100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>590900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>928300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>408500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>177900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-15800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>770900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>188500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>669300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>474800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>813600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>636600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>759600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>469400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1208900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>202300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>715400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>530400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>982200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>259100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>677800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>603600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>3900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>357400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>376500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>971600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>448000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>444400</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8363,112 +8582,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-224300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-399300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-264500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-336800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-449000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-322700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-280300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-365800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-48655000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-49879000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-36378000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-39135000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-41538000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-44307000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-279100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-314200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-380900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-374000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-317900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-397700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-434800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-439600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-403000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-453500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-552400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-411600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-382200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-288700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-389600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-331300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-390900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-378000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-298900</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8571,8 +8794,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8675,112 +8901,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-329600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-442200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-254700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-289500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-562000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-281600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-272200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-290500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-323700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-331000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-225400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-262000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-239100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-285800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-218000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-258800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-341100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-347300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-302300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-366600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-388200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-542900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-436300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-432300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-524300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-408300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-388400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-520100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-228800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>103500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2769300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-347600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-233600</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8817,8 +9049,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8828,101 +9061,104 @@
       <c r="E96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F96" s="3">
-        <v>0</v>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G96" s="3">
+        <v>0</v>
+      </c>
+      <c r="H96" s="3">
         <v>483400</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>490700</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-429800</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-357000</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-259900</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-257100</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-124700</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-314400</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-473400</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-510400</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-454600</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-411800</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-307100</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-247400</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-242700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9025,8 +9261,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9129,8 +9368,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9233,316 +9475,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-357100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-756600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>74500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-391600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>119200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-574500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>42900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-960600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>109900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-175500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>492900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-247600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>17200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-111700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-320400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-371100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-442100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-584000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-102700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-261700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>363600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-431900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>305300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-522600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>409300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-408800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>466900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-341500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>246200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-372500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2673000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-763500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>417200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-385800</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>8400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-9400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-107000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-77500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>227000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>40900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-100200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-71500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>207900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>33000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>21100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>10400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-8200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>19000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>10900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-17000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>10400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-20800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>12800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-24800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>62300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-40600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-66000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>69000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>13700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>8900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>13800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-66000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-434900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>426800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>394800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>185600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-175300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>370000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-332200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>94500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-400100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>459600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>294300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>275900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-53300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>175400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-127500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-160800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>63900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>563600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>188100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-280200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>412300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>206500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-179800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>11900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>35100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>97400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>278000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-125700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>416200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-166700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KMTUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KMTUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
   <si>
     <t>KMTUY</t>
   </si>
@@ -656,155 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -832,86 +836,89 @@
       <c r="K8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>6535500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5454400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5148100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5230000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>4968900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4637000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4764800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4794300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4072500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>3887100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3913000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5439500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5593100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5548200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5585500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6790800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6613400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6242700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>5872700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>6285600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5847500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5403600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5073300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5111600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>3819400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3608800</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -939,86 +946,89 @@
       <c r="K9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M9" s="3">
         <v>4573500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>3841100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3676000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3769800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3589200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3298400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3491800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3540700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2999800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2844100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2855200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3983000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4023200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>3933000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3914600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>4734300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4644500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4266600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4011000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4364100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4072000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3892100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3635600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3643900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2714800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2572600</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1046,86 +1056,89 @@
       <c r="K10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3">
         <v>1962000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1613400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1472100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1460200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1379700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1338600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1272900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1253500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1072700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1043000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1057800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1456500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1569900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1615200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1670900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>2056500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1968800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1976100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1861700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1921400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1775500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1511500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1437700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1467700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1104600</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1036300</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1163,8 +1176,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1270,8 +1284,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1377,8 +1394,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1415,24 +1435,24 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>9100</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3">
         <v>17000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1448,8 +1468,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1457,8 +1477,8 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1475,17 +1495,20 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>15500</v>
       </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1513,8 +1536,8 @@
       <c r="K15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1591,8 +1614,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1627,8 +1653,9 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1656,86 +1683,89 @@
       <c r="K17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="3">
         <v>5577300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>4701100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4517500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4610800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4367900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4099600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4310900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4370300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>3726600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3626700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3683400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>5061800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4993300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4930400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4900700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>5810800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5711600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5274100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4999600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>5531700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5170900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4865900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4606000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4516700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3304300</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1763,86 +1793,89 @@
       <c r="K18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>958300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>753300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>630600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>619200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>601000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>537400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>453900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>423900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>345900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>260400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>229600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>377800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>599900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>617800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>684800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>979900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>901800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>968600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>873100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>753900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>676500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>537700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>467400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>594900</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>380500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>304600</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1880,8 +1913,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1909,86 +1943,89 @@
       <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>-84700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>21900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>159000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>67100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>25400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>23800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>19600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>20000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>5800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>46200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-35100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>15000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>4900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>37200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-35000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>12000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>21000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-17900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>14300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>372500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-11900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>36500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2016,86 +2053,89 @@
       <c r="K21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3">
         <v>1146900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1010600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1033400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>933900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>841300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>802800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>725200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>691100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>597700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>517900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>547300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>645500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>911300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>916800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>973100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>1337600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1176100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1281800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1193400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1052800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>992600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1205300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>763800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>821800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>643700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>539800</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2123,86 +2163,89 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>78000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>39700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>31500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>23100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>20100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>21800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>22700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>23200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>27800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>32800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>50200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>52700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>59300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>60900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>61000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>59900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>55600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>49300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>44700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>46900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>42200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>32300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>22400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>16300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2230,86 +2273,89 @@
       <c r="K23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M23" s="3">
         <v>795500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>735500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>758100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>665700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>603200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>541100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>451700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>421300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>328600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>234000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>243100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>292400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>562200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>563400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>612900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>956100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>806800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>925000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>844800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>691300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>643900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>868000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>434800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>560600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>400600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>300600</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2337,86 +2383,89 @@
       <c r="K24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="3">
+      <c r="L24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M24" s="3">
         <v>272300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>187300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>198900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>204400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>158600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>149000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>132500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>113200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>101500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>56700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>83700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>114500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>129800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>163500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>163300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>239900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>227500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>274200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>254700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>293100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>142000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>259900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>85900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>135000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>124400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>105900</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2522,8 +2571,11 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2551,86 +2603,89 @@
       <c r="K26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M26" s="3">
         <v>523200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>548200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>559200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>461200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>444600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>392100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>319200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>308000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>227100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>177200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>159300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>177900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>432300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>399900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>449600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>716200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>579400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>650800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>590100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>398100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>501800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>608200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>348900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>425700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>276200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>194700</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2658,86 +2713,89 @@
       <c r="K27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M27" s="3">
         <v>492300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>523900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>542300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>461000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>428400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>376700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>300600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>285500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>210200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>163900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>138600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>163700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>411800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>391400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>434900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>694700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>555200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>579800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>572400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>373800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>481900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>590900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>329000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>399600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>273300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2843,8 +2901,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2872,8 +2933,8 @@
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2950,8 +3011,11 @@
       <c r="AK29" s="3">
         <v>0</v>
       </c>
+      <c r="AL29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3057,8 +3121,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3164,8 +3231,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3193,86 +3263,89 @@
       <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>84700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-21900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-159000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-67100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-25400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-23800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-19600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-20000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-5800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-46200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>35100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>11000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-37200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>35000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>17900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-14300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-372500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>11900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-36500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-12800</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3300,86 +3373,89 @@
       <c r="K33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M33" s="3">
         <v>492300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>523900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>542300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>461000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>428400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>376700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>300600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>285500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>210200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>163900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>138600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>163700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>411800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>391400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>434900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>694700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>555200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>579800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>572400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>373800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>481900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>590900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>329000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>399600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>273300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3485,8 +3561,11 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3514,198 +3593,204 @@
       <c r="K35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M35" s="3">
         <v>492300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>523900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>542300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>461000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>428400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>376700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>300600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>285500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>210200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>163900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>138600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>163700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>411800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>391400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>434900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>694700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>555200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>579800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>572400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>373800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>481900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>590900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>329000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>399600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>273300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3743,8 +3828,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3782,115 +3868,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D41" s="3">
+      <c r="D41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="3">
         <v>2586500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2858600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2933100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2665600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2436500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2124300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2375600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2181300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2372400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2046900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2585100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2094000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1862000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1975600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1732900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1723800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1601600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1837300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2194200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2199600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1689900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1514000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1792800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1449300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1421600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1196300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1343400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1327600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1516900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1482200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1381200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1083800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1209600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>789900</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3904,38 +3994,38 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>25000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>22700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>33500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>36600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>33800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>14300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>8700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>15600</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -3996,757 +4086,781 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="3">
         <v>7889900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>8090200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7925100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8399600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7993700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7485100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7882300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8383000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6885200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6610100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6705900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6338400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5855300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5745200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5791100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5818700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5049300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5218600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5668600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6558100</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7002300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>6799600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>7109800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>8093400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>7464600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7593000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7131300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7166100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>6920900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>6481500</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>5949400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5492900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5117000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>4460600</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
         <v>9957900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>10168000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>9924600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>9511700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>10355100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>9985900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9645900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9231700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>8832600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8134700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7917100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6560400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6192300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6123000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6020100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>5628400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6025000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6535000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>7393100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>7094800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>8199300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>8217800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>8015200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>8048900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>7793600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>7851600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>7246200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>6601800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>6847600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>6441600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>6211000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4735700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>5252300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4645600</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3">
         <v>1532900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1625000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1521800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1192600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1507000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1629000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1678900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1416200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1407800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1276600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1262900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1075800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1124300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>991000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1023700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>933200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>962600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1023800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1269500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1298700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1368900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1225300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1322900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1330200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1291000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1205900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1188900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1154700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1105700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1052800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1084600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1278800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1242800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1155000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D46" s="3">
+      <c r="D46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="3">
         <v>21967200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>22741800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>22304700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>21911300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22314900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>21257800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21619200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21338200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>19512400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>18073000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18478300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>16077300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>15049600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>14834700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14567700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>14104100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>13638400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>14614700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>16525500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>17151200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>18260400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>17756700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>18240800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>18921700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>17970800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>17846800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>16909800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>16250200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>16391200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>15458100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>14626200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>12591200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>12821700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>11051100</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
         <v>6618500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6518300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>6141100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>543600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>566700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>481600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>495500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>506000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4571500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4370400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4307100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3692900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3632900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3650400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3831400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3505200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3513400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3679600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4108100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4109500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4302400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4281700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4254400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4431700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>3945800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>4110500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>3870100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3656300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3775100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3603400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3962700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>3654400</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>3553700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>3114700</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="3">
         <v>6325000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6682600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>6287500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>6461200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6736200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6355000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6446100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6751400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6317900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5942400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6174500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5851600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5836700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>6043400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6152900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5993200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>6007500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6325100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6898700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>7146100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7436500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7400100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7454200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7461400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7167800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7111300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>6849300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6694400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6941200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6903500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6874400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>6023000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>6087900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>5725600</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D49" s="3">
+      <c r="D49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="3">
         <v>2738700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2857100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2800100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2834900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2960200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2667400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2733400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2816100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2643100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2594800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2585000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2367900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2330800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2406100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2479900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2408200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2370200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2505800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2768200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2815500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3096100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3079300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>2972100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3155200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3161900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3289100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3137100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2975000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3245200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3273300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3281300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>897200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>891700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>852900</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4852,8 +4966,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4959,8 +5076,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4973,101 +5093,104 @@
       <c r="F52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G52" s="3">
-        <v>300</v>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H52" s="3">
         <v>300</v>
       </c>
       <c r="I52" s="3">
+        <v>300</v>
+      </c>
+      <c r="J52" s="3">
         <v>500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>919000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>935600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>908800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>877800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>818200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>849300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>827500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>823800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>807200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>875700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>926900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>966700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>877800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>911400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>893200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>993200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>881500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>914100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>875400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>911800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>925500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>867000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>685400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>397300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>395700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>472700</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5173,115 +5296,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D54" s="3">
+      <c r="D54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="3">
         <v>37649300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>38799800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>37533500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>37265900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>38091300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>36181100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36643400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36678700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>33963900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>31916200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>32453700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>28867500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>27668100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>27783800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>27859400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>26834500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26336600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>28001000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>31227300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>32189000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>33973200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33429200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>33814600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>34963300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>33127800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>33271700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>31641700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>30487700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>31278300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>30105200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>29429900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>23563000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>23750700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>21217100</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5319,8 +5448,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5358,650 +5488,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
+      <c r="D57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="3">
         <v>2009600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2197800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2033200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2117700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2283500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2334400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2540800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2725900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2400400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2272000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2341700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2250800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1971700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1939100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1908900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1831500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1597300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1511700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1742400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1939600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2091700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2278800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2338800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2565400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2413100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2557500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2485200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2744100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2742000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2594600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2526300</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2129800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>1891800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1680000</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
+      <c r="D58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="3">
         <v>5519900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5145100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5344300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3976200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4600800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3474900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4366200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3813300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4369600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4638700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4641200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3442000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3599600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3247400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>2968400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2619500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2928500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3409100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5190700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5308400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5845400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5004000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>4708300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4403400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4835900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3995900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4127800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2982300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3226400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>2743000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>4866100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1932300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>2705700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1856900</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
+      <c r="D59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="3">
         <v>3973300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>4076100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>3891200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>2772300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3913300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3840200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3867500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2613000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3478900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3172600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3188000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3098700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2715800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2697500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2611000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2588500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2524800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2635500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2809300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2959500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>3169700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3262900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3290300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3430500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3011500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3336600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3020600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3220100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3131200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>2985200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2675700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2148500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1977100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1932900</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
+      <c r="D60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="3">
         <v>11502800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>11419000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>11268800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>10090200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10797500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9649600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>10774500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10318400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10248800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10083400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10170900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8791500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8287000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>7884100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7488300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7039400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7050600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7556300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>9742300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>10207500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>11106800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>10545700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10337400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>10399400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>10260500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>9890100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9633600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>8946500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>9099600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>8322800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>10068000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>6210600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6574700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>5469800</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3">
         <v>3603500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4100600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3992200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4441300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4454300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4727900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4457000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4600800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3890000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2829400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3203300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2848600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2748000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2986100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3685700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3832300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3788600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>4116400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3747600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3610700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3704600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3739100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4491900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4540600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4285500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4526300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4365800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4345500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4771500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4645600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2829700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1692900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1742600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1577700</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="3">
         <v>1065500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1092200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1051000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>3400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1803200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1699100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1735200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1581700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1611800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1672700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1756800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1697600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1628100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1786600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1929800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>2017500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1936900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1955600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1946800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1736800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1588900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1545500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1485000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1433600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1437400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1448700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1400700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1037100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1041600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>965200</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6107,8 +6256,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6214,8 +6366,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6321,115 +6476,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D66" s="3">
+      <c r="D66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="3">
         <v>16690100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>17155500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16811800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>16119800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>16881700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>15983100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16815400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16533700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16869600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>15474000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15972600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>14043700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>13489900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13380200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13660300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13276300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13146300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>14153500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>16184500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16581100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>17541800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>16997900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>17543800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>17515500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>16912800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16751000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16218100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>15440300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>16046200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>15109600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>14968700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>9577900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>9984500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>8556800</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6467,8 +6628,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6574,8 +6736,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6681,8 +6846,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6788,8 +6956,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6895,115 +7066,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>15852300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17644500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15142000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15973000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>16506900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>15373800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15189300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>16273500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>14688600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>13142900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13331000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12950700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12922300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>13385000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>13260900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>12749900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12886400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>13604200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>14720100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15384800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15739500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15939800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>15497700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>16338300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>15366800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>15023600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>14132800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>13901600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13527900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13353100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>12762200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>12442100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>12042600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>12011900</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7109,8 +7286,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7216,8 +7396,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7323,115 +7506,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="3">
         <v>19891900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>20490500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>19639200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>20056000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>20121200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>19183300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>18804800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19104500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>17094300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>16442200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16481100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14823900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14178100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14403600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14199100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>13558200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13190300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13847500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15042800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15607800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>16431500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16431400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16270800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17447700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>16215000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>16520700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>15423500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15047400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>15232100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>14995700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14461200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>13985100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>13766200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>12660300</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7537,120 +7726,126 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7678,86 +7873,89 @@
       <c r="K81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M81" s="3">
         <v>492300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>523900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>542300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>461000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>428400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>376700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>300600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>285500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>210200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>163900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>138600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>163700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>411800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>391400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>434900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>694700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>555200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>579800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>572400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>373800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>481900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>590900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>329000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>399600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>273300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7795,115 +7993,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>191200</v>
+      </c>
+      <c r="E83" s="3">
         <v>238400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>211300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>208200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>208000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>236900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>204000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>216600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>229000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>273400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>235400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>243800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>247600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>215000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>241600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>251700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>247200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>245900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>256200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>271400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>302800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>296400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>294100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>299300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>320500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>309400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>301200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>299200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>316900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>301900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>295000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>296800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>238900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>226700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>222400</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8009,8 +8211,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8116,8 +8321,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8223,8 +8431,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8330,8 +8541,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8437,115 +8651,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="3">
         <v>603000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>933500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>521800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1033300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>646800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>682100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>590900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>928300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>408500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>177900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-15800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>770900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>188500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>669300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>474800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>813600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>636600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>759600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>469400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1208900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>202300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>715400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>530400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>982200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>259100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>677800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>603600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>3900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>357400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>376500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>971600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>448000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>444400</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8583,115 +8803,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="3">
         <v>-224300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-399300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-264500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-336800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-449000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-322700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-280300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-365800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-48655000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-49879000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-36378000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-39135000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-41538000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-44307000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-279100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-314200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-380900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-374000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-317900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-397700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-434800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-439600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-403000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-453500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-552400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-411600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-382200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-288700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-389600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-331300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-390900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-378000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-298900</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8797,8 +9021,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8904,115 +9131,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="3">
         <v>-329600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-442200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-254700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-289500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-562000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-281600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-272200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-290500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-323700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-331000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-225400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-262000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-239100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-285800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-218000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-258800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-341100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-347300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-302300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-366600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-388200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-542900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-436300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-432300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-524300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-408300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-388400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-520100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-228800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>103500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2769300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-347600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-233600</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9050,8 +9283,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9064,101 +9298,104 @@
       <c r="F96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>483400</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>490700</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>-429800</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3">
         <v>-357000</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-259900</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3">
         <v>-257100</v>
       </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-124700</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-314400</v>
       </c>
-      <c r="W96" s="3">
-        <v>0</v>
-      </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-473400</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-510400</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-454600</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-411800</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-307100</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-247400</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-242700</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9264,8 +9501,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9371,8 +9611,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9478,325 +9721,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E100" s="3">
         <v>-357100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-756600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>74500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-391600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>119200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-574500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>42900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-960600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>109900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-175500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>492900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-247600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>17200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-111700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-320400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-371100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-442100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-584000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-102700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-261700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>363600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-431900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>305300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-522600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>409300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-408800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>466900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-341500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>246200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-372500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>2673000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-763500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>417200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-385800</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-18300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>8400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-9400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-107000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-77500</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>227000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>40900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-100200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-71500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>207900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>33000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>21100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>10400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-8200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>19000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>10900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-17000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>10400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-20800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>12800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-24800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>62300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-40600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-66000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>69000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>13700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>8900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>13800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-66000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-18300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-434900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>426800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>394800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>185600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-175300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>370000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-332200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>94500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-400100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>459600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>294300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>275900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-53300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>175400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-127500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-160800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>63900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>563600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>188100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-280200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>412300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>206500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-179800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>11900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>35100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>97400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>278000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-125700</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>416200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-166700</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/KMTUY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/KMTUY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="92">
   <si>
     <t>KMTUY</t>
   </si>
@@ -656,159 +656,163 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -839,86 +843,89 @@
       <c r="L8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M8" s="3">
+      <c r="M8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N8" s="3">
         <v>6535500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5454400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5148100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5230000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4968900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>4637000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>4764800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>4794300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4072500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>3887100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3913000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5439500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5593100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>5548200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>5585500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>6790800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>6613400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>6242700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5872700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>6285600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>5847500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>5403600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5073300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5111600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3819400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3608800</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -949,86 +956,89 @@
       <c r="L9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M9" s="3">
+      <c r="M9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="3">
         <v>4573500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3841100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3676000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>3769800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>3589200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3298400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>3491800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3540700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2999800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2844100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2855200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3983000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4023200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>3933000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>3914600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4734300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4644500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4266600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4011000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4364100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4072000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3892100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>3635600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>3643900</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2714800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2572600</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1059,86 +1069,89 @@
       <c r="L10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M10" s="3">
+      <c r="M10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N10" s="3">
         <v>1962000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1613400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1472100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1460200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1379700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>1338600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1272900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1253500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1072700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1043000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1057800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1456500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>1569900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1615200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1670900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2056500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>1968800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>1976100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>1861700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1921400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1775500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>1511500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>1437700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1467700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1104600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>1036300</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1177,8 +1190,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1287,8 +1301,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1397,8 +1414,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1438,24 +1458,24 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>9100</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>17000</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1471,8 +1491,8 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1480,8 +1500,8 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
+      <c r="AD14" s="3">
+        <v>0</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1498,17 +1518,20 @@
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK14" s="3">
         <v>15500</v>
       </c>
-      <c r="AK14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1539,8 +1562,8 @@
       <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="M15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1617,8 +1640,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1654,8 +1680,9 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1686,86 +1713,89 @@
       <c r="L17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M17" s="3">
+      <c r="M17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N17" s="3">
         <v>5577300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>4701100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4517500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>4610800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>4367900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4099600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4310900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4370300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>3726600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3626700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3683400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5061800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4993300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4930400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>4900700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>5810800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>5711600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>5274100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4999600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>5531700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>5170900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4865900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>4606000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>4516700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>3438900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3304300</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1796,86 +1826,89 @@
       <c r="L18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M18" s="3">
+      <c r="M18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N18" s="3">
         <v>958300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>753300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>630600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>619200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>601000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>537400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>453900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>423900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>345900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>260400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>229600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>377800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>599900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>617800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>684800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>979900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>901800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>968600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>873100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>753900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>676500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>537700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>467400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>594900</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>380500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>304600</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1914,8 +1947,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1946,86 +1980,89 @@
       <c r="L20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N20" s="3">
         <v>-84700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>21900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>159000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>67100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>25400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>23800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>19600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>20000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>5800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>46200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-35100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>15000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>4900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-11000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>37200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-35000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>12000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>21000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-17900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>14300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>372500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-11900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>36500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>12800</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2056,86 +2093,89 @@
       <c r="L21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N21" s="3">
         <v>1146900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1010600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1033400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>933900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>841300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>802800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>725200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>691100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>597700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>517900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>547300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>645500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>911300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>916800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>973100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1337600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1176100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1281800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1193400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1052800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>992600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1205300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>763800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>821800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>643700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>539800</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2166,86 +2206,89 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>78000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>39700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>31500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>20600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>23100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>20100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>21800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>22700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>27800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>32800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>50200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>52700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>59300</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>60900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>61000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>59900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>55600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>49300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>44700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>46900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>42200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>32300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>22400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>16300</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2276,86 +2319,89 @@
       <c r="L23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M23" s="3">
+      <c r="M23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N23" s="3">
         <v>795500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>735500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>758100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>665700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>603200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>541100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>451700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>421300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>328600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>234000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>243100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>292400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>562200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>563400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>612900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>956100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>806800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>925000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>844800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>691300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>643900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>868000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>434800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>560600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>400600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>300600</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2386,86 +2432,89 @@
       <c r="L24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M24" s="3">
+      <c r="M24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N24" s="3">
         <v>272300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>187300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>198900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>204400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>158600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>149000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>132500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>113200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>101500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>56700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>83700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>114500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>129800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>163500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>163300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>239900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>227500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>274200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>254700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>293100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>142000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>259900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>85900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>135000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>124400</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>105900</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2574,8 +2623,11 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2606,86 +2658,89 @@
       <c r="L26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M26" s="3">
+      <c r="M26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N26" s="3">
         <v>523200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>548200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>559200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>461200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>444600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>392100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>319200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>308000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>227100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>177200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>159300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>177900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>432300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>399900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>449600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>716200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>579400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>650800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>590100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>398100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>501800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>608200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>348900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>425700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>276200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>194700</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2716,86 +2771,89 @@
       <c r="L27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M27" s="3">
+      <c r="M27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N27" s="3">
         <v>492300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>523900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>542300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>461000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>428400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>376700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>300600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>285500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>210200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>163900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>138600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>163700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>411800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>391400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>434900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>694700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>555200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>579800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>572400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>373800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>481900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>590900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>329000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>399600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>273300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2904,8 +2962,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2936,8 +2997,8 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -3014,8 +3075,11 @@
       <c r="AL29" s="3">
         <v>0</v>
       </c>
+      <c r="AM29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3124,8 +3188,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3234,8 +3301,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3266,86 +3336,89 @@
       <c r="L32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N32" s="3">
         <v>84700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-21900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-159000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-67100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-25400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-23800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-19600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-20000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-5800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-46200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>35100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>11000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-37200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>35000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-21000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>17900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-14300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-372500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>11900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-36500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-12800</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3376,86 +3449,89 @@
       <c r="L33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M33" s="3">
+      <c r="M33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N33" s="3">
         <v>492300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>523900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>542300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>461000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>428400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>376700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>300600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>285500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>210200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>163900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>138600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>163700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>411800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>391400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>434900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>694700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>555200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>579800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>572400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>373800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>481900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>590900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>329000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>399600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>273300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3564,8 +3640,11 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3596,201 +3675,207 @@
       <c r="L35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M35" s="3">
+      <c r="M35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N35" s="3">
         <v>492300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>523900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>542300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>461000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>428400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>376700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>300600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>285500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>210200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>163900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>138600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>163700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>411800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>391400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>434900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>694700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>555200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>579800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>572400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>373800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>481900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>590900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>329000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>399600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>273300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3829,8 +3914,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3869,8 +3955,9 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -3878,109 +3965,112 @@
         <v>8</v>
       </c>
       <c r="E41" s="3">
-        <v>2586500</v>
-      </c>
-      <c r="F41" s="3">
+        <v>2574800</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G41" s="3">
         <v>2858600</v>
       </c>
-      <c r="G41" s="3">
-        <v>2933100</v>
-      </c>
-      <c r="H41" s="3">
+      <c r="H41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I41" s="3">
         <v>2665600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2436500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2124300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2375600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2181300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2372400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2046900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2585100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2094000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1862000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1975600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1732900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1723800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1601600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1837300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2194200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2199600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1689900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1514000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1792800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1449300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1421600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1196300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1343400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1327600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1516900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1482200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1381200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1083800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1209600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>789900</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3997,38 +4087,38 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>25000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>22700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>33500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>36600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>33800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>14300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>7300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>8700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>15600</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
       <c r="S42" s="3">
         <v>0</v>
       </c>
@@ -4089,8 +4179,11 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -4098,109 +4191,112 @@
         <v>8</v>
       </c>
       <c r="E43" s="3">
-        <v>7889900</v>
-      </c>
-      <c r="F43" s="3">
+        <v>8542400</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G43" s="3">
         <v>8090200</v>
       </c>
-      <c r="G43" s="3">
-        <v>7925100</v>
-      </c>
-      <c r="H43" s="3">
+      <c r="H43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I43" s="3">
         <v>8399600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7993700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7485100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7882300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8383000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6885200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6610100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>6705900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6338400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>5855300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>5745200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>5791100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>5818700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>5049300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5218600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>5668600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>6558100</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7002300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>6799600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7109800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8093400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7464600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7593000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7131300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7166100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>6920900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>6481500</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>5949400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>5492900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>5117000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>4460600</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4208,109 +4304,112 @@
         <v>8</v>
       </c>
       <c r="E44" s="3">
-        <v>9957900</v>
-      </c>
-      <c r="F44" s="3">
+        <v>9393500</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3">
         <v>10168000</v>
       </c>
-      <c r="G44" s="3">
-        <v>9924600</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3">
         <v>9511700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>10355100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>9985900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>9645900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>9231700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>8832600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>8134700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7917100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>6560400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>6192300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>6123000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6020100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5628400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>6025000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6535000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>7393100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>7094800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>8199300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>8217800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>8015200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>8048900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>7793600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>7851600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>7246200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>6601800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>6847600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>6441600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>6211000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4735700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>5252300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>4645600</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4318,109 +4417,112 @@
         <v>8</v>
       </c>
       <c r="E45" s="3">
-        <v>1532900</v>
-      </c>
-      <c r="F45" s="3">
+        <v>1415000</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3">
         <v>1625000</v>
       </c>
-      <c r="G45" s="3">
-        <v>1521800</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3">
         <v>1192600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>1507000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1629000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1678900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1416200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1407800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1276600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1262900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1075800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1124300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>991000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1023700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>933200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>962600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1023800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>1269500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1298700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1368900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1225300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1322900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1330200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1291000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1205900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>1188900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1154700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1105700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1052800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1084600</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1278800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1242800</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1155000</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4428,109 +4530,112 @@
         <v>8</v>
       </c>
       <c r="E46" s="3">
-        <v>21967200</v>
-      </c>
-      <c r="F46" s="3">
+        <v>22025700</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G46" s="3">
         <v>22741800</v>
       </c>
-      <c r="G46" s="3">
-        <v>22304700</v>
-      </c>
-      <c r="H46" s="3">
+      <c r="H46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I46" s="3">
         <v>21911300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22314900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>21257800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>21619200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>21338200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>19512400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>18073000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>18478300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>16077300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>15049600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>14834700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>14567700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>14104100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>13638400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>14614700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>16525500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>17151200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>18260400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>17756700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>18240800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18921700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>17970800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>17846800</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>16909800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>16250200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>16391200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>15458100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>14626200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>12591200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>12821700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>11051100</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4538,109 +4643,112 @@
         <v>8</v>
       </c>
       <c r="E47" s="3">
-        <v>6618500</v>
-      </c>
-      <c r="F47" s="3">
+        <v>6462800</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3">
         <v>6518300</v>
       </c>
-      <c r="G47" s="3">
-        <v>6141100</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>543600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>566700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>481600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>495500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>506000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4571500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4370400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4307100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3692900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3632900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3650400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3831400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3505200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3513400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>3679600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>4108100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>4109500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>4302400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>4281700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>4254400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>4431700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>3945800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>4110500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>3870100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>3656300</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>3775100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>3603400</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>3962700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>3654400</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>3553700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>3114700</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -4648,109 +4756,112 @@
         <v>8</v>
       </c>
       <c r="E48" s="3">
-        <v>6325000</v>
-      </c>
-      <c r="F48" s="3">
+        <v>6557500</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G48" s="3">
         <v>6682600</v>
       </c>
-      <c r="G48" s="3">
-        <v>6287500</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I48" s="3">
         <v>6461200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>6736200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>6355000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>6446100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>6751400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>6317900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5942400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6174500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5851600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5836700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>6043400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>6152900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5993200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>6007500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>6325100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>6898700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>7146100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>7436500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>7400100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>7454200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>7461400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>7167800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>7111300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>6849300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>6694400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>6941200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>6903500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>6874400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>6023000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>6087900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>5725600</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -4758,109 +4869,112 @@
         <v>8</v>
       </c>
       <c r="E49" s="3">
-        <v>2738700</v>
-      </c>
-      <c r="F49" s="3">
+        <v>2776600</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G49" s="3">
         <v>2857100</v>
       </c>
-      <c r="G49" s="3">
-        <v>2800100</v>
-      </c>
-      <c r="H49" s="3">
+      <c r="H49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I49" s="3">
         <v>2834900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2960200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2667400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2733400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2816100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2643100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2594800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2585000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2367900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2330800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2406100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2479900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2408200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2370200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2505800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>2768200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>2815500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3096100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3079300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>2972100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3155200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3161900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3289100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3137100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2975000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3245200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3273300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3281300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>897200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>891700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>852900</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4969,8 +5083,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5079,8 +5196,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5096,101 +5216,104 @@
       <c r="G52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H52" s="3">
-        <v>300</v>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I52" s="3">
         <v>300</v>
       </c>
       <c r="J52" s="3">
+        <v>300</v>
+      </c>
+      <c r="K52" s="3">
         <v>500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>919000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>935600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>908800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>877800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>818200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>849300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>827500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>823800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>807200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>875700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>926900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>966700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>877800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>911400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>893200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>993200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>881500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>914100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>875400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>911800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>925500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>867000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>685400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>397300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>395700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>472700</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5299,8 +5422,11 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
@@ -5308,109 +5434,112 @@
         <v>8</v>
       </c>
       <c r="E54" s="3">
-        <v>37649300</v>
-      </c>
-      <c r="F54" s="3">
+        <v>38554900</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G54" s="3">
         <v>38799800</v>
       </c>
-      <c r="G54" s="3">
-        <v>37533500</v>
-      </c>
-      <c r="H54" s="3">
+      <c r="H54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I54" s="3">
         <v>37265900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>38091300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>36181100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>36643400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>36678700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>33963900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>31916200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>32453700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>28867500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>27668100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>27783800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>27859400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>26834500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>26336600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>28001000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>31227300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>32189000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>33973200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>33429200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>33814600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>34963300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>33127800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>33271700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>31641700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>30487700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>31278300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>30105200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>29429900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>23563000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>23750700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>21217100</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5449,8 +5578,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5489,8 +5619,9 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -5498,109 +5629,112 @@
         <v>8</v>
       </c>
       <c r="E57" s="3">
-        <v>2009600</v>
-      </c>
-      <c r="F57" s="3">
+        <v>2236600</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G57" s="3">
         <v>2197800</v>
       </c>
-      <c r="G57" s="3">
-        <v>2033200</v>
-      </c>
-      <c r="H57" s="3">
+      <c r="H57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I57" s="3">
         <v>2117700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2283500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2334400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2540800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2725900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2400400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2272000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2341700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2250800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1971700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1939100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1908900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1831500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1597300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1511700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1742400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1939600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2091700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2278800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2338800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2565400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2413100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2557500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2485200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>2744100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2742000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2594600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2526300</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>2129800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>1891800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>1680000</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5608,109 +5742,112 @@
         <v>8</v>
       </c>
       <c r="E58" s="3">
-        <v>5519900</v>
-      </c>
-      <c r="F58" s="3">
+        <v>4499600</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G58" s="3">
         <v>5145100</v>
       </c>
-      <c r="G58" s="3">
-        <v>5344300</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="H58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I58" s="3">
         <v>3976200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4600800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3474900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4366200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3813300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4369600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4638700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4641200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3442000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3599600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3247400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2968400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2619500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>2928500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3409100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>5190700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>5308400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>5845400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5004000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4708300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>4403400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4835900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>3995900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4127800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>2982300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3226400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>2743000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>4866100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1932300</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2705700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1856900</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -5718,109 +5855,112 @@
         <v>8</v>
       </c>
       <c r="E59" s="3">
-        <v>3973300</v>
-      </c>
-      <c r="F59" s="3">
+        <v>2964700</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G59" s="3">
         <v>4076100</v>
       </c>
-      <c r="G59" s="3">
-        <v>3891200</v>
-      </c>
-      <c r="H59" s="3">
+      <c r="H59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I59" s="3">
         <v>2772300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3913300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3840200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3867500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>2613000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3478900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3172600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3188000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3098700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>2715800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>2697500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2611000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2588500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>2524800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2635500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2809300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2959500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>3169700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>3262900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>3290300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>3430500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>3011500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3336600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3020600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3220100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3131200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>2985200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>2675700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>2148500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1977100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1932900</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5828,109 +5968,112 @@
         <v>8</v>
       </c>
       <c r="E60" s="3">
-        <v>11502800</v>
-      </c>
-      <c r="F60" s="3">
+        <v>11014200</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G60" s="3">
         <v>11419000</v>
       </c>
-      <c r="G60" s="3">
-        <v>11268800</v>
-      </c>
-      <c r="H60" s="3">
+      <c r="H60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I60" s="3">
         <v>10090200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10797500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9649600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10774500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10318400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>10248800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10083400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10170900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>8791500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>8287000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>7884100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>7488300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>7039400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>7050600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>7556300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>9742300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10207500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11106800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>10545700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>10337400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>10399400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>10260500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>9890100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>9633600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>8946500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>9099600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>8322800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>10068000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>6210600</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>6574700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>5469800</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -5938,109 +6081,112 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>3603500</v>
+        <v>3652100</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
         <v>4100600</v>
       </c>
-      <c r="G61" s="3">
-        <v>3992200</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>4441300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4454300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4727900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4457000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4600800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3890000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2829400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3203300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2848600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2748000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2986100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3685700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3832300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3788600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4116400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3747600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>3610700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3704600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3739100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4491900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4540600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4285500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4526300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>4365800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>4345500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>4771500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>4645600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>2829700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1692900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1742600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1577700</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6048,109 +6194,112 @@
         <v>8</v>
       </c>
       <c r="E62" s="3">
-        <v>1065500</v>
-      </c>
-      <c r="F62" s="3">
+        <v>940300</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3">
         <v>1092200</v>
       </c>
-      <c r="G62" s="3">
-        <v>1051000</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I62" s="3">
         <v>2500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>3400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1803200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1699100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1735200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1581700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1611800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1672700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1756800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1697600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1628100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1786600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1929800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>2017500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1936900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1955600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1946800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1736800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1588900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1545500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1485000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1433600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>1437400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>1448700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>1400700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>1037100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>1041600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>965200</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6259,8 +6408,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6369,8 +6521,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6479,8 +6634,11 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -6488,109 +6646,112 @@
         <v>8</v>
       </c>
       <c r="E66" s="3">
-        <v>16690100</v>
-      </c>
-      <c r="F66" s="3">
+        <v>16218400</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G66" s="3">
         <v>17155500</v>
       </c>
-      <c r="G66" s="3">
-        <v>16811800</v>
-      </c>
-      <c r="H66" s="3">
+      <c r="H66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I66" s="3">
         <v>16119800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>16881700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>15983100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16815400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>16533700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>16869600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>15474000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15972600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>14043700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>13489900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>13380200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>13660300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>13276300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>13146300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>14153500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>16184500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>16581100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>17541800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>16997900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>17543800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>17515500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>16912800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>16751000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>16218100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>15440300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>16046200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>15109600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>14968700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>9577900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>9984500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>8556800</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6629,8 +6790,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6739,8 +6901,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6849,8 +7014,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6959,8 +7127,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7069,8 +7240,11 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -7078,109 +7252,112 @@
         <v>8</v>
       </c>
       <c r="E72" s="3">
-        <v>15852300</v>
-      </c>
-      <c r="F72" s="3">
+        <v>17508400</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3">
         <v>17644500</v>
       </c>
-      <c r="G72" s="3">
-        <v>15142000</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3">
         <v>15973000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>16506900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>15373800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>15189300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>16273500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>14688600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>13142900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>13331000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12950700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>12922300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>13385000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>13260900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12749900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12886400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>13604200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>14720100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>15384800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>15739500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>15939800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>15497700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>16338300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>15366800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>15023600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>14132800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>13901600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>13527900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>13353100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>12762200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>12442100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>12042600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>12011900</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7289,8 +7466,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7399,8 +7579,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7509,8 +7692,11 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -7518,109 +7704,112 @@
         <v>8</v>
       </c>
       <c r="E76" s="3">
-        <v>19891900</v>
-      </c>
-      <c r="F76" s="3">
+        <v>21191600</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G76" s="3">
         <v>20490500</v>
       </c>
-      <c r="G76" s="3">
-        <v>19639200</v>
-      </c>
-      <c r="H76" s="3">
+      <c r="H76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I76" s="3">
         <v>20056000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20121200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19183300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>18804800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19104500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>17094300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>16442200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16481100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14823900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14178100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14403600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>14199100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>13558200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13190300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>13847500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>15042800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>15607800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16431500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>16431400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>16270800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>17447700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>16215000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>16520700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>15423500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>15047400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>15232100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>14995700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>14461200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>13985100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>13766200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>12660300</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7729,123 +7918,129 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -7876,86 +8071,89 @@
       <c r="L81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M81" s="3">
+      <c r="M81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N81" s="3">
         <v>492300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>523900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>542300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>461000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>428400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>376700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>300600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>285500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>210200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>163900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>138600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>163700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>411800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>391400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>434900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>694700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>555200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>579800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>572400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>373800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>481900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>590900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>329000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>399600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>273300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>194500</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7994,118 +8192,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3">
         <v>191200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>238400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>211300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>208200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>208000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>236900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>204000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>216600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>229000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>273400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>235400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>243800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>247600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>215000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>241600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>251700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>247200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>245900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>256200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>271400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>302800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>296400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>294100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>299300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>320500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>309400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>301200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>299200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>316900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>301900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>295000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>296800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>238900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>226700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>222400</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8214,8 +8416,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8324,8 +8529,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8434,8 +8642,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8544,8 +8755,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8654,8 +8868,11 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -8663,109 +8880,112 @@
         <v>8</v>
       </c>
       <c r="E89" s="3">
-        <v>603000</v>
-      </c>
-      <c r="F89" s="3">
+        <v>1366900</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3">
         <v>933500</v>
       </c>
-      <c r="G89" s="3">
-        <v>521800</v>
-      </c>
-      <c r="H89" s="3">
+      <c r="H89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I89" s="3">
         <v>1033300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>646800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>682100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>590900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>928300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>408500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>177900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-15800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>770900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>188500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>669300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>474800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>813600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>636600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>759600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>469400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1208900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>202300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>715400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>530400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>982200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>259100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>677800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>603600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>357400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>376500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>971600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>448000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>444400</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8804,8 +9024,9 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8813,109 +9034,112 @@
         <v>8</v>
       </c>
       <c r="E91" s="3">
-        <v>-224300</v>
-      </c>
-      <c r="F91" s="3">
+        <v>-473000</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3">
         <v>-399300</v>
       </c>
-      <c r="G91" s="3">
-        <v>-264500</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="H91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I91" s="3">
         <v>-336800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-449000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-322700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-280300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-365800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-48655000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-49879000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-36378000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-39135000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-41538000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-44307000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-279100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-314200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-380900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-374000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-317900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-397700</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-434800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-439600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-403000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-453500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-552400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-411600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-382200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-288700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-389600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-331300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-390900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-378000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-358000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-298900</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9024,8 +9248,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9134,8 +9361,11 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -9143,109 +9373,112 @@
         <v>8</v>
       </c>
       <c r="E94" s="3">
-        <v>-329600</v>
-      </c>
-      <c r="F94" s="3">
+        <v>-364200</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3">
         <v>-442200</v>
       </c>
-      <c r="G94" s="3">
-        <v>-254700</v>
-      </c>
-      <c r="H94" s="3">
+      <c r="H94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I94" s="3">
         <v>-289500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-562000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-281600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-272200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-290500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-323700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-331000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-225400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-262000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-239100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-285800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-218000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-258800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-341100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-347300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-302300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-366600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-388200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-542900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-436300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-432300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-524300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-408300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-388400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-520100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-228800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>103500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2769300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-347600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-383000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-233600</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9284,8 +9517,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9301,101 +9535,104 @@
       <c r="G96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>483400</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>490700</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-429800</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
+        <v>0</v>
+      </c>
+      <c r="P96" s="3">
         <v>-357000</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3">
         <v>-259900</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-257100</v>
       </c>
-      <c r="T96" s="3">
-        <v>0</v>
-      </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-124700</v>
       </c>
-      <c r="V96" s="3">
-        <v>0</v>
-      </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-314400</v>
       </c>
-      <c r="X96" s="3">
-        <v>0</v>
-      </c>
       <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-473400</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-510400</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-454600</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-411800</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-307100</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-247400</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-242700</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9504,8 +9741,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9614,8 +9854,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9724,8 +9967,11 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -9733,219 +9979,225 @@
         <v>8</v>
       </c>
       <c r="E100" s="3">
-        <v>-357100</v>
-      </c>
-      <c r="F100" s="3">
+        <v>-1127700</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3">
         <v>-756600</v>
       </c>
-      <c r="G100" s="3">
-        <v>74500</v>
-      </c>
-      <c r="H100" s="3">
+      <c r="H100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I100" s="3">
         <v>-391600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>119200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-574500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>42900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-960600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>109900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-175500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>492900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-247600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>17200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-111700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-320400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-371100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-442100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-584000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-102700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-261700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>363600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-431900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>305300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-522600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>409300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-408800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>466900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-341500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>246200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-372500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>2673000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-763500</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>417200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-385800</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3">
         <v>42600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-18300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>8400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-107000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-77500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>227000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>40900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-100200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-71500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>207900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>33000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>21100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>10400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-8200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>19000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>10900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-17000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>10400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-20800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>12800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-24800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>62300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-40600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-66000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>69000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>13700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>8900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>13800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-66000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>8300</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -9953,105 +10205,108 @@
         <v>0</v>
       </c>
       <c r="E102" s="3">
-        <v>-18300</v>
+        <v>-140800</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-434900</v>
       </c>
-      <c r="G102" s="3">
-        <v>426800</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>394800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>185600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-175300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>370000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-332200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>94500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-400100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>459600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>294300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-12300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>275900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-53300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>175400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-127500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-160800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>63900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>563600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>188100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-280200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>412300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>2500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>206500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-179800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>11900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-189000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>35100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>97400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>278000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-125700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>416200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-166700</v>
       </c>
     </row>
